--- a/outputs/workbook_mining/literature_mining_collected.xlsx
+++ b/outputs/workbook_mining/literature_mining_collected.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="데이터마이닝" sheetId="1" r:id="R80264aaadc82490a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확보현황" sheetId="2" r:id="R8fc4f8e164b04275"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문헌검토" sheetId="3" r:id="Rb27356de8dab42a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="데이터마이닝" sheetId="1" r:id="R32210cbd860e460f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확보현황" sheetId="2" r:id="R65d57c03dae04f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문헌검토" sheetId="3" r:id="R54c9fed05baa4382"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -172,8 +172,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MiningRecords" displayName="MiningRecords" ref="A1:BE115" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="57">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MiningRecords" displayName="MiningRecords" ref="A1:BF152" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="58">
     <x:tableColumn id="1" name="논문#"/>
     <x:tableColumn id="2" name="강종"/>
     <x:tableColumn id="3" name="시료"/>
@@ -225,20 +225,21 @@
     <x:tableColumn id="49" name="RE_total_wt_pct"/>
     <x:tableColumn id="50" name="B_addition_wt_pct"/>
     <x:tableColumn id="51" name="REO_addition_wt_pct"/>
-    <x:tableColumn id="52" name="S_upper_bound_wt_pct"/>
-    <x:tableColumn id="53" name="missing_measurement_count"/>
-    <x:tableColumn id="54" name="all_measurements_complete"/>
-    <x:tableColumn id="55" name="eligible_under_requested_all_column_policy"/>
-    <x:tableColumn id="56" name="missing_measurement_columns"/>
-    <x:tableColumn id="57" name="remarks"/>
+    <x:tableColumn id="52" name="surface_Ce_at_pct"/>
+    <x:tableColumn id="53" name="S_upper_bound_wt_pct"/>
+    <x:tableColumn id="54" name="missing_measurement_count"/>
+    <x:tableColumn id="55" name="all_measurements_complete"/>
+    <x:tableColumn id="56" name="eligible_under_requested_all_column_policy"/>
+    <x:tableColumn id="57" name="missing_measurement_columns"/>
+    <x:tableColumn id="58" name="remarks"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="LiteratureReview" displayName="LiteratureReview" ref="A1:J50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="LiteratureReview" displayName="LiteratureReview" ref="A1:K50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="11">
     <x:tableColumn id="1" name="paper_number"/>
     <x:tableColumn id="2" name="doi"/>
     <x:tableColumn id="3" name="paper_title"/>
@@ -248,7 +249,8 @@
     <x:tableColumn id="7" name="reported_icorr_rows"/>
     <x:tableColumn id="8" name="full_measurement_rows"/>
     <x:tableColumn id="9" name="this_batch_status"/>
-    <x:tableColumn id="10" name="workbook_note"/>
+    <x:tableColumn id="10" name="source_access_result"/>
+    <x:tableColumn id="11" name="workbook_note"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -504,8 +506,9 @@
     <x:col min="53" max="53" width="14" hidden="0" customWidth="1"/>
     <x:col min="54" max="54" width="14" hidden="0" customWidth="1"/>
     <x:col min="55" max="55" width="14" hidden="0" customWidth="1"/>
-    <x:col min="56" max="56" width="70" hidden="0" customWidth="1"/>
+    <x:col min="56" max="56" width="14" hidden="0" customWidth="1"/>
     <x:col min="57" max="57" width="70" hidden="0" customWidth="1"/>
+    <x:col min="58" max="58" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
@@ -663,21 +666,24 @@
         <x:v>REO_addition_wt_pct</x:v>
       </x:c>
       <x:c r="AZ1" s="7" t="str">
+        <x:v>surface_Ce_at_pct</x:v>
+      </x:c>
+      <x:c r="BA1" s="7" t="str">
         <x:v>S_upper_bound_wt_pct</x:v>
       </x:c>
-      <x:c r="BA1" s="7" t="str">
+      <x:c r="BB1" s="7" t="str">
         <x:v>missing_measurement_count</x:v>
       </x:c>
-      <x:c r="BB1" s="7" t="str">
+      <x:c r="BC1" s="7" t="str">
         <x:v>all_measurements_complete</x:v>
       </x:c>
-      <x:c r="BC1" s="7" t="str">
+      <x:c r="BD1" s="7" t="str">
         <x:v>eligible_under_requested_all_column_policy</x:v>
       </x:c>
-      <x:c r="BD1" s="7" t="str">
+      <x:c r="BE1" s="7" t="str">
         <x:v>missing_measurement_columns</x:v>
       </x:c>
-      <x:c r="BE1" s="7" t="str">
+      <x:c r="BF1" s="7" t="str">
         <x:v>remarks</x:v>
       </x:c>
     </x:row>
@@ -788,19 +794,20 @@
       <x:c r="AX2" s="12"/>
       <x:c r="AY2" s="12"/>
       <x:c r="AZ2" s="12"/>
-      <x:c r="BA2" s="12" t="n">
+      <x:c r="BA2" s="12"/>
+      <x:c r="BB2" s="12" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="BB2" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC2" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD2" s="12" t="str">
+      <x:c r="BD2" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE2" s="12" t="str">
         <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min)</x:v>
       </x:c>
-      <x:c r="BE2" s="12" t="str">
+      <x:c r="BF2" s="12" t="str">
         <x:v>Al vs Ti/Zr 탈산법 동시 변화; RE 인과효과로 해석 금지; control_composition_unreported</x:v>
       </x:c>
     </x:row>
@@ -913,19 +920,20 @@
       <x:c r="AX3" s="12"/>
       <x:c r="AY3" s="12"/>
       <x:c r="AZ3" s="12"/>
-      <x:c r="BA3" s="12" t="n">
+      <x:c r="BA3" s="12"/>
+      <x:c r="BB3" s="12" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="BB3" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC3" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD3" s="12" t="str">
+      <x:c r="BD3" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE3" s="12" t="str">
         <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min)</x:v>
       </x:c>
-      <x:c r="BE3" s="12" t="str">
+      <x:c r="BF3" s="12" t="str">
         <x:v>Al vs Ti/Zr 탈산법 동시 변화; RE 인과효과로 해석 금지; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -1038,19 +1046,20 @@
       <x:c r="AX4" s="12"/>
       <x:c r="AY4" s="12"/>
       <x:c r="AZ4" s="12"/>
-      <x:c r="BA4" s="12" t="n">
+      <x:c r="BA4" s="12"/>
+      <x:c r="BB4" s="12" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="BB4" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC4" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD4" s="12" t="str">
+      <x:c r="BD4" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE4" s="12" t="str">
         <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min)</x:v>
       </x:c>
-      <x:c r="BE4" s="12" t="str">
+      <x:c r="BF4" s="12" t="str">
         <x:v>Al vs Ti/Zr 탈산법 동시 변화; RE 인과효과로 해석 금지; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -1155,19 +1164,20 @@
       <x:c r="AX5" s="12"/>
       <x:c r="AY5" s="12"/>
       <x:c r="AZ5" s="12"/>
-      <x:c r="BA5" s="12" t="n">
+      <x:c r="BA5" s="12"/>
+      <x:c r="BB5" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB5" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC5" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD5" s="12" t="str">
+      <x:c r="BD5" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE5" s="12" t="str">
         <x:v>P; S; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE5" s="12" t="str">
+      <x:c r="BF5" s="12" t="str">
         <x:v>Sb 동시 변화; Ecorr 원문 mV/수치 불일치; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -1274,19 +1284,20 @@
       <x:c r="AX6" s="12"/>
       <x:c r="AY6" s="12"/>
       <x:c r="AZ6" s="12"/>
-      <x:c r="BA6" s="12" t="n">
+      <x:c r="BA6" s="12"/>
+      <x:c r="BB6" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB6" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC6" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD6" s="12" t="str">
+      <x:c r="BD6" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE6" s="12" t="str">
         <x:v>P; S; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE6" s="12" t="str">
+      <x:c r="BF6" s="12" t="str">
         <x:v>Sb 동시 변화; Ecorr 원문 mV/수치 불일치; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -1393,19 +1404,20 @@
       <x:c r="AX7" s="12"/>
       <x:c r="AY7" s="12"/>
       <x:c r="AZ7" s="12"/>
-      <x:c r="BA7" s="12" t="n">
+      <x:c r="BA7" s="12"/>
+      <x:c r="BB7" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB7" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC7" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD7" s="12" t="str">
+      <x:c r="BD7" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE7" s="12" t="str">
         <x:v>P; S; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE7" s="12" t="str">
+      <x:c r="BF7" s="12" t="str">
         <x:v>Sb 동시 변화; Ecorr 원문 mV/수치 불일치; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -1518,19 +1530,20 @@
       <x:c r="AX8" s="12"/>
       <x:c r="AY8" s="12"/>
       <x:c r="AZ8" s="12"/>
-      <x:c r="BA8" s="12" t="n">
+      <x:c r="BA8" s="12"/>
+      <x:c r="BB8" s="12" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="BB8" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC8" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD8" s="12" t="str">
+      <x:c r="BD8" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE8" s="12" t="str">
         <x:v>T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; Time(min); 냉각방식; 침지시간(min); 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE8" s="12" t="str">
+      <x:c r="BF8" s="12" t="str">
         <x:v>용체화1050°C; 별도 FeCl3 시험조건은 PDP에 넣지 않음; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -1645,19 +1658,20 @@
       <x:c r="AX9" s="12"/>
       <x:c r="AY9" s="12"/>
       <x:c r="AZ9" s="12"/>
-      <x:c r="BA9" s="12" t="n">
+      <x:c r="BA9" s="12"/>
+      <x:c r="BB9" s="12" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="BB9" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC9" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD9" s="12" t="str">
+      <x:c r="BD9" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE9" s="12" t="str">
         <x:v>T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; Time(min); 냉각방식; 침지시간(min); 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE9" s="12" t="str">
+      <x:c r="BF9" s="12" t="str">
         <x:v>용체화1050°C; 별도 FeCl3 시험조건은 PDP에 넣지 않음; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -1772,19 +1786,20 @@
       <x:c r="AX10" s="12"/>
       <x:c r="AY10" s="12"/>
       <x:c r="AZ10" s="12"/>
-      <x:c r="BA10" s="12" t="n">
+      <x:c r="BA10" s="12"/>
+      <x:c r="BB10" s="12" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="BB10" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC10" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD10" s="12" t="str">
+      <x:c r="BD10" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE10" s="12" t="str">
         <x:v>T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; Time(min); 냉각방식; 침지시간(min); 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE10" s="12" t="str">
+      <x:c r="BF10" s="12" t="str">
         <x:v>용체화1050°C; 별도 FeCl3 시험조건은 PDP에 넣지 않음; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -1889,19 +1904,20 @@
       <x:c r="AX11" s="12"/>
       <x:c r="AY11" s="12"/>
       <x:c r="AZ11" s="12"/>
-      <x:c r="BA11" s="12" t="n">
+      <x:c r="BA11" s="12"/>
+      <x:c r="BB11" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB11" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC11" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD11" s="12" t="str">
+      <x:c r="BD11" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE11" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE11" s="12" t="str">
+      <x:c r="BF11" s="12" t="str">
         <x:v>PDP ±5mV 범위 원문 기재; Ce 초록/Table2 불일치; Table2 사용; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -2008,19 +2024,20 @@
       <x:c r="AX12" s="12"/>
       <x:c r="AY12" s="12"/>
       <x:c r="AZ12" s="12"/>
-      <x:c r="BA12" s="12" t="n">
+      <x:c r="BA12" s="12"/>
+      <x:c r="BB12" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB12" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC12" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD12" s="12" t="str">
+      <x:c r="BD12" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE12" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE12" s="12" t="str">
+      <x:c r="BF12" s="12" t="str">
         <x:v>PDP ±5mV 범위 원문 기재; Ce 초록/Table2 불일치; Table2 사용; RE_measured_other_composition_unreported</x:v>
       </x:c>
     </x:row>
@@ -2127,19 +2144,20 @@
       <x:c r="AX13" s="12"/>
       <x:c r="AY13" s="12"/>
       <x:c r="AZ13" s="12"/>
-      <x:c r="BA13" s="12" t="n">
+      <x:c r="BA13" s="12"/>
+      <x:c r="BB13" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB13" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC13" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD13" s="12" t="str">
+      <x:c r="BD13" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE13" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE13" s="12" t="str">
+      <x:c r="BF13" s="12" t="str">
         <x:v>PDP ±5mV 범위 원문 기재; Ce 초록/Table2 불일치; Table2 사용; RE_measured_other_composition_unreported</x:v>
       </x:c>
     </x:row>
@@ -2246,19 +2264,20 @@
       <x:c r="AX14" s="12"/>
       <x:c r="AY14" s="12"/>
       <x:c r="AZ14" s="12"/>
-      <x:c r="BA14" s="12" t="n">
+      <x:c r="BA14" s="12"/>
+      <x:c r="BB14" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB14" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC14" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD14" s="12" t="str">
+      <x:c r="BD14" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE14" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE14" s="12" t="str">
+      <x:c r="BF14" s="12" t="str">
         <x:v>PDP ±5mV 범위 원문 기재; Ce 초록/Table2 불일치; Table2 사용; RE_measured_other_composition_unreported</x:v>
       </x:c>
     </x:row>
@@ -2369,19 +2388,20 @@
       <x:c r="AX15" s="12"/>
       <x:c r="AY15" s="12"/>
       <x:c r="AZ15" s="12"/>
-      <x:c r="BA15" s="12" t="n">
+      <x:c r="BA15" s="12"/>
+      <x:c r="BB15" s="12" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="BB15" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC15" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD15" s="12" t="str">
+      <x:c r="BD15" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE15" s="12" t="str">
         <x:v>Ni; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; Y; La+Ce_합산; Fe; PREN; 냉각방식; 전해질 농도(wt%); 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE15" s="12" t="str">
+      <x:c r="BF15" s="12" t="str">
         <x:v>W 동시 첨가; Ecorr 부호/단위 모호하므로 Ecorr 미사용; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -2494,19 +2514,20 @@
       <x:c r="AX16" s="12"/>
       <x:c r="AY16" s="12"/>
       <x:c r="AZ16" s="12"/>
-      <x:c r="BA16" s="12" t="n">
+      <x:c r="BA16" s="12"/>
+      <x:c r="BB16" s="12" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="BB16" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC16" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD16" s="12" t="str">
+      <x:c r="BD16" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE16" s="12" t="str">
         <x:v>Ni; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; Y; La+Ce_합산; Fe; PREN; 냉각방식; 전해질 농도(wt%); 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE16" s="12" t="str">
+      <x:c r="BF16" s="12" t="str">
         <x:v>W 동시 첨가; Ecorr 부호/단위 모호하므로 Ecorr 미사용; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -2619,19 +2640,20 @@
       <x:c r="AX17" s="12"/>
       <x:c r="AY17" s="12"/>
       <x:c r="AZ17" s="12"/>
-      <x:c r="BA17" s="12" t="n">
+      <x:c r="BA17" s="12"/>
+      <x:c r="BB17" s="12" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="BB17" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC17" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD17" s="12" t="str">
+      <x:c r="BD17" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE17" s="12" t="str">
         <x:v>Ni; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; Y; La+Ce_합산; Fe; PREN; 냉각방식; 전해질 농도(wt%); 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE17" s="12" t="str">
+      <x:c r="BF17" s="12" t="str">
         <x:v>W 동시 첨가; Ecorr 부호/단위 모호하므로 Ecorr 미사용; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -2744,19 +2766,20 @@
       <x:c r="AX18" s="12"/>
       <x:c r="AY18" s="12"/>
       <x:c r="AZ18" s="12"/>
-      <x:c r="BA18" s="12" t="n">
+      <x:c r="BA18" s="12"/>
+      <x:c r="BB18" s="12" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="BB18" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC18" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD18" s="12" t="str">
+      <x:c r="BD18" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE18" s="12" t="str">
         <x:v>Ni; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; Y; La+Ce_합산; Fe; PREN; 냉각방식; 전해질 농도(wt%); 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE18" s="12" t="str">
+      <x:c r="BF18" s="12" t="str">
         <x:v>W 동시 첨가; Ecorr 부호/단위 모호하므로 Ecorr 미사용; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -2859,19 +2882,20 @@
       <x:c r="AX19" s="12"/>
       <x:c r="AY19" s="12"/>
       <x:c r="AZ19" s="12"/>
-      <x:c r="BA19" s="12" t="n">
+      <x:c r="BA19" s="12"/>
+      <x:c r="BB19" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB19" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC19" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD19" s="12" t="str">
+      <x:c r="BD19" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE19" s="12" t="str">
         <x:v>P; S; Mo; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 주사속도(mV/s)</x:v>
       </x:c>
-      <x:c r="BE19" s="12" t="str">
+      <x:c r="BF19" s="12" t="str">
         <x:v>시험온도 수치 미기재: 염수분무25°C를 PDP 온도로 대체하지 않음; 3.5%NaCl 맥락 연결; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -2976,19 +3000,20 @@
       <x:c r="AX20" s="12"/>
       <x:c r="AY20" s="12"/>
       <x:c r="AZ20" s="12"/>
-      <x:c r="BA20" s="12" t="n">
+      <x:c r="BA20" s="12"/>
+      <x:c r="BB20" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB20" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC20" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD20" s="12" t="str">
+      <x:c r="BD20" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE20" s="12" t="str">
         <x:v>P; S; Mo; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 주사속도(mV/s)</x:v>
       </x:c>
-      <x:c r="BE20" s="12" t="str">
+      <x:c r="BF20" s="12" t="str">
         <x:v>시험온도 수치 미기재: 염수분무25°C를 PDP 온도로 대체하지 않음; 3.5%NaCl 맥락 연결; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -3093,19 +3118,20 @@
       <x:c r="AX21" s="12"/>
       <x:c r="AY21" s="12"/>
       <x:c r="AZ21" s="12"/>
-      <x:c r="BA21" s="12" t="n">
+      <x:c r="BA21" s="12"/>
+      <x:c r="BB21" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB21" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC21" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD21" s="12" t="str">
+      <x:c r="BD21" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE21" s="12" t="str">
         <x:v>P; S; Mo; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 주사속도(mV/s)</x:v>
       </x:c>
-      <x:c r="BE21" s="12" t="str">
+      <x:c r="BF21" s="12" t="str">
         <x:v>시험온도 수치 미기재: 염수분무25°C를 PDP 온도로 대체하지 않음; 3.5%NaCl 맥락 연결; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -3216,19 +3242,20 @@
       <x:c r="AX22" s="12"/>
       <x:c r="AY22" s="12"/>
       <x:c r="AZ22" s="12"/>
-      <x:c r="BA22" s="12" t="n">
+      <x:c r="BA22" s="12"/>
+      <x:c r="BB22" s="12" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="BB22" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC22" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD22" s="12" t="str">
+      <x:c r="BD22" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE22" s="12" t="str">
         <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE22" s="12" t="str">
+      <x:c r="BF22" s="12" t="str">
         <x:v>La .0015+Ce .0025; C/R 공정·비RE 조성 교란; 원문 mA 단위 명시; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -3339,19 +3366,20 @@
       <x:c r="AX23" s="12"/>
       <x:c r="AY23" s="12"/>
       <x:c r="AZ23" s="12"/>
-      <x:c r="BA23" s="12" t="n">
+      <x:c r="BA23" s="12"/>
+      <x:c r="BB23" s="12" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="BB23" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC23" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD23" s="12" t="str">
+      <x:c r="BD23" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE23" s="12" t="str">
         <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE23" s="12" t="str">
+      <x:c r="BF23" s="12" t="str">
         <x:v>La .0015+Ce .0025; C/R 공정·비RE 조성 교란; 원문 mA 단위 명시; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -3460,19 +3488,20 @@
       <x:c r="AX24" s="12"/>
       <x:c r="AY24" s="12"/>
       <x:c r="AZ24" s="12"/>
-      <x:c r="BA24" s="12" t="n">
+      <x:c r="BA24" s="12"/>
+      <x:c r="BB24" s="12" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="BB24" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC24" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD24" s="12" t="str">
+      <x:c r="BD24" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE24" s="12" t="str">
         <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE24" s="12" t="str">
+      <x:c r="BF24" s="12" t="str">
         <x:v>La .0015+Ce .0025; C/R 공정·비RE 조성 교란; 원문 mA 단위 명시; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -3581,19 +3610,20 @@
       <x:c r="AX25" s="12"/>
       <x:c r="AY25" s="12"/>
       <x:c r="AZ25" s="12"/>
-      <x:c r="BA25" s="12" t="n">
+      <x:c r="BA25" s="12"/>
+      <x:c r="BB25" s="12" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="BB25" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC25" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD25" s="12" t="str">
+      <x:c r="BD25" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE25" s="12" t="str">
         <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE25" s="12" t="str">
+      <x:c r="BF25" s="12" t="str">
         <x:v>La .0015+Ce .0025; C/R 공정·비RE 조성 교란; 원문 mA 단위 명시; reported_sample</x:v>
       </x:c>
     </x:row>
@@ -3702,19 +3732,20 @@
       <x:c r="AX26" s="12"/>
       <x:c r="AY26" s="12"/>
       <x:c r="AZ26" s="12"/>
-      <x:c r="BA26" s="12" t="n">
+      <x:c r="BA26" s="12"/>
+      <x:c r="BB26" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB26" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC26" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD26" s="12" t="str">
+      <x:c r="BD26" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE26" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE26" s="12" t="str">
+      <x:c r="BF26" s="12" t="str">
         <x:v>Exact Table2 target replaces old estimates; PDP surface/pre-exposure mapping ambiguous;72h belongs to separate cyclic test and not assigned toPDP; roomtemperature not25C; reheating1200C/coiling550C not finalHT; reported_steel_composition</x:v>
       </x:c>
     </x:row>
@@ -3823,19 +3854,20 @@
       <x:c r="AX27" s="12"/>
       <x:c r="AY27" s="12"/>
       <x:c r="AZ27" s="12"/>
-      <x:c r="BA27" s="12" t="n">
+      <x:c r="BA27" s="12"/>
+      <x:c r="BB27" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB27" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC27" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD27" s="12" t="str">
+      <x:c r="BD27" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE27" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE27" s="12" t="str">
+      <x:c r="BF27" s="12" t="str">
         <x:v>Exact Table2 target replaces old estimates; PDP surface/pre-exposure mapping ambiguous;72h belongs to separate cyclic test and not assigned toPDP; roomtemperature not25C; reheating1200C/coiling550C not finalHT; reported_steel_composition</x:v>
       </x:c>
     </x:row>
@@ -3944,19 +3976,20 @@
       <x:c r="AX28" s="12"/>
       <x:c r="AY28" s="12"/>
       <x:c r="AZ28" s="12"/>
-      <x:c r="BA28" s="12" t="n">
+      <x:c r="BA28" s="12"/>
+      <x:c r="BB28" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB28" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC28" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD28" s="12" t="str">
+      <x:c r="BD28" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE28" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE28" s="12" t="str">
+      <x:c r="BF28" s="12" t="str">
         <x:v>Exact Table2 target replaces old estimates; PDP surface/pre-exposure mapping ambiguous;72h belongs to separate cyclic test and not assigned toPDP; roomtemperature not25C; reheating1200C/coiling550C not finalHT; reported_steel_composition</x:v>
       </x:c>
     </x:row>
@@ -4065,19 +4098,20 @@
       <x:c r="AX29" s="12"/>
       <x:c r="AY29" s="12"/>
       <x:c r="AZ29" s="12"/>
-      <x:c r="BA29" s="12" t="n">
+      <x:c r="BA29" s="12"/>
+      <x:c r="BB29" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB29" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC29" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD29" s="12" t="str">
+      <x:c r="BD29" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE29" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE29" s="12" t="str">
+      <x:c r="BF29" s="12" t="str">
         <x:v>Exact Table2 target replaces old estimates; PDP surface/pre-exposure mapping ambiguous;72h belongs to separate cyclic test and not assigned toPDP; roomtemperature not25C; reheating1200C/coiling550C not finalHT; reported_steel_composition</x:v>
       </x:c>
     </x:row>
@@ -4186,19 +4220,20 @@
       <x:c r="AX30" s="12"/>
       <x:c r="AY30" s="12"/>
       <x:c r="AZ30" s="12"/>
-      <x:c r="BA30" s="12" t="n">
+      <x:c r="BA30" s="12"/>
+      <x:c r="BB30" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB30" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC30" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD30" s="12" t="str">
+      <x:c r="BD30" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE30" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V)</x:v>
       </x:c>
-      <x:c r="BE30" s="12" t="str">
+      <x:c r="BF30" s="12" t="str">
         <x:v>Exact Table2 target replaces old estimates; PDP surface/pre-exposure mapping ambiguous;72h belongs to separate cyclic test and not assigned toPDP; roomtemperature not25C; reheating1200C/coiling550C not finalHT; reported_steel_composition</x:v>
       </x:c>
     </x:row>
@@ -4303,19 +4338,20 @@
       <x:c r="AX31" s="12"/>
       <x:c r="AY31" s="12"/>
       <x:c r="AZ31" s="12"/>
-      <x:c r="BA31" s="12" t="n">
+      <x:c r="BA31" s="12"/>
+      <x:c r="BB31" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB31" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC31" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD31" s="12" t="str">
+      <x:c r="BD31" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE31" s="12" t="str">
         <x:v>P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 침지시간(min); 온도(°C); 주사속도(mV/s)</x:v>
       </x:c>
-      <x:c r="BE31" s="12" t="str">
+      <x:c r="BF31" s="12" t="str">
         <x:v>Base slab composition Sec1 PDF p2; residual Ce ICP-AES Sec1 p3. Non-RE chemistry shared from base slab, not individual remelt measurements. P unreported; S only graphical and changes with Ce: left missing. Temperature, scan rate and pre-exposure unreported. 1150C/30min is separate in-situ microscopy, not PDP heat treatment. C2/C4 have no tabulated icorr and are not invented.; documented_base_plus_measured_RE</x:v>
       </x:c>
     </x:row>
@@ -4420,19 +4456,20 @@
       <x:c r="AX32" s="12"/>
       <x:c r="AY32" s="12"/>
       <x:c r="AZ32" s="12"/>
-      <x:c r="BA32" s="12" t="n">
+      <x:c r="BA32" s="12"/>
+      <x:c r="BB32" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB32" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC32" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD32" s="12" t="str">
+      <x:c r="BD32" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE32" s="12" t="str">
         <x:v>P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 침지시간(min); 온도(°C); 주사속도(mV/s)</x:v>
       </x:c>
-      <x:c r="BE32" s="12" t="str">
+      <x:c r="BF32" s="12" t="str">
         <x:v>Base slab composition Sec1 PDF p2; residual Ce ICP-AES Sec1 p3. Non-RE chemistry shared from base slab, not individual remelt measurements. P unreported; S only graphical and changes with Ce: left missing. Temperature, scan rate and pre-exposure unreported. 1150C/30min is separate in-situ microscopy, not PDP heat treatment. C2/C4 have no tabulated icorr and are not invented.; documented_base_plus_measured_RE</x:v>
       </x:c>
     </x:row>
@@ -4537,19 +4574,20 @@
       <x:c r="AX33" s="12"/>
       <x:c r="AY33" s="12"/>
       <x:c r="AZ33" s="12"/>
-      <x:c r="BA33" s="12" t="n">
+      <x:c r="BA33" s="12"/>
+      <x:c r="BB33" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB33" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC33" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD33" s="12" t="str">
+      <x:c r="BD33" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE33" s="12" t="str">
         <x:v>P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 침지시간(min); 온도(°C); 주사속도(mV/s)</x:v>
       </x:c>
-      <x:c r="BE33" s="12" t="str">
+      <x:c r="BF33" s="12" t="str">
         <x:v>Base slab composition Sec1 PDF p2; residual Ce ICP-AES Sec1 p3. Non-RE chemistry shared from base slab, not individual remelt measurements. P unreported; S only graphical and changes with Ce: left missing. Temperature, scan rate and pre-exposure unreported. 1150C/30min is separate in-situ microscopy, not PDP heat treatment. C2/C4 have no tabulated icorr and are not invented.; documented_base_plus_measured_RE</x:v>
       </x:c>
     </x:row>
@@ -4668,19 +4706,20 @@
       <x:c r="AX34" s="12"/>
       <x:c r="AY34" s="12"/>
       <x:c r="AZ34" s="12"/>
-      <x:c r="BA34" s="12" t="n">
+      <x:c r="BA34" s="12"/>
+      <x:c r="BB34" s="12" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="BB34" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC34" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD34" s="12" t="str">
+      <x:c r="BD34" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE34" s="12" t="str">
         <x:v>P; S; Ni; Cu; T.N.(Total Nitrogen); Nb; Ti; Al; Sb; Ce; La; Pr; W; La+Ce_합산; PREN; 전해질 농도(wt%); 침지시간(min)</x:v>
       </x:c>
-      <x:c r="BE34" s="12" t="str">
+      <x:c r="BF34" s="12" t="str">
         <x:v>P/S unreported. Table1 caption nominal; ICP-MS method reported. Separate 20h immersion is not automatically PDP pre-exposure. Molarity not guessed as wt%.</x:v>
       </x:c>
     </x:row>
@@ -4799,19 +4838,20 @@
       <x:c r="AX35" s="12"/>
       <x:c r="AY35" s="12"/>
       <x:c r="AZ35" s="12"/>
-      <x:c r="BA35" s="12" t="n">
+      <x:c r="BA35" s="12"/>
+      <x:c r="BB35" s="12" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="BB35" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC35" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD35" s="12" t="str">
+      <x:c r="BD35" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE35" s="12" t="str">
         <x:v>P; S; Ni; Cu; T.N.(Total Nitrogen); Nb; Ti; Al; Sb; Ce; La; Pr; W; La+Ce_합산; PREN; 전해질 농도(wt%); 침지시간(min)</x:v>
       </x:c>
-      <x:c r="BE35" s="12" t="str">
+      <x:c r="BF35" s="12" t="str">
         <x:v>P/S unreported. Table1 caption nominal; ICP-MS method reported. Separate 20h immersion is not automatically PDP pre-exposure. Molarity not guessed as wt%.</x:v>
       </x:c>
     </x:row>
@@ -4930,19 +4970,20 @@
       <x:c r="AX36" s="12"/>
       <x:c r="AY36" s="12"/>
       <x:c r="AZ36" s="12"/>
-      <x:c r="BA36" s="12" t="n">
+      <x:c r="BA36" s="12"/>
+      <x:c r="BB36" s="12" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="BB36" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC36" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD36" s="12" t="str">
+      <x:c r="BD36" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE36" s="12" t="str">
         <x:v>P; S; Ni; Cu; T.N.(Total Nitrogen); Nb; Ti; Al; Sb; Ce; La; Pr; W; La+Ce_합산; PREN; 전해질 농도(wt%); 침지시간(min)</x:v>
       </x:c>
-      <x:c r="BE36" s="12" t="str">
+      <x:c r="BF36" s="12" t="str">
         <x:v>P/S unreported. Table1 caption nominal; ICP-MS method reported. Separate 20h immersion is not automatically PDP pre-exposure. Molarity not guessed as wt%.</x:v>
       </x:c>
     </x:row>
@@ -5061,19 +5102,20 @@
       <x:c r="AX37" s="12"/>
       <x:c r="AY37" s="12"/>
       <x:c r="AZ37" s="12"/>
-      <x:c r="BA37" s="12" t="n">
+      <x:c r="BA37" s="12"/>
+      <x:c r="BB37" s="12" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="BB37" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC37" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD37" s="12" t="str">
+      <x:c r="BD37" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE37" s="12" t="str">
         <x:v>P; S; Ni; Cu; T.N.(Total Nitrogen); Nb; Ti; Al; Sb; Ce; La; Pr; W; La+Ce_합산; PREN; 전해질 농도(wt%); 침지시간(min)</x:v>
       </x:c>
-      <x:c r="BE37" s="12" t="str">
+      <x:c r="BF37" s="12" t="str">
         <x:v>P/S unreported. Table1 caption nominal; ICP-MS method reported. Separate 20h immersion is not automatically PDP pre-exposure. Molarity not guessed as wt%.</x:v>
       </x:c>
     </x:row>
@@ -5202,19 +5244,20 @@
       </x:c>
       <x:c r="AY38" s="12"/>
       <x:c r="AZ38" s="12"/>
-      <x:c r="BA38" s="12" t="n">
+      <x:c r="BA38" s="12"/>
+      <x:c r="BB38" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB38" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC38" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD38" s="12" t="str">
+      <x:c r="BD38" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE38" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; 전해질 농도(wt%); 주사속도(mV/s)</x:v>
       </x:c>
-      <x:c r="BE38" s="12" t="str">
+      <x:c r="BF38" s="12" t="str">
         <x:v>AF=30min explicitly pre-PDP stabilization; prior cathodic depassivation5min separate. Scan rate unreported. B also changes; not causal Ce comparison. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -5343,19 +5386,20 @@
       </x:c>
       <x:c r="AY39" s="12"/>
       <x:c r="AZ39" s="12"/>
-      <x:c r="BA39" s="12" t="n">
+      <x:c r="BA39" s="12"/>
+      <x:c r="BB39" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB39" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC39" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD39" s="12" t="str">
+      <x:c r="BD39" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE39" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; 전해질 농도(wt%); 주사속도(mV/s)</x:v>
       </x:c>
-      <x:c r="BE39" s="12" t="str">
+      <x:c r="BF39" s="12" t="str">
         <x:v>AF=30min explicitly pre-PDP stabilization; prior cathodic depassivation5min separate. Scan rate unreported. B also changes; not causal Ce comparison. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -5484,19 +5528,20 @@
       </x:c>
       <x:c r="AY40" s="12"/>
       <x:c r="AZ40" s="12"/>
-      <x:c r="BA40" s="12" t="n">
+      <x:c r="BA40" s="12"/>
+      <x:c r="BB40" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB40" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC40" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD40" s="12" t="str">
+      <x:c r="BD40" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE40" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; 전해질 농도(wt%); 주사속도(mV/s)</x:v>
       </x:c>
-      <x:c r="BE40" s="12" t="str">
+      <x:c r="BF40" s="12" t="str">
         <x:v>AF=30min explicitly pre-PDP stabilization; prior cathodic depassivation5min separate. Scan rate unreported. B also changes; not causal Ce comparison. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -5625,19 +5670,20 @@
       </x:c>
       <x:c r="AY41" s="12"/>
       <x:c r="AZ41" s="12"/>
-      <x:c r="BA41" s="12" t="n">
+      <x:c r="BA41" s="12"/>
+      <x:c r="BB41" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB41" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC41" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD41" s="12" t="str">
+      <x:c r="BD41" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE41" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; 전해질 농도(wt%); 주사속도(mV/s)</x:v>
       </x:c>
-      <x:c r="BE41" s="12" t="str">
+      <x:c r="BF41" s="12" t="str">
         <x:v>AF=30min explicitly pre-PDP stabilization; prior cathodic depassivation5min separate. Scan rate unreported. B also changes; not causal Ce comparison. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -5760,19 +5806,20 @@
       <x:c r="AX42" s="12"/>
       <x:c r="AY42" s="12"/>
       <x:c r="AZ42" s="12"/>
-      <x:c r="BA42" s="12" t="n">
+      <x:c r="BA42" s="12"/>
+      <x:c r="BB42" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB42" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC42" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD42" s="12" t="str">
+      <x:c r="BD42" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE42" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE42" s="12" t="str">
+      <x:c r="BF42" s="12" t="str">
         <x:v>Do not infer missing minus sign from graph or bibliography. AL intentionally unavailable until correction verified. Different aging states are separate conditions. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -5895,19 +5942,20 @@
       <x:c r="AX43" s="12"/>
       <x:c r="AY43" s="12"/>
       <x:c r="AZ43" s="12"/>
-      <x:c r="BA43" s="12" t="n">
+      <x:c r="BA43" s="12"/>
+      <x:c r="BB43" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB43" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC43" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD43" s="12" t="str">
+      <x:c r="BD43" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE43" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE43" s="12" t="str">
+      <x:c r="BF43" s="12" t="str">
         <x:v>Do not infer missing minus sign from graph or bibliography. AL intentionally unavailable until correction verified. Different aging states are separate conditions. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -6030,19 +6078,20 @@
       <x:c r="AX44" s="12"/>
       <x:c r="AY44" s="12"/>
       <x:c r="AZ44" s="12"/>
-      <x:c r="BA44" s="12" t="n">
+      <x:c r="BA44" s="12"/>
+      <x:c r="BB44" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB44" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC44" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD44" s="12" t="str">
+      <x:c r="BD44" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE44" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE44" s="12" t="str">
+      <x:c r="BF44" s="12" t="str">
         <x:v>Do not infer missing minus sign from graph or bibliography. AL intentionally unavailable until correction verified. Different aging states are separate conditions. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -6165,19 +6214,20 @@
       <x:c r="AX45" s="12"/>
       <x:c r="AY45" s="12"/>
       <x:c r="AZ45" s="12"/>
-      <x:c r="BA45" s="12" t="n">
+      <x:c r="BA45" s="12"/>
+      <x:c r="BB45" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB45" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC45" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD45" s="12" t="str">
+      <x:c r="BD45" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE45" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE45" s="12" t="str">
+      <x:c r="BF45" s="12" t="str">
         <x:v>Do not infer missing minus sign from graph or bibliography. AL intentionally unavailable until correction verified. Different aging states are separate conditions. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -6300,19 +6350,20 @@
       <x:c r="AX46" s="12"/>
       <x:c r="AY46" s="12"/>
       <x:c r="AZ46" s="12"/>
-      <x:c r="BA46" s="12" t="n">
+      <x:c r="BA46" s="12"/>
+      <x:c r="BB46" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB46" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC46" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD46" s="12" t="str">
+      <x:c r="BD46" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE46" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE46" s="12" t="str">
+      <x:c r="BF46" s="12" t="str">
         <x:v>Do not infer missing minus sign from graph or bibliography. AL intentionally unavailable until correction verified. Different aging states are separate conditions. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -6435,19 +6486,20 @@
       <x:c r="AX47" s="12"/>
       <x:c r="AY47" s="12"/>
       <x:c r="AZ47" s="12"/>
-      <x:c r="BA47" s="12" t="n">
+      <x:c r="BA47" s="12"/>
+      <x:c r="BB47" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB47" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC47" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD47" s="12" t="str">
+      <x:c r="BD47" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE47" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE47" s="12" t="str">
+      <x:c r="BF47" s="12" t="str">
         <x:v>Do not infer missing minus sign from graph or bibliography. AL intentionally unavailable until correction verified. Different aging states are separate conditions. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -6570,19 +6622,20 @@
       <x:c r="AX48" s="12"/>
       <x:c r="AY48" s="12"/>
       <x:c r="AZ48" s="12"/>
-      <x:c r="BA48" s="12" t="n">
+      <x:c r="BA48" s="12"/>
+      <x:c r="BB48" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="BB48" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC48" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD48" s="12" t="str">
+      <x:c r="BD48" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE48" s="12" t="str">
         <x:v>Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE48" s="12" t="str">
+      <x:c r="BF48" s="12" t="str">
         <x:v>Do not infer missing minus sign from graph or bibliography. AL intentionally unavailable until correction verified. Different aging states are separate conditions. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -6689,19 +6742,20 @@
       <x:c r="AX49" s="12"/>
       <x:c r="AY49" s="12"/>
       <x:c r="AZ49" s="12"/>
-      <x:c r="BA49" s="12" t="n">
+      <x:c r="BA49" s="12"/>
+      <x:c r="BB49" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB49" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC49" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD49" s="12" t="str">
+      <x:c r="BD49" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE49" s="12" t="str">
         <x:v>P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%)</x:v>
       </x:c>
-      <x:c r="BE49" s="12" t="str">
+      <x:c r="BF49" s="12" t="str">
         <x:v>P/S unreported; Y2O3 powder addition is not measured elemental Y. Nominal ODS recipe and measured OES chemistry differ. Comparator is different material. AF explicit 2h OCP soaking.</x:v>
       </x:c>
     </x:row>
@@ -6808,19 +6862,20 @@
       <x:c r="AX50" s="12"/>
       <x:c r="AY50" s="12"/>
       <x:c r="AZ50" s="12"/>
-      <x:c r="BA50" s="12" t="n">
+      <x:c r="BA50" s="12"/>
+      <x:c r="BB50" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB50" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC50" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD50" s="12" t="str">
+      <x:c r="BD50" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE50" s="12" t="str">
         <x:v>P; S; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%)</x:v>
       </x:c>
-      <x:c r="BE50" s="12" t="str">
+      <x:c r="BF50" s="12" t="str">
         <x:v>P/S unreported; Y2O3 powder addition is not measured elemental Y. Nominal ODS recipe and measured OES chemistry differ. Comparator is different material. AF explicit 2h OCP soaking.</x:v>
       </x:c>
     </x:row>
@@ -6927,19 +6982,20 @@
       <x:c r="AX51" s="12"/>
       <x:c r="AY51" s="12"/>
       <x:c r="AZ51" s="12"/>
-      <x:c r="BA51" s="12" t="n">
+      <x:c r="BA51" s="12"/>
+      <x:c r="BB51" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB51" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC51" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD51" s="12" t="str">
+      <x:c r="BD51" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE51" s="12" t="str">
         <x:v>P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%)</x:v>
       </x:c>
-      <x:c r="BE51" s="12" t="str">
+      <x:c r="BF51" s="12" t="str">
         <x:v>P/S unreported; Y2O3 powder addition is not measured elemental Y. Nominal ODS recipe and measured OES chemistry differ. Comparator is different material. AF explicit 2h OCP soaking.</x:v>
       </x:c>
     </x:row>
@@ -7046,19 +7102,20 @@
       <x:c r="AX52" s="12"/>
       <x:c r="AY52" s="12"/>
       <x:c r="AZ52" s="12"/>
-      <x:c r="BA52" s="12" t="n">
+      <x:c r="BA52" s="12"/>
+      <x:c r="BB52" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB52" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC52" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD52" s="12" t="str">
+      <x:c r="BD52" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE52" s="12" t="str">
         <x:v>P; S; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%)</x:v>
       </x:c>
-      <x:c r="BE52" s="12" t="str">
+      <x:c r="BF52" s="12" t="str">
         <x:v>P/S unreported; Y2O3 powder addition is not measured elemental Y. Nominal ODS recipe and measured OES chemistry differ. Comparator is different material. AF explicit 2h OCP soaking.</x:v>
       </x:c>
     </x:row>
@@ -7165,19 +7222,20 @@
       <x:c r="AX53" s="12"/>
       <x:c r="AY53" s="12"/>
       <x:c r="AZ53" s="12"/>
-      <x:c r="BA53" s="12" t="n">
+      <x:c r="BA53" s="12"/>
+      <x:c r="BB53" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB53" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC53" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD53" s="12" t="str">
+      <x:c r="BD53" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE53" s="12" t="str">
         <x:v>P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%)</x:v>
       </x:c>
-      <x:c r="BE53" s="12" t="str">
+      <x:c r="BF53" s="12" t="str">
         <x:v>P/S unreported; Y2O3 powder addition is not measured elemental Y. Nominal ODS recipe and measured OES chemistry differ. Comparator is different material. AF explicit 2h OCP soaking.</x:v>
       </x:c>
     </x:row>
@@ -7284,19 +7342,20 @@
       <x:c r="AX54" s="12"/>
       <x:c r="AY54" s="12"/>
       <x:c r="AZ54" s="12"/>
-      <x:c r="BA54" s="12" t="n">
+      <x:c r="BA54" s="12"/>
+      <x:c r="BB54" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB54" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC54" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD54" s="12" t="str">
+      <x:c r="BD54" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE54" s="12" t="str">
         <x:v>P; S; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%)</x:v>
       </x:c>
-      <x:c r="BE54" s="12" t="str">
+      <x:c r="BF54" s="12" t="str">
         <x:v>P/S unreported; Y2O3 powder addition is not measured elemental Y. Nominal ODS recipe and measured OES chemistry differ. Comparator is different material. AF explicit 2h OCP soaking.</x:v>
       </x:c>
     </x:row>
@@ -7413,19 +7472,20 @@
       <x:c r="AX55" s="12"/>
       <x:c r="AY55" s="12"/>
       <x:c r="AZ55" s="12"/>
-      <x:c r="BA55" s="12" t="n">
+      <x:c r="BA55" s="12"/>
+      <x:c r="BB55" s="12" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="BB55" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC55" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD55" s="12" t="str">
+      <x:c r="BD55" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE55" s="12" t="str">
         <x:v>Nb; V; Ti; Sb; Ce; La; Pr; W; La+Ce_합산; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE55" s="12" t="str">
+      <x:c r="BF55" s="12" t="str">
         <x:v>298K converted to24.85C. Shared starting-steel composition and nominal experimental Y levels, not individual residual measurements. Table2 has no icorr; do not import workbook AL. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -7542,19 +7602,20 @@
       <x:c r="AX56" s="12"/>
       <x:c r="AY56" s="12"/>
       <x:c r="AZ56" s="12"/>
-      <x:c r="BA56" s="12" t="n">
+      <x:c r="BA56" s="12"/>
+      <x:c r="BB56" s="12" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="BB56" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC56" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD56" s="12" t="str">
+      <x:c r="BD56" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE56" s="12" t="str">
         <x:v>Nb; V; Ti; Sb; Ce; La; Pr; W; La+Ce_합산; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE56" s="12" t="str">
+      <x:c r="BF56" s="12" t="str">
         <x:v>298K converted to24.85C. Shared starting-steel composition and nominal experimental Y levels, not individual residual measurements. Table2 has no icorr; do not import workbook AL. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -7671,19 +7732,20 @@
       <x:c r="AX57" s="12"/>
       <x:c r="AY57" s="12"/>
       <x:c r="AZ57" s="12"/>
-      <x:c r="BA57" s="12" t="n">
+      <x:c r="BA57" s="12"/>
+      <x:c r="BB57" s="12" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="BB57" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC57" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD57" s="12" t="str">
+      <x:c r="BD57" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE57" s="12" t="str">
         <x:v>Nb; V; Ti; Sb; Ce; La; Pr; W; La+Ce_합산; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE57" s="12" t="str">
+      <x:c r="BF57" s="12" t="str">
         <x:v>298K converted to24.85C. Shared starting-steel composition and nominal experimental Y levels, not individual residual measurements. Table2 has no icorr; do not import workbook AL. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -7800,19 +7862,20 @@
       <x:c r="AX58" s="12"/>
       <x:c r="AY58" s="12"/>
       <x:c r="AZ58" s="12"/>
-      <x:c r="BA58" s="12" t="n">
+      <x:c r="BA58" s="12"/>
+      <x:c r="BB58" s="12" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="BB58" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC58" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD58" s="12" t="str">
+      <x:c r="BD58" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE58" s="12" t="str">
         <x:v>Nb; V; Ti; Sb; Ce; La; Pr; W; La+Ce_합산; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE58" s="12" t="str">
+      <x:c r="BF58" s="12" t="str">
         <x:v>298K converted to24.85C. Shared starting-steel composition and nominal experimental Y levels, not individual residual measurements. Table2 has no icorr; do not import workbook AL. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -7929,19 +7992,20 @@
       <x:c r="AX59" s="12"/>
       <x:c r="AY59" s="12"/>
       <x:c r="AZ59" s="12"/>
-      <x:c r="BA59" s="12" t="n">
+      <x:c r="BA59" s="12"/>
+      <x:c r="BB59" s="12" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="BB59" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC59" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD59" s="12" t="str">
+      <x:c r="BD59" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE59" s="12" t="str">
         <x:v>Nb; V; Ti; Sb; Ce; La; Pr; W; La+Ce_합산; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE59" s="12" t="str">
+      <x:c r="BF59" s="12" t="str">
         <x:v>298K converted to24.85C. Shared starting-steel composition and nominal experimental Y levels, not individual residual measurements. Table2 has no icorr; do not import workbook AL. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -8038,19 +8102,20 @@
       <x:c r="AX60" s="12"/>
       <x:c r="AY60" s="12"/>
       <x:c r="AZ60" s="12"/>
-      <x:c r="BA60" s="12" t="n">
+      <x:c r="BA60" s="12"/>
+      <x:c r="BB60" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB60" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC60" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD60" s="12" t="str">
+      <x:c r="BD60" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE60" s="12" t="str">
         <x:v>Cr; Mo; Nb; V; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE60" s="12" t="str">
+      <x:c r="BF60" s="12" t="str">
         <x:v>Table5 reports pitting potential and KI, not icorr. Dash Ce not converted to zero.</x:v>
       </x:c>
     </x:row>
@@ -8147,19 +8212,20 @@
       <x:c r="AX61" s="12"/>
       <x:c r="AY61" s="12"/>
       <x:c r="AZ61" s="12"/>
-      <x:c r="BA61" s="12" t="n">
+      <x:c r="BA61" s="12"/>
+      <x:c r="BB61" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB61" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC61" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD61" s="12" t="str">
+      <x:c r="BD61" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE61" s="12" t="str">
         <x:v>Cr; Mo; Nb; V; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE61" s="12" t="str">
+      <x:c r="BF61" s="12" t="str">
         <x:v>Table5 reports pitting potential and KI, not icorr. Dash Ce not converted to zero.</x:v>
       </x:c>
     </x:row>
@@ -8258,19 +8324,20 @@
       <x:c r="AX62" s="12"/>
       <x:c r="AY62" s="12"/>
       <x:c r="AZ62" s="12"/>
-      <x:c r="BA62" s="12" t="n">
+      <x:c r="BA62" s="12"/>
+      <x:c r="BB62" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB62" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC62" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD62" s="12" t="str">
+      <x:c r="BD62" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE62" s="12" t="str">
         <x:v>Cr; Mo; Nb; V; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE62" s="12" t="str">
+      <x:c r="BF62" s="12" t="str">
         <x:v>Table5 reports pitting potential and KI, not icorr. Dash Ce not converted to zero.</x:v>
       </x:c>
     </x:row>
@@ -8369,19 +8436,20 @@
       <x:c r="AX63" s="12"/>
       <x:c r="AY63" s="12"/>
       <x:c r="AZ63" s="12"/>
-      <x:c r="BA63" s="12" t="n">
+      <x:c r="BA63" s="12"/>
+      <x:c r="BB63" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB63" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC63" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD63" s="12" t="str">
+      <x:c r="BD63" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE63" s="12" t="str">
         <x:v>Cr; Mo; Nb; V; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE63" s="12" t="str">
+      <x:c r="BF63" s="12" t="str">
         <x:v>Table5 reports pitting potential and KI, not icorr. Dash Ce not converted to zero.</x:v>
       </x:c>
     </x:row>
@@ -8476,19 +8544,20 @@
       <x:c r="AX64" s="12"/>
       <x:c r="AY64" s="12"/>
       <x:c r="AZ64" s="12"/>
-      <x:c r="BA64" s="12" t="n">
+      <x:c r="BA64" s="12"/>
+      <x:c r="BB64" s="12" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="BB64" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC64" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD64" s="12" t="str">
+      <x:c r="BD64" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE64" s="12" t="str">
         <x:v>Cr; Mo; T.N.(Total Nitrogen); Nb; V; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE64" s="12" t="str">
+      <x:c r="BF64" s="12" t="str">
         <x:v>Standard-grade0# is bounds/ranges and excluded. No numerical icorr table recovered.</x:v>
       </x:c>
     </x:row>
@@ -8583,19 +8652,20 @@
       <x:c r="AX65" s="12"/>
       <x:c r="AY65" s="12"/>
       <x:c r="AZ65" s="12"/>
-      <x:c r="BA65" s="12" t="n">
+      <x:c r="BA65" s="12"/>
+      <x:c r="BB65" s="12" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="BB65" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC65" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD65" s="12" t="str">
+      <x:c r="BD65" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE65" s="12" t="str">
         <x:v>Cr; Mo; T.N.(Total Nitrogen); Nb; V; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE65" s="12" t="str">
+      <x:c r="BF65" s="12" t="str">
         <x:v>Standard-grade0# is bounds/ranges and excluded. No numerical icorr table recovered.</x:v>
       </x:c>
     </x:row>
@@ -8690,19 +8760,20 @@
       <x:c r="AX66" s="12"/>
       <x:c r="AY66" s="12"/>
       <x:c r="AZ66" s="12"/>
-      <x:c r="BA66" s="12" t="n">
+      <x:c r="BA66" s="12"/>
+      <x:c r="BB66" s="12" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="BB66" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC66" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD66" s="12" t="str">
+      <x:c r="BD66" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE66" s="12" t="str">
         <x:v>Cr; Mo; T.N.(Total Nitrogen); Nb; V; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE66" s="12" t="str">
+      <x:c r="BF66" s="12" t="str">
         <x:v>Standard-grade0# is bounds/ranges and excluded. No numerical icorr table recovered.</x:v>
       </x:c>
     </x:row>
@@ -8801,19 +8872,20 @@
       <x:c r="AX67" s="12"/>
       <x:c r="AY67" s="12"/>
       <x:c r="AZ67" s="12"/>
-      <x:c r="BA67" s="12" t="n">
+      <x:c r="BA67" s="12"/>
+      <x:c r="BB67" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB67" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC67" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD67" s="12" t="str">
+      <x:c r="BD67" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE67" s="12" t="str">
         <x:v>Mo; Cu; T.N.(Total Nitrogen); Nb; V; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE67" s="12" t="str">
+      <x:c r="BF67" s="12" t="str">
         <x:v>Composition is surfaced-metal common chemistry. Table2 is mass-loss corrosion rate and hydrogen-evolution Tafel constants, not icorr. Coating1%Y is not bulk Y.</x:v>
       </x:c>
     </x:row>
@@ -8914,19 +8986,20 @@
       <x:c r="AX68" s="12"/>
       <x:c r="AY68" s="12"/>
       <x:c r="AZ68" s="12"/>
-      <x:c r="BA68" s="12" t="n">
+      <x:c r="BA68" s="12"/>
+      <x:c r="BB68" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB68" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC68" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD68" s="12" t="str">
+      <x:c r="BD68" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE68" s="12" t="str">
         <x:v>Mo; Cu; T.N.(Total Nitrogen); Nb; V; Al; Sb; Ce; La; Pr; W; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE68" s="12" t="str">
+      <x:c r="BF68" s="12" t="str">
         <x:v>Composition is surfaced-metal common chemistry. Table2 is mass-loss corrosion rate and hydrogen-evolution Tafel constants, not icorr. Coating1%Y is not bulk Y.</x:v>
       </x:c>
     </x:row>
@@ -9027,19 +9100,20 @@
       <x:c r="AX69" s="12"/>
       <x:c r="AY69" s="12"/>
       <x:c r="AZ69" s="12"/>
-      <x:c r="BA69" s="12" t="n">
+      <x:c r="BA69" s="12"/>
+      <x:c r="BB69" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB69" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC69" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD69" s="12" t="str">
+      <x:c r="BD69" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE69" s="12" t="str">
         <x:v>Mo; Cu; T.N.(Total Nitrogen); Nb; V; Al; Sb; Ce; La; Pr; W; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE69" s="12" t="str">
+      <x:c r="BF69" s="12" t="str">
         <x:v>Composition is surfaced-metal common chemistry. Table2 is mass-loss corrosion rate and hydrogen-evolution Tafel constants, not icorr. Coating1%Y is not bulk Y.</x:v>
       </x:c>
     </x:row>
@@ -9136,19 +9210,20 @@
       <x:c r="AX70" s="12"/>
       <x:c r="AY70" s="12"/>
       <x:c r="AZ70" s="12"/>
-      <x:c r="BA70" s="12" t="n">
+      <x:c r="BA70" s="12"/>
+      <x:c r="BB70" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB70" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC70" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD70" s="12" t="str">
+      <x:c r="BD70" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE70" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE70" s="12" t="str">
+      <x:c r="BF70" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -9245,19 +9320,20 @@
       <x:c r="AX71" s="12"/>
       <x:c r="AY71" s="12"/>
       <x:c r="AZ71" s="12"/>
-      <x:c r="BA71" s="12" t="n">
+      <x:c r="BA71" s="12"/>
+      <x:c r="BB71" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB71" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC71" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD71" s="12" t="str">
+      <x:c r="BD71" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE71" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE71" s="12" t="str">
+      <x:c r="BF71" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -9354,19 +9430,20 @@
       <x:c r="AX72" s="12"/>
       <x:c r="AY72" s="12"/>
       <x:c r="AZ72" s="12"/>
-      <x:c r="BA72" s="12" t="n">
+      <x:c r="BA72" s="12"/>
+      <x:c r="BB72" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB72" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC72" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD72" s="12" t="str">
+      <x:c r="BD72" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE72" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE72" s="12" t="str">
+      <x:c r="BF72" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -9463,19 +9540,20 @@
       <x:c r="AX73" s="12"/>
       <x:c r="AY73" s="12"/>
       <x:c r="AZ73" s="12"/>
-      <x:c r="BA73" s="12" t="n">
+      <x:c r="BA73" s="12"/>
+      <x:c r="BB73" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB73" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC73" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD73" s="12" t="str">
+      <x:c r="BD73" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE73" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE73" s="12" t="str">
+      <x:c r="BF73" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -9574,19 +9652,20 @@
       <x:c r="AX74" s="12"/>
       <x:c r="AY74" s="12"/>
       <x:c r="AZ74" s="12"/>
-      <x:c r="BA74" s="12" t="n">
+      <x:c r="BA74" s="12"/>
+      <x:c r="BB74" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB74" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC74" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD74" s="12" t="str">
+      <x:c r="BD74" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE74" s="12" t="str">
         <x:v>Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE74" s="12" t="str">
+      <x:c r="BF74" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -9685,19 +9764,20 @@
       <x:c r="AX75" s="12"/>
       <x:c r="AY75" s="12"/>
       <x:c r="AZ75" s="12"/>
-      <x:c r="BA75" s="12" t="n">
+      <x:c r="BA75" s="12"/>
+      <x:c r="BB75" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB75" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC75" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD75" s="12" t="str">
+      <x:c r="BD75" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE75" s="12" t="str">
         <x:v>Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE75" s="12" t="str">
+      <x:c r="BF75" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -9796,19 +9876,20 @@
       <x:c r="AX76" s="12"/>
       <x:c r="AY76" s="12"/>
       <x:c r="AZ76" s="12"/>
-      <x:c r="BA76" s="12" t="n">
+      <x:c r="BA76" s="12"/>
+      <x:c r="BB76" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB76" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC76" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD76" s="12" t="str">
+      <x:c r="BD76" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE76" s="12" t="str">
         <x:v>Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE76" s="12" t="str">
+      <x:c r="BF76" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -9907,19 +9988,20 @@
       <x:c r="AX77" s="12"/>
       <x:c r="AY77" s="12"/>
       <x:c r="AZ77" s="12"/>
-      <x:c r="BA77" s="12" t="n">
+      <x:c r="BA77" s="12"/>
+      <x:c r="BB77" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB77" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC77" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD77" s="12" t="str">
+      <x:c r="BD77" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE77" s="12" t="str">
         <x:v>Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE77" s="12" t="str">
+      <x:c r="BF77" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -10020,19 +10102,20 @@
       <x:c r="AX78" s="12"/>
       <x:c r="AY78" s="12"/>
       <x:c r="AZ78" s="12"/>
-      <x:c r="BA78" s="12" t="n">
+      <x:c r="BA78" s="12"/>
+      <x:c r="BB78" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB78" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC78" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD78" s="12" t="str">
+      <x:c r="BD78" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE78" s="12" t="str">
         <x:v>Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE78" s="12" t="str">
+      <x:c r="BF78" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -10133,19 +10216,20 @@
       <x:c r="AX79" s="12"/>
       <x:c r="AY79" s="12"/>
       <x:c r="AZ79" s="12"/>
-      <x:c r="BA79" s="12" t="n">
+      <x:c r="BA79" s="12"/>
+      <x:c r="BB79" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB79" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC79" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD79" s="12" t="str">
+      <x:c r="BD79" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE79" s="12" t="str">
         <x:v>Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE79" s="12" t="str">
+      <x:c r="BF79" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -10246,19 +10330,20 @@
       <x:c r="AX80" s="12"/>
       <x:c r="AY80" s="12"/>
       <x:c r="AZ80" s="12"/>
-      <x:c r="BA80" s="12" t="n">
+      <x:c r="BA80" s="12"/>
+      <x:c r="BB80" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB80" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC80" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD80" s="12" t="str">
+      <x:c r="BD80" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE80" s="12" t="str">
         <x:v>Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE80" s="12" t="str">
+      <x:c r="BF80" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -10359,19 +10444,20 @@
       <x:c r="AX81" s="12"/>
       <x:c r="AY81" s="12"/>
       <x:c r="AZ81" s="12"/>
-      <x:c r="BA81" s="12" t="n">
+      <x:c r="BA81" s="12"/>
+      <x:c r="BB81" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="BB81" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC81" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD81" s="12" t="str">
+      <x:c r="BD81" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE81" s="12" t="str">
         <x:v>Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE81" s="12" t="str">
+      <x:c r="BF81" s="12" t="str">
         <x:v>Table1 Ipass is passive current, not corrosion current. P/S retained as printed (S0.06/0.08wt%). TotalCeLa only; no invented individual fractions.</x:v>
       </x:c>
     </x:row>
@@ -10458,19 +10544,20 @@
       <x:c r="AX82" s="12"/>
       <x:c r="AY82" s="12"/>
       <x:c r="AZ82" s="12"/>
-      <x:c r="BA82" s="12" t="n">
+      <x:c r="BA82" s="12"/>
+      <x:c r="BB82" s="12" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="BB82" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC82" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD82" s="12" t="str">
+      <x:c r="BD82" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE82" s="12" t="str">
         <x:v>P; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE82" s="12" t="str">
+      <x:c r="BF82" s="12" t="str">
         <x:v>P unreported. No tabulated electrochemical icorr; avoid treating thermodynamic coefficients as composition. Dash La not zero.</x:v>
       </x:c>
     </x:row>
@@ -10559,19 +10646,20 @@
       <x:c r="AX83" s="12"/>
       <x:c r="AY83" s="12"/>
       <x:c r="AZ83" s="12"/>
-      <x:c r="BA83" s="12" t="n">
+      <x:c r="BA83" s="12"/>
+      <x:c r="BB83" s="12" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="BB83" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC83" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD83" s="12" t="str">
+      <x:c r="BD83" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE83" s="12" t="str">
         <x:v>P; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE83" s="12" t="str">
+      <x:c r="BF83" s="12" t="str">
         <x:v>P unreported. No tabulated electrochemical icorr; avoid treating thermodynamic coefficients as composition. Dash La not zero.</x:v>
       </x:c>
     </x:row>
@@ -10660,19 +10748,20 @@
       <x:c r="AX84" s="12"/>
       <x:c r="AY84" s="12"/>
       <x:c r="AZ84" s="12"/>
-      <x:c r="BA84" s="12" t="n">
+      <x:c r="BA84" s="12"/>
+      <x:c r="BB84" s="12" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="BB84" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC84" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD84" s="12" t="str">
+      <x:c r="BD84" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE84" s="12" t="str">
         <x:v>P; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE84" s="12" t="str">
+      <x:c r="BF84" s="12" t="str">
         <x:v>P unreported. No tabulated electrochemical icorr; avoid treating thermodynamic coefficients as composition. Dash La not zero.</x:v>
       </x:c>
     </x:row>
@@ -10761,19 +10850,20 @@
       <x:c r="AX85" s="12"/>
       <x:c r="AY85" s="12"/>
       <x:c r="AZ85" s="12"/>
-      <x:c r="BA85" s="12" t="n">
+      <x:c r="BA85" s="12"/>
+      <x:c r="BB85" s="12" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="BB85" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC85" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD85" s="12" t="str">
+      <x:c r="BD85" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE85" s="12" t="str">
         <x:v>P; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE85" s="12" t="str">
+      <x:c r="BF85" s="12" t="str">
         <x:v>P unreported. No tabulated electrochemical icorr; avoid treating thermodynamic coefficients as composition. Dash La not zero.</x:v>
       </x:c>
     </x:row>
@@ -10868,19 +10958,20 @@
       <x:c r="AX86" s="12"/>
       <x:c r="AY86" s="12"/>
       <x:c r="AZ86" s="12"/>
-      <x:c r="BA86" s="12" t="n">
+      <x:c r="BA86" s="12"/>
+      <x:c r="BB86" s="12" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="BB86" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC86" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD86" s="12" t="str">
+      <x:c r="BD86" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE86" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE86" s="12" t="str">
+      <x:c r="BF86" s="12" t="str">
         <x:v>Base chemistry shared plus nominal additions. Table1 reports EIS values, not icorr. Room temperature not assigned25C; 50min stabilization is explicitly pre-EIS, not pre-PDP.</x:v>
       </x:c>
     </x:row>
@@ -10977,19 +11068,20 @@
       <x:c r="AX87" s="12"/>
       <x:c r="AY87" s="12"/>
       <x:c r="AZ87" s="12"/>
-      <x:c r="BA87" s="12" t="n">
+      <x:c r="BA87" s="12"/>
+      <x:c r="BB87" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB87" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC87" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD87" s="12" t="str">
+      <x:c r="BD87" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE87" s="12" t="str">
         <x:v>Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE87" s="12" t="str">
+      <x:c r="BF87" s="12" t="str">
         <x:v>Base chemistry shared plus nominal additions. Table1 reports EIS values, not icorr. Room temperature not assigned25C; 50min stabilization is explicitly pre-EIS, not pre-PDP.</x:v>
       </x:c>
     </x:row>
@@ -11088,19 +11180,20 @@
       <x:c r="AX88" s="12"/>
       <x:c r="AY88" s="12"/>
       <x:c r="AZ88" s="12"/>
-      <x:c r="BA88" s="12" t="n">
+      <x:c r="BA88" s="12"/>
+      <x:c r="BB88" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB88" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC88" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD88" s="12" t="str">
+      <x:c r="BD88" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE88" s="12" t="str">
         <x:v>Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE88" s="12" t="str">
+      <x:c r="BF88" s="12" t="str">
         <x:v>Base chemistry shared plus nominal additions. Table1 reports EIS values, not icorr. Room temperature not assigned25C; 50min stabilization is explicitly pre-EIS, not pre-PDP.</x:v>
       </x:c>
     </x:row>
@@ -11217,19 +11310,20 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AZ89" s="12"/>
-      <x:c r="BA89" s="12" t="n">
+      <x:c r="BA89" s="12"/>
+      <x:c r="BB89" s="12" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="BB89" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC89" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD89" s="12" t="str">
+      <x:c r="BD89" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE89" s="12" t="str">
         <x:v>Si; S; Cu; Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE89" s="12" t="str">
+      <x:c r="BF89" s="12" t="str">
         <x:v>Surface chromizing domain. Y2O3 is pack addition, not measured steelY. Table1 has TWO S headings with .75/.015 and Cr8/Ni11 inconsistent with grade; Si/S left unavailable, other printed values retained. Substrate chemistry not layer chemistry. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -11346,19 +11440,20 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AZ90" s="12"/>
-      <x:c r="BA90" s="12" t="n">
+      <x:c r="BA90" s="12"/>
+      <x:c r="BB90" s="12" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="BB90" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC90" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD90" s="12" t="str">
+      <x:c r="BD90" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE90" s="12" t="str">
         <x:v>Si; S; Cu; Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE90" s="12" t="str">
+      <x:c r="BF90" s="12" t="str">
         <x:v>Surface chromizing domain. Y2O3 is pack addition, not measured steelY. Table1 has TWO S headings with .75/.015 and Cr8/Ni11 inconsistent with grade; Si/S left unavailable, other printed values retained. Substrate chemistry not layer chemistry. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -11475,19 +11570,20 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AZ91" s="12"/>
-      <x:c r="BA91" s="12" t="n">
+      <x:c r="BA91" s="12"/>
+      <x:c r="BB91" s="12" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="BB91" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC91" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD91" s="12" t="str">
+      <x:c r="BD91" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE91" s="12" t="str">
         <x:v>Si; S; Cu; Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE91" s="12" t="str">
+      <x:c r="BF91" s="12" t="str">
         <x:v>Surface chromizing domain. Y2O3 is pack addition, not measured steelY. Table1 has TWO S headings with .75/.015 and Cr8/Ni11 inconsistent with grade; Si/S left unavailable, other printed values retained. Substrate chemistry not layer chemistry. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -11604,19 +11700,20 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AZ92" s="12"/>
-      <x:c r="BA92" s="12" t="n">
+      <x:c r="BA92" s="12"/>
+      <x:c r="BB92" s="12" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="BB92" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC92" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD92" s="12" t="str">
+      <x:c r="BD92" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE92" s="12" t="str">
         <x:v>Si; S; Cu; Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE92" s="12" t="str">
+      <x:c r="BF92" s="12" t="str">
         <x:v>Surface chromizing domain. Y2O3 is pack addition, not measured steelY. Table1 has TWO S headings with .75/.015 and Cr8/Ni11 inconsistent with grade; Si/S left unavailable, other printed values retained. Substrate chemistry not layer chemistry. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -11733,19 +11830,20 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AZ93" s="12"/>
-      <x:c r="BA93" s="12" t="n">
+      <x:c r="BA93" s="12"/>
+      <x:c r="BB93" s="12" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="BB93" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC93" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD93" s="12" t="str">
+      <x:c r="BD93" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE93" s="12" t="str">
         <x:v>Si; S; Cu; Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE93" s="12" t="str">
+      <x:c r="BF93" s="12" t="str">
         <x:v>Surface chromizing domain. Y2O3 is pack addition, not measured steelY. Table1 has TWO S headings with .75/.015 and Cr8/Ni11 inconsistent with grade; Si/S left unavailable, other printed values retained. Substrate chemistry not layer chemistry. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -11862,19 +11960,20 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AZ94" s="12"/>
-      <x:c r="BA94" s="12" t="n">
+      <x:c r="BA94" s="12"/>
+      <x:c r="BB94" s="12" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="BB94" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC94" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD94" s="12" t="str">
+      <x:c r="BD94" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE94" s="12" t="str">
         <x:v>Si; S; Cu; Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; 침지시간(min); 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE94" s="12" t="str">
+      <x:c r="BF94" s="12" t="str">
         <x:v>Surface chromizing domain. Y2O3 is pack addition, not measured steelY. Table1 has TWO S headings with .75/.015 and Cr8/Ni11 inconsistent with grade; Si/S left unavailable, other printed values retained. Substrate chemistry not layer chemistry. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
       </x:c>
     </x:row>
@@ -11967,19 +12066,20 @@
       <x:c r="AX95" s="12"/>
       <x:c r="AY95" s="12"/>
       <x:c r="AZ95" s="12"/>
-      <x:c r="BA95" s="12" t="n">
+      <x:c r="BA95" s="12"/>
+      <x:c r="BB95" s="12" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="BB95" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC95" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD95" s="12" t="str">
+      <x:c r="BD95" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE95" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE95" s="12" t="str">
+      <x:c r="BF95" s="12" t="str">
         <x:v>Original workbook has shifted chemistry. Source chemistry retained exactly. Fig6 current unit conflicts curve magnitude; C2 6.350 vs3.35 prose conflict. C1 numeric target not extracted. 960h corrosion clock not automatically AF minute soak.</x:v>
       </x:c>
     </x:row>
@@ -12072,19 +12172,20 @@
       <x:c r="AX96" s="12"/>
       <x:c r="AY96" s="12"/>
       <x:c r="AZ96" s="12"/>
-      <x:c r="BA96" s="12" t="n">
+      <x:c r="BA96" s="12"/>
+      <x:c r="BB96" s="12" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="BB96" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC96" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD96" s="12" t="str">
+      <x:c r="BD96" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE96" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE96" s="12" t="str">
+      <x:c r="BF96" s="12" t="str">
         <x:v>Original workbook has shifted chemistry. Source chemistry retained exactly. Fig6 current unit conflicts curve magnitude; C2 6.350 vs3.35 prose conflict. C1 numeric target not extracted. 960h corrosion clock not automatically AF minute soak.</x:v>
       </x:c>
     </x:row>
@@ -12179,19 +12280,20 @@
       <x:c r="AX97" s="12"/>
       <x:c r="AY97" s="12"/>
       <x:c r="AZ97" s="12"/>
-      <x:c r="BA97" s="12" t="n">
+      <x:c r="BA97" s="12"/>
+      <x:c r="BB97" s="12" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="BB97" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC97" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD97" s="12" t="str">
+      <x:c r="BD97" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE97" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE97" s="12" t="str">
+      <x:c r="BF97" s="12" t="str">
         <x:v>Original workbook has shifted chemistry. Source chemistry retained exactly. Fig6 current unit conflicts curve magnitude; C2 6.350 vs3.35 prose conflict. C1 numeric target not extracted. 960h corrosion clock not automatically AF minute soak.</x:v>
       </x:c>
     </x:row>
@@ -12286,19 +12388,20 @@
       <x:c r="AX98" s="12"/>
       <x:c r="AY98" s="12"/>
       <x:c r="AZ98" s="12"/>
-      <x:c r="BA98" s="12" t="n">
+      <x:c r="BA98" s="12"/>
+      <x:c r="BB98" s="12" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="BB98" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC98" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD98" s="12" t="str">
+      <x:c r="BD98" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE98" s="12" t="str">
         <x:v>Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE98" s="12" t="str">
+      <x:c r="BF98" s="12" t="str">
         <x:v>Original workbook has shifted chemistry. Source chemistry retained exactly. Fig6 current unit conflicts curve magnitude; C2 6.350 vs3.35 prose conflict. C1 numeric target not extracted. 960h corrosion clock not automatically AF minute soak.</x:v>
       </x:c>
     </x:row>
@@ -12394,22 +12497,23 @@
       <x:c r="AW99" s="12"/>
       <x:c r="AX99" s="12"/>
       <x:c r="AY99" s="12"/>
-      <x:c r="AZ99" s="12" t="n">
+      <x:c r="AZ99" s="12"/>
+      <x:c r="BA99" s="12" t="n">
         <x:v>0.002</x:v>
       </x:c>
-      <x:c r="BA99" s="12" t="n">
+      <x:c r="BB99" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB99" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC99" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD99" s="12" t="str">
+      <x:c r="BD99" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE99" s="12" t="str">
         <x:v>S; Mo; T.N.(Total Nitrogen); V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE99" s="12" t="str">
+      <x:c r="BF99" s="12" t="str">
         <x:v>S is &lt;0.002, not measured0.002. No tabulated icorr. Salt-spray exposure and 20min pre-EIS soaking not assigned to PDP time.</x:v>
       </x:c>
     </x:row>
@@ -12507,22 +12611,23 @@
       <x:c r="AW100" s="12"/>
       <x:c r="AX100" s="12"/>
       <x:c r="AY100" s="12"/>
-      <x:c r="AZ100" s="12" t="n">
+      <x:c r="AZ100" s="12"/>
+      <x:c r="BA100" s="12" t="n">
         <x:v>0.002</x:v>
       </x:c>
-      <x:c r="BA100" s="12" t="n">
+      <x:c r="BB100" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB100" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC100" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD100" s="12" t="str">
+      <x:c r="BD100" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE100" s="12" t="str">
         <x:v>S; Mo; T.N.(Total Nitrogen); V; Ti; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE100" s="12" t="str">
+      <x:c r="BF100" s="12" t="str">
         <x:v>S is &lt;0.002, not measured0.002. No tabulated icorr. Salt-spray exposure and 20min pre-EIS soaking not assigned to PDP time.</x:v>
       </x:c>
     </x:row>
@@ -12620,22 +12725,23 @@
       <x:c r="AW101" s="12"/>
       <x:c r="AX101" s="12"/>
       <x:c r="AY101" s="12"/>
-      <x:c r="AZ101" s="12" t="n">
+      <x:c r="AZ101" s="12"/>
+      <x:c r="BA101" s="12" t="n">
         <x:v>0.002</x:v>
       </x:c>
-      <x:c r="BA101" s="12" t="n">
+      <x:c r="BB101" s="12" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="BB101" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC101" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD101" s="12" t="str">
+      <x:c r="BD101" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE101" s="12" t="str">
         <x:v>S; Mo; T.N.(Total Nitrogen); V; Ti; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE101" s="12" t="str">
+      <x:c r="BF101" s="12" t="str">
         <x:v>S is &lt;0.002, not measured0.002. No tabulated icorr. Salt-spray exposure and 20min pre-EIS soaking not assigned to PDP time.</x:v>
       </x:c>
     </x:row>
@@ -12726,19 +12832,20 @@
       <x:c r="AX102" s="12"/>
       <x:c r="AY102" s="12"/>
       <x:c r="AZ102" s="12"/>
-      <x:c r="BA102" s="12" t="n">
+      <x:c r="BA102" s="12"/>
+      <x:c r="BB102" s="12" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="BB102" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC102" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD102" s="12" t="str">
+      <x:c r="BD102" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE102" s="12" t="str">
         <x:v>Ni; Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE102" s="12" t="str">
+      <x:c r="BF102" s="12" t="str">
         <x:v>Final average chemical compositions as reported. No numerical PDP icorr table. Dash controls not treated as analytical zero. Mass-loss target not converted to icorr.</x:v>
       </x:c>
     </x:row>
@@ -12835,19 +12942,20 @@
       <x:c r="AX103" s="12"/>
       <x:c r="AY103" s="12"/>
       <x:c r="AZ103" s="12"/>
-      <x:c r="BA103" s="12" t="n">
+      <x:c r="BA103" s="12"/>
+      <x:c r="BB103" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB103" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC103" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD103" s="12" t="str">
+      <x:c r="BD103" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE103" s="12" t="str">
         <x:v>Ni; Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE103" s="12" t="str">
+      <x:c r="BF103" s="12" t="str">
         <x:v>Final average chemical compositions as reported. No numerical PDP icorr table. Dash controls not treated as analytical zero. Mass-loss target not converted to icorr.</x:v>
       </x:c>
     </x:row>
@@ -12938,19 +13046,20 @@
       <x:c r="AX104" s="12"/>
       <x:c r="AY104" s="12"/>
       <x:c r="AZ104" s="12"/>
-      <x:c r="BA104" s="12" t="n">
+      <x:c r="BA104" s="12"/>
+      <x:c r="BB104" s="12" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="BB104" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC104" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD104" s="12" t="str">
+      <x:c r="BD104" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE104" s="12" t="str">
         <x:v>Ni; Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE104" s="12" t="str">
+      <x:c r="BF104" s="12" t="str">
         <x:v>Final average chemical compositions as reported. No numerical PDP icorr table. Dash controls not treated as analytical zero. Mass-loss target not converted to icorr.</x:v>
       </x:c>
     </x:row>
@@ -13047,19 +13156,20 @@
       <x:c r="AX105" s="12"/>
       <x:c r="AY105" s="12"/>
       <x:c r="AZ105" s="12"/>
-      <x:c r="BA105" s="12" t="n">
+      <x:c r="BA105" s="12"/>
+      <x:c r="BB105" s="12" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="BB105" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC105" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD105" s="12" t="str">
+      <x:c r="BD105" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE105" s="12" t="str">
         <x:v>Ni; Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE105" s="12" t="str">
+      <x:c r="BF105" s="12" t="str">
         <x:v>Final average chemical compositions as reported. No numerical PDP icorr table. Dash controls not treated as analytical zero. Mass-loss target not converted to icorr.</x:v>
       </x:c>
     </x:row>
@@ -13166,19 +13276,20 @@
       <x:c r="AX106" s="12"/>
       <x:c r="AY106" s="12"/>
       <x:c r="AZ106" s="12"/>
-      <x:c r="BA106" s="12" t="n">
+      <x:c r="BA106" s="12"/>
+      <x:c r="BB106" s="12" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="BB106" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC106" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD106" s="12" t="str">
+      <x:c r="BD106" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE106" s="12" t="str">
         <x:v>P; S; Cr; Cu; T.N.(Total Nitrogen); Nb; V; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE106" s="12" t="str">
+      <x:c r="BF106" s="12" t="str">
         <x:v>P/S and bulk RE unreported. Ferroalloy addition to powdered flux is not weld residual Ce/La. No base-plate composition substitution.</x:v>
       </x:c>
     </x:row>
@@ -13285,19 +13396,20 @@
       <x:c r="AX107" s="12"/>
       <x:c r="AY107" s="12"/>
       <x:c r="AZ107" s="12"/>
-      <x:c r="BA107" s="12" t="n">
+      <x:c r="BA107" s="12"/>
+      <x:c r="BB107" s="12" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="BB107" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC107" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD107" s="12" t="str">
+      <x:c r="BD107" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE107" s="12" t="str">
         <x:v>P; S; Cr; Cu; T.N.(Total Nitrogen); Nb; V; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE107" s="12" t="str">
+      <x:c r="BF107" s="12" t="str">
         <x:v>P/S and bulk RE unreported. Ferroalloy addition to powdered flux is not weld residual Ce/La. No base-plate composition substitution.</x:v>
       </x:c>
     </x:row>
@@ -13404,19 +13516,20 @@
       <x:c r="AX108" s="12"/>
       <x:c r="AY108" s="12"/>
       <x:c r="AZ108" s="12"/>
-      <x:c r="BA108" s="12" t="n">
+      <x:c r="BA108" s="12"/>
+      <x:c r="BB108" s="12" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="BB108" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC108" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD108" s="12" t="str">
+      <x:c r="BD108" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE108" s="12" t="str">
         <x:v>P; S; Cr; Cu; T.N.(Total Nitrogen); Nb; V; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE108" s="12" t="str">
+      <x:c r="BF108" s="12" t="str">
         <x:v>P/S and bulk RE unreported. Ferroalloy addition to powdered flux is not weld residual Ce/La. No base-plate composition substitution.</x:v>
       </x:c>
     </x:row>
@@ -13523,19 +13636,20 @@
       <x:c r="AX109" s="12"/>
       <x:c r="AY109" s="12"/>
       <x:c r="AZ109" s="12"/>
-      <x:c r="BA109" s="12" t="n">
+      <x:c r="BA109" s="12"/>
+      <x:c r="BB109" s="12" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="BB109" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC109" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD109" s="12" t="str">
+      <x:c r="BD109" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE109" s="12" t="str">
         <x:v>P; S; Cr; Cu; T.N.(Total Nitrogen); Nb; V; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE109" s="12" t="str">
+      <x:c r="BF109" s="12" t="str">
         <x:v>P/S and bulk RE unreported. Ferroalloy addition to powdered flux is not weld residual Ce/La. No base-plate composition substitution.</x:v>
       </x:c>
     </x:row>
@@ -13642,19 +13756,20 @@
       <x:c r="AX110" s="12"/>
       <x:c r="AY110" s="12"/>
       <x:c r="AZ110" s="12"/>
-      <x:c r="BA110" s="12" t="n">
+      <x:c r="BA110" s="12"/>
+      <x:c r="BB110" s="12" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="BB110" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC110" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD110" s="12" t="str">
+      <x:c r="BD110" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE110" s="12" t="str">
         <x:v>P; S; Cr; Cu; T.N.(Total Nitrogen); Nb; V; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 온도(°C)</x:v>
       </x:c>
-      <x:c r="BE110" s="12" t="str">
+      <x:c r="BF110" s="12" t="str">
         <x:v>P/S and bulk RE unreported. Ferroalloy addition to powdered flux is not weld residual Ce/La. No base-plate composition substitution.</x:v>
       </x:c>
     </x:row>
@@ -13737,19 +13852,20 @@
       <x:c r="AX111" s="12"/>
       <x:c r="AY111" s="12"/>
       <x:c r="AZ111" s="12"/>
-      <x:c r="BA111" s="12" t="n">
+      <x:c r="BA111" s="12"/>
+      <x:c r="BB111" s="12" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="BB111" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC111" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD111" s="12" t="str">
+      <x:c r="BD111" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE111" s="12" t="str">
         <x:v>C; Si; Mn; P; S; Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE111" s="12" t="str">
+      <x:c r="BF111" s="12" t="str">
         <x:v>No quantitative elemental chemistry table. Y2O3 powder addition kept separate from bulk Y. Table4 has Ecorr/Eb but no icorr;5Y sample not present in Table4.</x:v>
       </x:c>
     </x:row>
@@ -13832,19 +13948,20 @@
       <x:c r="AX112" s="12"/>
       <x:c r="AY112" s="12"/>
       <x:c r="AZ112" s="12"/>
-      <x:c r="BA112" s="12" t="n">
+      <x:c r="BA112" s="12"/>
+      <x:c r="BB112" s="12" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="BB112" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC112" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD112" s="12" t="str">
+      <x:c r="BD112" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE112" s="12" t="str">
         <x:v>C; Si; Mn; P; S; Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE112" s="12" t="str">
+      <x:c r="BF112" s="12" t="str">
         <x:v>No quantitative elemental chemistry table. Y2O3 powder addition kept separate from bulk Y. Table4 has Ecorr/Eb but no icorr;5Y sample not present in Table4.</x:v>
       </x:c>
     </x:row>
@@ -13929,19 +14046,20 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AZ113" s="12"/>
-      <x:c r="BA113" s="12" t="n">
+      <x:c r="BA113" s="12"/>
+      <x:c r="BB113" s="12" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="BB113" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC113" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD113" s="12" t="str">
+      <x:c r="BD113" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE113" s="12" t="str">
         <x:v>C; Si; Mn; P; S; Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE113" s="12" t="str">
+      <x:c r="BF113" s="12" t="str">
         <x:v>No quantitative elemental chemistry table. Y2O3 powder addition kept separate from bulk Y. Table4 has Ecorr/Eb but no icorr;5Y sample not present in Table4.</x:v>
       </x:c>
     </x:row>
@@ -14026,19 +14144,20 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AZ114" s="12"/>
-      <x:c r="BA114" s="12" t="n">
+      <x:c r="BA114" s="12"/>
+      <x:c r="BB114" s="12" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="BB114" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC114" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD114" s="12" t="str">
+      <x:c r="BD114" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE114" s="12" t="str">
         <x:v>C; Si; Mn; P; S; Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 주사속도(mV/s); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE114" s="12" t="str">
+      <x:c r="BF114" s="12" t="str">
         <x:v>No quantitative elemental chemistry table. Y2O3 powder addition kept separate from bulk Y. Table4 has Ecorr/Eb but no icorr;5Y sample not present in Table4.</x:v>
       </x:c>
     </x:row>
@@ -14121,26 +14240,4383 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AZ115" s="12"/>
-      <x:c r="BA115" s="12" t="n">
+      <x:c r="BA115" s="12"/>
+      <x:c r="BB115" s="12" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="BB115" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC115" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BD115" s="12" t="str">
+      <x:c r="BD115" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE115" s="12" t="str">
         <x:v>C; Si; Mn; P; S; Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
       </x:c>
-      <x:c r="BE115" s="12" t="str">
+      <x:c r="BF115" s="12" t="str">
         <x:v>No quantitative elemental chemistry table. Y2O3 powder addition kept separate from bulk Y. Table4 has Ecorr/Eb but no icorr;5Y sample not present in Table4.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="40" customHeight="1">
+      <x:c r="A116" s="12" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B116" s="13" t="str">
+        <x:v>Zr–Ti–Al–RE 탈산 고강도 저합금강(HSLA, TMCP 12mm)</x:v>
+      </x:c>
+      <x:c r="C116" s="13" t="str">
+        <x:v>BM</x:v>
+      </x:c>
+      <x:c r="D116" s="14" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="E116" s="14" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+      <x:c r="F116" s="14" t="n">
+        <x:v>1.55</x:v>
+      </x:c>
+      <x:c r="G116" s="14"/>
+      <x:c r="H116" s="14"/>
+      <x:c r="I116" s="14"/>
+      <x:c r="J116" s="14"/>
+      <x:c r="K116" s="14"/>
+      <x:c r="L116" s="14"/>
+      <x:c r="M116" s="14"/>
+      <x:c r="N116" s="14" t="n">
+        <x:v>0.034</x:v>
+      </x:c>
+      <x:c r="O116" s="14"/>
+      <x:c r="P116" s="14"/>
+      <x:c r="Q116" s="14"/>
+      <x:c r="R116" s="14"/>
+      <x:c r="S116" s="14"/>
+      <x:c r="T116" s="14"/>
+      <x:c r="U116" s="14"/>
+      <x:c r="V116" s="14"/>
+      <x:c r="W116" s="14"/>
+      <x:c r="X116" s="14"/>
+      <x:c r="Y116" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z116" s="12"/>
+      <x:c r="AA116" s="15"/>
+      <x:c r="AB116" s="15"/>
+      <x:c r="AC116" s="12"/>
+      <x:c r="AD116" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE116" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF116" s="12"/>
+      <x:c r="AG116" s="12"/>
+      <x:c r="AH116" s="12"/>
+      <x:c r="AI116" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ116" s="12"/>
+      <x:c r="AK116" s="16"/>
+      <x:c r="AL116" s="16"/>
+      <x:c r="AM116" s="12" t="str">
+        <x:v>WM39_BM</x:v>
+      </x:c>
+      <x:c r="AN116" s="12" t="str">
+        <x:v>10.3390/ma16020876</x:v>
+      </x:c>
+      <x:c r="AO116" s="12" t="str">
+        <x:v>https://doi.org/10.3390/ma16020876</x:v>
+      </x:c>
+      <x:c r="AP116" s="12" t="str">
+        <x:v>Table1 PDF p4; Table4/Fig5 PDF pp9-10; electrochemical methods</x:v>
+      </x:c>
+      <x:c r="AQ116" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR116" s="12" t="str">
+        <x:v>quarantined_printed_unit_conflict</x:v>
+      </x:c>
+      <x:c r="AS116" s="12" t="n">
+        <x:v>0.00000931</x:v>
+      </x:c>
+      <x:c r="AT116" s="12" t="str">
+        <x:v>Table4 prints A cm^2; corrosion-density area exponent unresolved</x:v>
+      </x:c>
+      <x:c r="AU116" s="12"/>
+      <x:c r="AV116" s="12"/>
+      <x:c r="AW116" s="12"/>
+      <x:c r="AX116" s="12"/>
+      <x:c r="AY116" s="12"/>
+      <x:c r="AZ116" s="12"/>
+      <x:c r="BA116" s="12"/>
+      <x:c r="BB116" s="12" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="BC116" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD116" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE116" s="12" t="str">
+        <x:v>P; S; Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF116" s="12" t="str">
+        <x:v>Al+Ca+Zr+Ti+RE reported only as combined0.04wt%; no individual RE amount. Preserve exact Table4 values in raw column; canonical area-unit correction not assumed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="40" customHeight="1">
+      <x:c r="A117" s="12" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B117" s="13" t="str">
+        <x:v>Zr–Ti–Al–RE 탈산 고강도 저합금강(HSLA, TMCP 12mm)</x:v>
+      </x:c>
+      <x:c r="C117" s="13" t="str">
+        <x:v>CGHAZ</x:v>
+      </x:c>
+      <x:c r="D117" s="14" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="E117" s="14" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+      <x:c r="F117" s="14" t="n">
+        <x:v>1.55</x:v>
+      </x:c>
+      <x:c r="G117" s="14"/>
+      <x:c r="H117" s="14"/>
+      <x:c r="I117" s="14"/>
+      <x:c r="J117" s="14"/>
+      <x:c r="K117" s="14"/>
+      <x:c r="L117" s="14"/>
+      <x:c r="M117" s="14"/>
+      <x:c r="N117" s="14" t="n">
+        <x:v>0.034</x:v>
+      </x:c>
+      <x:c r="O117" s="14"/>
+      <x:c r="P117" s="14"/>
+      <x:c r="Q117" s="14"/>
+      <x:c r="R117" s="14"/>
+      <x:c r="S117" s="14"/>
+      <x:c r="T117" s="14"/>
+      <x:c r="U117" s="14"/>
+      <x:c r="V117" s="14"/>
+      <x:c r="W117" s="14"/>
+      <x:c r="X117" s="14"/>
+      <x:c r="Y117" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z117" s="12"/>
+      <x:c r="AA117" s="15"/>
+      <x:c r="AB117" s="15"/>
+      <x:c r="AC117" s="12"/>
+      <x:c r="AD117" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE117" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF117" s="12"/>
+      <x:c r="AG117" s="12"/>
+      <x:c r="AH117" s="12"/>
+      <x:c r="AI117" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ117" s="12"/>
+      <x:c r="AK117" s="16"/>
+      <x:c r="AL117" s="16"/>
+      <x:c r="AM117" s="12" t="str">
+        <x:v>WM39_CGHAZ</x:v>
+      </x:c>
+      <x:c r="AN117" s="12" t="str">
+        <x:v>10.3390/ma16020876</x:v>
+      </x:c>
+      <x:c r="AO117" s="12" t="str">
+        <x:v>https://doi.org/10.3390/ma16020876</x:v>
+      </x:c>
+      <x:c r="AP117" s="12" t="str">
+        <x:v>Table1 PDF p4; Table4/Fig5 PDF pp9-10; electrochemical methods</x:v>
+      </x:c>
+      <x:c r="AQ117" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR117" s="12" t="str">
+        <x:v>quarantined_printed_unit_conflict</x:v>
+      </x:c>
+      <x:c r="AS117" s="12" t="n">
+        <x:v>0.0000102</x:v>
+      </x:c>
+      <x:c r="AT117" s="12" t="str">
+        <x:v>Table4 prints A cm^2; corrosion-density area exponent unresolved</x:v>
+      </x:c>
+      <x:c r="AU117" s="12"/>
+      <x:c r="AV117" s="12"/>
+      <x:c r="AW117" s="12"/>
+      <x:c r="AX117" s="12"/>
+      <x:c r="AY117" s="12"/>
+      <x:c r="AZ117" s="12"/>
+      <x:c r="BA117" s="12"/>
+      <x:c r="BB117" s="12" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="BC117" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD117" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE117" s="12" t="str">
+        <x:v>P; S; Cr; Ni; Mo; Cu; T.N.(Total Nitrogen); V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF117" s="12" t="str">
+        <x:v>Al+Ca+Zr+Ti+RE reported only as combined0.04wt%; no individual RE amount. Preserve exact Table4 values in raw column; canonical area-unit correction not assumed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="40" customHeight="1">
+      <x:c r="A118" s="12" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B118" s="13" t="str">
+        <x:v>저Ni 오스테나이트계 스테인리스강</x:v>
+      </x:c>
+      <x:c r="C118" s="13" t="str">
+        <x:v>A1</x:v>
+      </x:c>
+      <x:c r="D118" s="14" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="E118" s="14" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="F118" s="14" t="n">
+        <x:v>15.2</x:v>
+      </x:c>
+      <x:c r="G118" s="14" t="n">
+        <x:v>0.009</x:v>
+      </x:c>
+      <x:c r="H118" s="14" t="n">
+        <x:v>0.006</x:v>
+      </x:c>
+      <x:c r="I118" s="14" t="n">
+        <x:v>17.51</x:v>
+      </x:c>
+      <x:c r="J118" s="14" t="n">
+        <x:v>1.29</x:v>
+      </x:c>
+      <x:c r="K118" s="14"/>
+      <x:c r="L118" s="14"/>
+      <x:c r="M118" s="14" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="N118" s="14"/>
+      <x:c r="O118" s="14"/>
+      <x:c r="P118" s="14"/>
+      <x:c r="Q118" s="14" t="n">
+        <x:v>0.022</x:v>
+      </x:c>
+      <x:c r="R118" s="14"/>
+      <x:c r="S118" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T118" s="14"/>
+      <x:c r="U118" s="14"/>
+      <x:c r="V118" s="14"/>
+      <x:c r="W118" s="14"/>
+      <x:c r="X118" s="14"/>
+      <x:c r="Y118" s="12"/>
+      <x:c r="Z118" s="12"/>
+      <x:c r="AA118" s="15"/>
+      <x:c r="AB118" s="15"/>
+      <x:c r="AC118" s="12"/>
+      <x:c r="AD118" s="12" t="str">
+        <x:v>H2SO4</x:v>
+      </x:c>
+      <x:c r="AE118" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AF118" s="12"/>
+      <x:c r="AG118" s="12"/>
+      <x:c r="AH118" s="12"/>
+      <x:c r="AI118" s="12"/>
+      <x:c r="AJ118" s="12"/>
+      <x:c r="AK118" s="16"/>
+      <x:c r="AL118" s="16"/>
+      <x:c r="AM118" s="12" t="str">
+        <x:v>WM26_A1</x:v>
+      </x:c>
+      <x:c r="AN118" s="12" t="str">
+        <x:v>10.2355/isijinternational.ISIJINT-2019-248</x:v>
+      </x:c>
+      <x:c r="AO118" s="12" t="str">
+        <x:v>https://www.jstage.jst.go.jp/article/isijinternational/59/12/59_ISIJINT-2019-248/_html/-char/en</x:v>
+      </x:c>
+      <x:c r="AP118" s="12" t="str">
+        <x:v>Publisher J-STAGE full text Table1; corrosion-weight-loss methods</x:v>
+      </x:c>
+      <x:c r="AQ118" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR118" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS118" s="12"/>
+      <x:c r="AT118" s="12"/>
+      <x:c r="AU118" s="12"/>
+      <x:c r="AV118" s="12"/>
+      <x:c r="AW118" s="12"/>
+      <x:c r="AX118" s="12"/>
+      <x:c r="AY118" s="12"/>
+      <x:c r="AZ118" s="12"/>
+      <x:c r="BA118" s="12"/>
+      <x:c r="BB118" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="BC118" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD118" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE118" s="12" t="str">
+        <x:v>Mo; Cu; Nb; V; Ti; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF118" s="12" t="str">
+        <x:v>Corrosion target is gravimetric rate, not Tafel icorr. No target conversion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="40" customHeight="1">
+      <x:c r="A119" s="12" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B119" s="13" t="str">
+        <x:v>저Ni 오스테나이트계 스테인리스강</x:v>
+      </x:c>
+      <x:c r="C119" s="13" t="str">
+        <x:v>A2</x:v>
+      </x:c>
+      <x:c r="D119" s="14" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="E119" s="14" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="F119" s="14" t="n">
+        <x:v>15.4</x:v>
+      </x:c>
+      <x:c r="G119" s="14" t="n">
+        <x:v>0.008</x:v>
+      </x:c>
+      <x:c r="H119" s="14" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+      <x:c r="I119" s="14" t="n">
+        <x:v>17.53</x:v>
+      </x:c>
+      <x:c r="J119" s="14" t="n">
+        <x:v>1.27</x:v>
+      </x:c>
+      <x:c r="K119" s="14"/>
+      <x:c r="L119" s="14"/>
+      <x:c r="M119" s="14" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="N119" s="14"/>
+      <x:c r="O119" s="14"/>
+      <x:c r="P119" s="14"/>
+      <x:c r="Q119" s="14" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="R119" s="14"/>
+      <x:c r="S119" s="14" t="n">
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="T119" s="14"/>
+      <x:c r="U119" s="14"/>
+      <x:c r="V119" s="14"/>
+      <x:c r="W119" s="14"/>
+      <x:c r="X119" s="14"/>
+      <x:c r="Y119" s="12"/>
+      <x:c r="Z119" s="12"/>
+      <x:c r="AA119" s="15"/>
+      <x:c r="AB119" s="15"/>
+      <x:c r="AC119" s="12"/>
+      <x:c r="AD119" s="12" t="str">
+        <x:v>H2SO4</x:v>
+      </x:c>
+      <x:c r="AE119" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AF119" s="12"/>
+      <x:c r="AG119" s="12"/>
+      <x:c r="AH119" s="12"/>
+      <x:c r="AI119" s="12"/>
+      <x:c r="AJ119" s="12"/>
+      <x:c r="AK119" s="16"/>
+      <x:c r="AL119" s="16"/>
+      <x:c r="AM119" s="12" t="str">
+        <x:v>WM26_A2</x:v>
+      </x:c>
+      <x:c r="AN119" s="12" t="str">
+        <x:v>10.2355/isijinternational.ISIJINT-2019-248</x:v>
+      </x:c>
+      <x:c r="AO119" s="12" t="str">
+        <x:v>https://www.jstage.jst.go.jp/article/isijinternational/59/12/59_ISIJINT-2019-248/_html/-char/en</x:v>
+      </x:c>
+      <x:c r="AP119" s="12" t="str">
+        <x:v>Publisher J-STAGE full text Table1; corrosion-weight-loss methods</x:v>
+      </x:c>
+      <x:c r="AQ119" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR119" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS119" s="12"/>
+      <x:c r="AT119" s="12"/>
+      <x:c r="AU119" s="12"/>
+      <x:c r="AV119" s="12"/>
+      <x:c r="AW119" s="12"/>
+      <x:c r="AX119" s="12"/>
+      <x:c r="AY119" s="12"/>
+      <x:c r="AZ119" s="12"/>
+      <x:c r="BA119" s="12"/>
+      <x:c r="BB119" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="BC119" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD119" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE119" s="12" t="str">
+        <x:v>Mo; Cu; Nb; V; Ti; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF119" s="12" t="str">
+        <x:v>Corrosion target is gravimetric rate, not Tafel icorr. No target conversion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="40" customHeight="1">
+      <x:c r="A120" s="12" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B120" s="13" t="str">
+        <x:v>저Ni 오스테나이트계 스테인리스강</x:v>
+      </x:c>
+      <x:c r="C120" s="13" t="str">
+        <x:v>A3</x:v>
+      </x:c>
+      <x:c r="D120" s="14" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="E120" s="14" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="F120" s="14" t="n">
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="G120" s="14" t="n">
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="H120" s="14" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+      <x:c r="I120" s="14" t="n">
+        <x:v>17.51</x:v>
+      </x:c>
+      <x:c r="J120" s="14" t="n">
+        <x:v>1.28</x:v>
+      </x:c>
+      <x:c r="K120" s="14"/>
+      <x:c r="L120" s="14"/>
+      <x:c r="M120" s="14" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="N120" s="14"/>
+      <x:c r="O120" s="14"/>
+      <x:c r="P120" s="14"/>
+      <x:c r="Q120" s="14" t="n">
+        <x:v>0.026</x:v>
+      </x:c>
+      <x:c r="R120" s="14"/>
+      <x:c r="S120" s="14" t="n">
+        <x:v>0.016</x:v>
+      </x:c>
+      <x:c r="T120" s="14"/>
+      <x:c r="U120" s="14"/>
+      <x:c r="V120" s="14"/>
+      <x:c r="W120" s="14"/>
+      <x:c r="X120" s="14"/>
+      <x:c r="Y120" s="12"/>
+      <x:c r="Z120" s="12"/>
+      <x:c r="AA120" s="15"/>
+      <x:c r="AB120" s="15"/>
+      <x:c r="AC120" s="12"/>
+      <x:c r="AD120" s="12" t="str">
+        <x:v>H2SO4</x:v>
+      </x:c>
+      <x:c r="AE120" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AF120" s="12"/>
+      <x:c r="AG120" s="12"/>
+      <x:c r="AH120" s="12"/>
+      <x:c r="AI120" s="12"/>
+      <x:c r="AJ120" s="12"/>
+      <x:c r="AK120" s="16"/>
+      <x:c r="AL120" s="16"/>
+      <x:c r="AM120" s="12" t="str">
+        <x:v>WM26_A3</x:v>
+      </x:c>
+      <x:c r="AN120" s="12" t="str">
+        <x:v>10.2355/isijinternational.ISIJINT-2019-248</x:v>
+      </x:c>
+      <x:c r="AO120" s="12" t="str">
+        <x:v>https://www.jstage.jst.go.jp/article/isijinternational/59/12/59_ISIJINT-2019-248/_html/-char/en</x:v>
+      </x:c>
+      <x:c r="AP120" s="12" t="str">
+        <x:v>Publisher J-STAGE full text Table1; corrosion-weight-loss methods</x:v>
+      </x:c>
+      <x:c r="AQ120" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR120" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS120" s="12"/>
+      <x:c r="AT120" s="12"/>
+      <x:c r="AU120" s="12"/>
+      <x:c r="AV120" s="12"/>
+      <x:c r="AW120" s="12"/>
+      <x:c r="AX120" s="12"/>
+      <x:c r="AY120" s="12"/>
+      <x:c r="AZ120" s="12"/>
+      <x:c r="BA120" s="12"/>
+      <x:c r="BB120" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="BC120" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD120" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE120" s="12" t="str">
+        <x:v>Mo; Cu; Nb; V; Ti; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF120" s="12" t="str">
+        <x:v>Corrosion target is gravimetric rate, not Tafel icorr. No target conversion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="40" customHeight="1">
+      <x:c r="A121" s="12" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B121" s="13" t="str">
+        <x:v>저Ni 오스테나이트계 스테인리스강</x:v>
+      </x:c>
+      <x:c r="C121" s="13" t="str">
+        <x:v>A4</x:v>
+      </x:c>
+      <x:c r="D121" s="14" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="E121" s="14" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="F121" s="14" t="n">
+        <x:v>15.2</x:v>
+      </x:c>
+      <x:c r="G121" s="14" t="n">
+        <x:v>0.008</x:v>
+      </x:c>
+      <x:c r="H121" s="14" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+      <x:c r="I121" s="14" t="n">
+        <x:v>17.54</x:v>
+      </x:c>
+      <x:c r="J121" s="14" t="n">
+        <x:v>1.27</x:v>
+      </x:c>
+      <x:c r="K121" s="14"/>
+      <x:c r="L121" s="14"/>
+      <x:c r="M121" s="14" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="N121" s="14"/>
+      <x:c r="O121" s="14"/>
+      <x:c r="P121" s="14"/>
+      <x:c r="Q121" s="14" t="n">
+        <x:v>0.021</x:v>
+      </x:c>
+      <x:c r="R121" s="14"/>
+      <x:c r="S121" s="14" t="n">
+        <x:v>0.023</x:v>
+      </x:c>
+      <x:c r="T121" s="14"/>
+      <x:c r="U121" s="14"/>
+      <x:c r="V121" s="14"/>
+      <x:c r="W121" s="14"/>
+      <x:c r="X121" s="14"/>
+      <x:c r="Y121" s="12"/>
+      <x:c r="Z121" s="12"/>
+      <x:c r="AA121" s="15"/>
+      <x:c r="AB121" s="15"/>
+      <x:c r="AC121" s="12"/>
+      <x:c r="AD121" s="12" t="str">
+        <x:v>H2SO4</x:v>
+      </x:c>
+      <x:c r="AE121" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AF121" s="12"/>
+      <x:c r="AG121" s="12"/>
+      <x:c r="AH121" s="12"/>
+      <x:c r="AI121" s="12"/>
+      <x:c r="AJ121" s="12"/>
+      <x:c r="AK121" s="16"/>
+      <x:c r="AL121" s="16"/>
+      <x:c r="AM121" s="12" t="str">
+        <x:v>WM26_A4</x:v>
+      </x:c>
+      <x:c r="AN121" s="12" t="str">
+        <x:v>10.2355/isijinternational.ISIJINT-2019-248</x:v>
+      </x:c>
+      <x:c r="AO121" s="12" t="str">
+        <x:v>https://www.jstage.jst.go.jp/article/isijinternational/59/12/59_ISIJINT-2019-248/_html/-char/en</x:v>
+      </x:c>
+      <x:c r="AP121" s="12" t="str">
+        <x:v>Publisher J-STAGE full text Table1; corrosion-weight-loss methods</x:v>
+      </x:c>
+      <x:c r="AQ121" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR121" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS121" s="12"/>
+      <x:c r="AT121" s="12"/>
+      <x:c r="AU121" s="12"/>
+      <x:c r="AV121" s="12"/>
+      <x:c r="AW121" s="12"/>
+      <x:c r="AX121" s="12"/>
+      <x:c r="AY121" s="12"/>
+      <x:c r="AZ121" s="12"/>
+      <x:c r="BA121" s="12"/>
+      <x:c r="BB121" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="BC121" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD121" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE121" s="12" t="str">
+        <x:v>Mo; Cu; Nb; V; Ti; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF121" s="12" t="str">
+        <x:v>Corrosion target is gravimetric rate, not Tafel icorr. No target conversion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="40" customHeight="1">
+      <x:c r="A122" s="12" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B122" s="13" t="str">
+        <x:v>Q355 저합금강(Ce-La 첨가)</x:v>
+      </x:c>
+      <x:c r="C122" s="13" t="str">
+        <x:v>Q355</x:v>
+      </x:c>
+      <x:c r="D122" s="14" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="E122" s="14" t="n">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="F122" s="14" t="n">
+        <x:v>1.26</x:v>
+      </x:c>
+      <x:c r="G122" s="14" t="n">
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="H122" s="14" t="n">
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="I122" s="14" t="n">
+        <x:v>0.024</x:v>
+      </x:c>
+      <x:c r="J122" s="14" t="n">
+        <x:v>0.013</x:v>
+      </x:c>
+      <x:c r="K122" s="14"/>
+      <x:c r="L122" s="14" t="n">
+        <x:v>0.021</x:v>
+      </x:c>
+      <x:c r="M122" s="14"/>
+      <x:c r="N122" s="14"/>
+      <x:c r="O122" s="14"/>
+      <x:c r="P122" s="14"/>
+      <x:c r="Q122" s="14" t="n">
+        <x:v>0.049</x:v>
+      </x:c>
+      <x:c r="R122" s="14"/>
+      <x:c r="S122" s="14"/>
+      <x:c r="T122" s="14"/>
+      <x:c r="U122" s="14"/>
+      <x:c r="V122" s="14"/>
+      <x:c r="W122" s="14"/>
+      <x:c r="X122" s="14"/>
+      <x:c r="Y122" s="12"/>
+      <x:c r="Z122" s="12"/>
+      <x:c r="AA122" s="15"/>
+      <x:c r="AB122" s="15"/>
+      <x:c r="AC122" s="12"/>
+      <x:c r="AD122" s="12"/>
+      <x:c r="AE122" s="12"/>
+      <x:c r="AF122" s="12"/>
+      <x:c r="AG122" s="12"/>
+      <x:c r="AH122" s="12"/>
+      <x:c r="AI122" s="12"/>
+      <x:c r="AJ122" s="12"/>
+      <x:c r="AK122" s="16"/>
+      <x:c r="AL122" s="16"/>
+      <x:c r="AM122" s="12" t="str">
+        <x:v>WM47_Q355</x:v>
+      </x:c>
+      <x:c r="AN122" s="12" t="str">
+        <x:v>10.1007/s40195-022-01404-8</x:v>
+      </x:c>
+      <x:c r="AO122" s="12" t="str">
+        <x:v>https://doi.org/10.1007/s40195-022-01404-8</x:v>
+      </x:c>
+      <x:c r="AP122" s="12" t="str">
+        <x:v>Table1 PDF p2; Sec2.2; rust products Table3</x:v>
+      </x:c>
+      <x:c r="AQ122" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR122" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS122" s="12"/>
+      <x:c r="AT122" s="12"/>
+      <x:c r="AU122" s="12"/>
+      <x:c r="AV122" s="12"/>
+      <x:c r="AW122" s="12"/>
+      <x:c r="AX122" s="12"/>
+      <x:c r="AY122" s="12"/>
+      <x:c r="AZ122" s="12"/>
+      <x:c r="BA122" s="12"/>
+      <x:c r="BB122" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="BC122" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD122" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE122" s="12" t="str">
+        <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF122" s="12" t="str">
+        <x:v>Exact sample chemistry. Paper reports wet-dry mass loss and rust composition; no tabulated numerical icorr. Dash RE controls not analytical zero.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="40" customHeight="1">
+      <x:c r="A123" s="12" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B123" s="13" t="str">
+        <x:v>Q355 저합금강(Ce-La 첨가)</x:v>
+      </x:c>
+      <x:c r="C123" s="13" t="str">
+        <x:v>Q355RE</x:v>
+      </x:c>
+      <x:c r="D123" s="14" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="E123" s="14" t="n">
+        <x:v>0.22</x:v>
+      </x:c>
+      <x:c r="F123" s="14" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="G123" s="14" t="n">
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="H123" s="14" t="n">
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="I123" s="14" t="n">
+        <x:v>0.023</x:v>
+      </x:c>
+      <x:c r="J123" s="14" t="n">
+        <x:v>0.013</x:v>
+      </x:c>
+      <x:c r="K123" s="14"/>
+      <x:c r="L123" s="14" t="n">
+        <x:v>0.021</x:v>
+      </x:c>
+      <x:c r="M123" s="14"/>
+      <x:c r="N123" s="14"/>
+      <x:c r="O123" s="14"/>
+      <x:c r="P123" s="14"/>
+      <x:c r="Q123" s="14" t="n">
+        <x:v>0.049</x:v>
+      </x:c>
+      <x:c r="R123" s="14"/>
+      <x:c r="S123" s="14" t="n">
+        <x:v>0.0144</x:v>
+      </x:c>
+      <x:c r="T123" s="14" t="n">
+        <x:v>0.0064</x:v>
+      </x:c>
+      <x:c r="U123" s="14"/>
+      <x:c r="V123" s="14"/>
+      <x:c r="W123" s="14"/>
+      <x:c r="X123" s="14" t="n">
+        <x:v>0.0208</x:v>
+      </x:c>
+      <x:c r="Y123" s="12"/>
+      <x:c r="Z123" s="12"/>
+      <x:c r="AA123" s="15"/>
+      <x:c r="AB123" s="15"/>
+      <x:c r="AC123" s="12"/>
+      <x:c r="AD123" s="12"/>
+      <x:c r="AE123" s="12"/>
+      <x:c r="AF123" s="12"/>
+      <x:c r="AG123" s="12"/>
+      <x:c r="AH123" s="12"/>
+      <x:c r="AI123" s="12"/>
+      <x:c r="AJ123" s="12"/>
+      <x:c r="AK123" s="16"/>
+      <x:c r="AL123" s="16"/>
+      <x:c r="AM123" s="12" t="str">
+        <x:v>WM47_Q355RE</x:v>
+      </x:c>
+      <x:c r="AN123" s="12" t="str">
+        <x:v>10.1007/s40195-022-01404-8</x:v>
+      </x:c>
+      <x:c r="AO123" s="12" t="str">
+        <x:v>https://doi.org/10.1007/s40195-022-01404-8</x:v>
+      </x:c>
+      <x:c r="AP123" s="12" t="str">
+        <x:v>Table1 PDF p2; Sec2.2; rust products Table3</x:v>
+      </x:c>
+      <x:c r="AQ123" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR123" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS123" s="12"/>
+      <x:c r="AT123" s="12"/>
+      <x:c r="AU123" s="12"/>
+      <x:c r="AV123" s="12"/>
+      <x:c r="AW123" s="12"/>
+      <x:c r="AX123" s="12"/>
+      <x:c r="AY123" s="12"/>
+      <x:c r="AZ123" s="12"/>
+      <x:c r="BA123" s="12"/>
+      <x:c r="BB123" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="BC123" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD123" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE123" s="12" t="str">
+        <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질; 전해질 농도(wt%); 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF123" s="12" t="str">
+        <x:v>Exact sample chemistry. Paper reports wet-dry mass loss and rust composition; no tabulated numerical icorr. Dash RE controls not analytical zero.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="40" customHeight="1">
+      <x:c r="A124" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B124" s="13" t="str">
+        <x:v>실험용 고강도 파이프라인강(H20B/H21/H22/H23+X100)</x:v>
+      </x:c>
+      <x:c r="C124" s="13" t="str">
+        <x:v>H20B</x:v>
+      </x:c>
+      <x:c r="D124" s="14" t="n">
+        <x:v>0.066</x:v>
+      </x:c>
+      <x:c r="E124" s="14" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="F124" s="14" t="n">
+        <x:v>1.78</x:v>
+      </x:c>
+      <x:c r="G124" s="14"/>
+      <x:c r="H124" s="14"/>
+      <x:c r="I124" s="14" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="J124" s="14" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="K124" s="14" t="n">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="L124" s="14" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="M124" s="14"/>
+      <x:c r="N124" s="14" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="O124" s="14" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="P124" s="14"/>
+      <x:c r="Q124" s="14"/>
+      <x:c r="R124" s="14"/>
+      <x:c r="S124" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T124" s="14"/>
+      <x:c r="U124" s="14"/>
+      <x:c r="V124" s="14"/>
+      <x:c r="W124" s="14"/>
+      <x:c r="X124" s="14"/>
+      <x:c r="Y124" s="12"/>
+      <x:c r="Z124" s="12"/>
+      <x:c r="AA124" s="15"/>
+      <x:c r="AB124" s="15"/>
+      <x:c r="AC124" s="12"/>
+      <x:c r="AD124" s="12" t="str">
+        <x:v>CO2_NaCl</x:v>
+      </x:c>
+      <x:c r="AE124" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF124" s="12" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AG124" s="12"/>
+      <x:c r="AH124" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AI124" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ124" s="12"/>
+      <x:c r="AK124" s="16" t="n">
+        <x:v>-0.709</x:v>
+      </x:c>
+      <x:c r="AL124" s="16"/>
+      <x:c r="AM124" s="12" t="str">
+        <x:v>WM19_H20B</x:v>
+      </x:c>
+      <x:c r="AN124" s="12" t="str">
+        <x:v>10.5006/C2024-20450</x:v>
+      </x:c>
+      <x:c r="AO124" s="12" t="str">
+        <x:v>https://netl.doe.gov/projects/VueConnection/download.aspx?filename=EffectofMinorCeAdditionsonCorrosionBehaviorofExperimentalPipelineSteel_030324.pdf&amp;id=ccdc6afc-4fb1-49ae-9c7c-737d0869e7c5</x:v>
+      </x:c>
+      <x:c r="AP124" s="12" t="str">
+        <x:v>NETL-hosted author conference manuscript Table1 pp2-3; Table3 p6; Fig3 p7</x:v>
+      </x:c>
+      <x:c r="AQ124" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR124" s="12" t="str">
+        <x:v>quarantined_printed_unit_conflict</x:v>
+      </x:c>
+      <x:c r="AS124" s="12" t="n">
+        <x:v>0.000018</x:v>
+      </x:c>
+      <x:c r="AT124" s="12" t="str">
+        <x:v>A/m2 (Table3 printed)</x:v>
+      </x:c>
+      <x:c r="AU124" s="12"/>
+      <x:c r="AV124" s="12"/>
+      <x:c r="AW124" s="12"/>
+      <x:c r="AX124" s="12"/>
+      <x:c r="AY124" s="12"/>
+      <x:c r="AZ124" s="12"/>
+      <x:c r="BA124" s="12"/>
+      <x:c r="BB124" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="BC124" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD124" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE124" s="12" t="str">
+        <x:v>P; S; T.N.(Total Nitrogen); Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 주사속도(mV/s); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF124" s="12" t="str">
+        <x:v>Table3 A/m2 conflicts current/derivedCR magnitudes; do not silently reinterpret as A/cm2. P/S/Ti combined column; B/N combined column: no individual values. Author draft has revision annotations; not final published table verification.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="40" customHeight="1">
+      <x:c r="A125" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B125" s="13" t="str">
+        <x:v>실험용 고강도 파이프라인강(H20B/H21/H22/H23+X100)</x:v>
+      </x:c>
+      <x:c r="C125" s="13" t="str">
+        <x:v>H21</x:v>
+      </x:c>
+      <x:c r="D125" s="14" t="n">
+        <x:v>0.056</x:v>
+      </x:c>
+      <x:c r="E125" s="14" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F125" s="14" t="n">
+        <x:v>1.77</x:v>
+      </x:c>
+      <x:c r="G125" s="14"/>
+      <x:c r="H125" s="14"/>
+      <x:c r="I125" s="14" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="J125" s="14" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="K125" s="14" t="n">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="L125" s="14" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="M125" s="14"/>
+      <x:c r="N125" s="14" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="O125" s="14" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="P125" s="14"/>
+      <x:c r="Q125" s="14"/>
+      <x:c r="R125" s="14"/>
+      <x:c r="S125" s="14" t="n">
+        <x:v>0.0057</x:v>
+      </x:c>
+      <x:c r="T125" s="14"/>
+      <x:c r="U125" s="14"/>
+      <x:c r="V125" s="14"/>
+      <x:c r="W125" s="14"/>
+      <x:c r="X125" s="14"/>
+      <x:c r="Y125" s="12"/>
+      <x:c r="Z125" s="12"/>
+      <x:c r="AA125" s="15"/>
+      <x:c r="AB125" s="15"/>
+      <x:c r="AC125" s="12"/>
+      <x:c r="AD125" s="12" t="str">
+        <x:v>CO2_NaCl</x:v>
+      </x:c>
+      <x:c r="AE125" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF125" s="12" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AG125" s="12"/>
+      <x:c r="AH125" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AI125" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ125" s="12"/>
+      <x:c r="AK125" s="16" t="n">
+        <x:v>-0.716</x:v>
+      </x:c>
+      <x:c r="AL125" s="16"/>
+      <x:c r="AM125" s="12" t="str">
+        <x:v>WM19_H21</x:v>
+      </x:c>
+      <x:c r="AN125" s="12" t="str">
+        <x:v>10.5006/C2024-20450</x:v>
+      </x:c>
+      <x:c r="AO125" s="12" t="str">
+        <x:v>https://netl.doe.gov/projects/VueConnection/download.aspx?filename=EffectofMinorCeAdditionsonCorrosionBehaviorofExperimentalPipelineSteel_030324.pdf&amp;id=ccdc6afc-4fb1-49ae-9c7c-737d0869e7c5</x:v>
+      </x:c>
+      <x:c r="AP125" s="12" t="str">
+        <x:v>NETL-hosted author conference manuscript Table1 pp2-3; Table3 p6; Fig3 p7</x:v>
+      </x:c>
+      <x:c r="AQ125" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR125" s="12" t="str">
+        <x:v>quarantined_printed_unit_conflict</x:v>
+      </x:c>
+      <x:c r="AS125" s="12" t="n">
+        <x:v>0.000023</x:v>
+      </x:c>
+      <x:c r="AT125" s="12" t="str">
+        <x:v>A/m2 (Table3 printed)</x:v>
+      </x:c>
+      <x:c r="AU125" s="12"/>
+      <x:c r="AV125" s="12"/>
+      <x:c r="AW125" s="12"/>
+      <x:c r="AX125" s="12"/>
+      <x:c r="AY125" s="12"/>
+      <x:c r="AZ125" s="12"/>
+      <x:c r="BA125" s="12"/>
+      <x:c r="BB125" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="BC125" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD125" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE125" s="12" t="str">
+        <x:v>P; S; T.N.(Total Nitrogen); Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 주사속도(mV/s); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF125" s="12" t="str">
+        <x:v>Table3 A/m2 conflicts current/derivedCR magnitudes; do not silently reinterpret as A/cm2. P/S/Ti combined column; B/N combined column: no individual values. Author draft has revision annotations; not final published table verification.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="40" customHeight="1">
+      <x:c r="A126" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B126" s="13" t="str">
+        <x:v>실험용 고강도 파이프라인강(H20B/H21/H22/H23+X100)</x:v>
+      </x:c>
+      <x:c r="C126" s="13" t="str">
+        <x:v>H22</x:v>
+      </x:c>
+      <x:c r="D126" s="14" t="n">
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="E126" s="14" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="F126" s="14" t="n">
+        <x:v>1.79</x:v>
+      </x:c>
+      <x:c r="G126" s="14"/>
+      <x:c r="H126" s="14"/>
+      <x:c r="I126" s="14" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="J126" s="14" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="K126" s="14" t="n">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="L126" s="14" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="M126" s="14"/>
+      <x:c r="N126" s="14" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="O126" s="14" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="P126" s="14"/>
+      <x:c r="Q126" s="14"/>
+      <x:c r="R126" s="14"/>
+      <x:c r="S126" s="14" t="n">
+        <x:v>0.0164</x:v>
+      </x:c>
+      <x:c r="T126" s="14"/>
+      <x:c r="U126" s="14"/>
+      <x:c r="V126" s="14"/>
+      <x:c r="W126" s="14"/>
+      <x:c r="X126" s="14"/>
+      <x:c r="Y126" s="12"/>
+      <x:c r="Z126" s="12"/>
+      <x:c r="AA126" s="15"/>
+      <x:c r="AB126" s="15"/>
+      <x:c r="AC126" s="12"/>
+      <x:c r="AD126" s="12" t="str">
+        <x:v>CO2_NaCl</x:v>
+      </x:c>
+      <x:c r="AE126" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF126" s="12" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AG126" s="12"/>
+      <x:c r="AH126" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AI126" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ126" s="12"/>
+      <x:c r="AK126" s="16" t="n">
+        <x:v>-0.723</x:v>
+      </x:c>
+      <x:c r="AL126" s="16"/>
+      <x:c r="AM126" s="12" t="str">
+        <x:v>WM19_H22</x:v>
+      </x:c>
+      <x:c r="AN126" s="12" t="str">
+        <x:v>10.5006/C2024-20450</x:v>
+      </x:c>
+      <x:c r="AO126" s="12" t="str">
+        <x:v>https://netl.doe.gov/projects/VueConnection/download.aspx?filename=EffectofMinorCeAdditionsonCorrosionBehaviorofExperimentalPipelineSteel_030324.pdf&amp;id=ccdc6afc-4fb1-49ae-9c7c-737d0869e7c5</x:v>
+      </x:c>
+      <x:c r="AP126" s="12" t="str">
+        <x:v>NETL-hosted author conference manuscript Table1 pp2-3; Table3 p6; Fig3 p7</x:v>
+      </x:c>
+      <x:c r="AQ126" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR126" s="12" t="str">
+        <x:v>quarantined_printed_unit_conflict</x:v>
+      </x:c>
+      <x:c r="AS126" s="12" t="n">
+        <x:v>0.000026</x:v>
+      </x:c>
+      <x:c r="AT126" s="12" t="str">
+        <x:v>A/m2 (Table3 printed)</x:v>
+      </x:c>
+      <x:c r="AU126" s="12"/>
+      <x:c r="AV126" s="12"/>
+      <x:c r="AW126" s="12"/>
+      <x:c r="AX126" s="12"/>
+      <x:c r="AY126" s="12"/>
+      <x:c r="AZ126" s="12"/>
+      <x:c r="BA126" s="12"/>
+      <x:c r="BB126" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="BC126" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD126" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE126" s="12" t="str">
+        <x:v>P; S; T.N.(Total Nitrogen); Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 주사속도(mV/s); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF126" s="12" t="str">
+        <x:v>Table3 A/m2 conflicts current/derivedCR magnitudes; do not silently reinterpret as A/cm2. P/S/Ti combined column; B/N combined column: no individual values. Author draft has revision annotations; not final published table verification.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="40" customHeight="1">
+      <x:c r="A127" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B127" s="13" t="str">
+        <x:v>실험용 고강도 파이프라인강(H20B/H21/H22/H23+X100)</x:v>
+      </x:c>
+      <x:c r="C127" s="13" t="str">
+        <x:v>H23</x:v>
+      </x:c>
+      <x:c r="D127" s="14" t="n">
+        <x:v>0.063</x:v>
+      </x:c>
+      <x:c r="E127" s="14" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="F127" s="14" t="n">
+        <x:v>1.82</x:v>
+      </x:c>
+      <x:c r="G127" s="14"/>
+      <x:c r="H127" s="14"/>
+      <x:c r="I127" s="14" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="J127" s="14" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="K127" s="14" t="n">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="L127" s="14" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="M127" s="14"/>
+      <x:c r="N127" s="14" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="O127" s="14" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="P127" s="14"/>
+      <x:c r="Q127" s="14"/>
+      <x:c r="R127" s="14"/>
+      <x:c r="S127" s="14" t="n">
+        <x:v>0.0263</x:v>
+      </x:c>
+      <x:c r="T127" s="14"/>
+      <x:c r="U127" s="14"/>
+      <x:c r="V127" s="14"/>
+      <x:c r="W127" s="14"/>
+      <x:c r="X127" s="14"/>
+      <x:c r="Y127" s="12"/>
+      <x:c r="Z127" s="12"/>
+      <x:c r="AA127" s="15"/>
+      <x:c r="AB127" s="15"/>
+      <x:c r="AC127" s="12"/>
+      <x:c r="AD127" s="12" t="str">
+        <x:v>CO2_NaCl</x:v>
+      </x:c>
+      <x:c r="AE127" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF127" s="12" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AG127" s="12"/>
+      <x:c r="AH127" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AI127" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ127" s="12"/>
+      <x:c r="AK127" s="16" t="n">
+        <x:v>-0.712</x:v>
+      </x:c>
+      <x:c r="AL127" s="16"/>
+      <x:c r="AM127" s="12" t="str">
+        <x:v>WM19_H23</x:v>
+      </x:c>
+      <x:c r="AN127" s="12" t="str">
+        <x:v>10.5006/C2024-20450</x:v>
+      </x:c>
+      <x:c r="AO127" s="12" t="str">
+        <x:v>https://netl.doe.gov/projects/VueConnection/download.aspx?filename=EffectofMinorCeAdditionsonCorrosionBehaviorofExperimentalPipelineSteel_030324.pdf&amp;id=ccdc6afc-4fb1-49ae-9c7c-737d0869e7c5</x:v>
+      </x:c>
+      <x:c r="AP127" s="12" t="str">
+        <x:v>NETL-hosted author conference manuscript Table1 pp2-3; Table3 p6; Fig3 p7</x:v>
+      </x:c>
+      <x:c r="AQ127" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR127" s="12" t="str">
+        <x:v>quarantined_printed_unit_conflict</x:v>
+      </x:c>
+      <x:c r="AS127" s="12" t="n">
+        <x:v>0.000039</x:v>
+      </x:c>
+      <x:c r="AT127" s="12" t="str">
+        <x:v>A/m2 (Table3 printed)</x:v>
+      </x:c>
+      <x:c r="AU127" s="12"/>
+      <x:c r="AV127" s="12"/>
+      <x:c r="AW127" s="12"/>
+      <x:c r="AX127" s="12"/>
+      <x:c r="AY127" s="12"/>
+      <x:c r="AZ127" s="12"/>
+      <x:c r="BA127" s="12"/>
+      <x:c r="BB127" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="BC127" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD127" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE127" s="12" t="str">
+        <x:v>P; S; T.N.(Total Nitrogen); Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 주사속도(mV/s); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF127" s="12" t="str">
+        <x:v>Table3 A/m2 conflicts current/derivedCR magnitudes; do not silently reinterpret as A/cm2. P/S/Ti combined column; B/N combined column: no individual values. Author draft has revision annotations; not final published table verification.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="40" customHeight="1">
+      <x:c r="A128" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B128" s="13" t="str">
+        <x:v>실험용 고강도 파이프라인강(H20B/H21/H22/H23+X100)</x:v>
+      </x:c>
+      <x:c r="C128" s="13" t="str">
+        <x:v>X100</x:v>
+      </x:c>
+      <x:c r="D128" s="14" t="n">
+        <x:v>0.085</x:v>
+      </x:c>
+      <x:c r="E128" s="14" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="F128" s="14" t="n">
+        <x:v>1.69</x:v>
+      </x:c>
+      <x:c r="G128" s="14"/>
+      <x:c r="H128" s="14"/>
+      <x:c r="I128" s="14" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="J128" s="14" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K128" s="14" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+      <x:c r="L128" s="14" t="n">
+        <x:v>0.14</x:v>
+      </x:c>
+      <x:c r="M128" s="14"/>
+      <x:c r="N128" s="14" t="n">
+        <x:v>0.047</x:v>
+      </x:c>
+      <x:c r="O128" s="14"/>
+      <x:c r="P128" s="14"/>
+      <x:c r="Q128" s="14"/>
+      <x:c r="R128" s="14"/>
+      <x:c r="S128" s="14"/>
+      <x:c r="T128" s="14"/>
+      <x:c r="U128" s="14"/>
+      <x:c r="V128" s="14"/>
+      <x:c r="W128" s="14"/>
+      <x:c r="X128" s="14"/>
+      <x:c r="Y128" s="12"/>
+      <x:c r="Z128" s="12"/>
+      <x:c r="AA128" s="15"/>
+      <x:c r="AB128" s="15"/>
+      <x:c r="AC128" s="12"/>
+      <x:c r="AD128" s="12" t="str">
+        <x:v>CO2_NaCl</x:v>
+      </x:c>
+      <x:c r="AE128" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF128" s="12" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AG128" s="12"/>
+      <x:c r="AH128" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AI128" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ128" s="12"/>
+      <x:c r="AK128" s="16" t="n">
+        <x:v>-0.724</x:v>
+      </x:c>
+      <x:c r="AL128" s="16"/>
+      <x:c r="AM128" s="12" t="str">
+        <x:v>WM19_X100</x:v>
+      </x:c>
+      <x:c r="AN128" s="12" t="str">
+        <x:v>10.5006/C2024-20450</x:v>
+      </x:c>
+      <x:c r="AO128" s="12" t="str">
+        <x:v>https://netl.doe.gov/projects/VueConnection/download.aspx?filename=EffectofMinorCeAdditionsonCorrosionBehaviorofExperimentalPipelineSteel_030324.pdf&amp;id=ccdc6afc-4fb1-49ae-9c7c-737d0869e7c5</x:v>
+      </x:c>
+      <x:c r="AP128" s="12" t="str">
+        <x:v>NETL-hosted author conference manuscript Table1 pp2-3; Table3 p6; Fig3 p7</x:v>
+      </x:c>
+      <x:c r="AQ128" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR128" s="12" t="str">
+        <x:v>quarantined_printed_unit_conflict</x:v>
+      </x:c>
+      <x:c r="AS128" s="12" t="n">
+        <x:v>0.0000535</x:v>
+      </x:c>
+      <x:c r="AT128" s="12" t="str">
+        <x:v>A/m2 (Table3 printed)</x:v>
+      </x:c>
+      <x:c r="AU128" s="12"/>
+      <x:c r="AV128" s="12"/>
+      <x:c r="AW128" s="12"/>
+      <x:c r="AX128" s="12"/>
+      <x:c r="AY128" s="12"/>
+      <x:c r="AZ128" s="12"/>
+      <x:c r="BA128" s="12"/>
+      <x:c r="BB128" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="BC128" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD128" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE128" s="12" t="str">
+        <x:v>P; S; T.N.(Total Nitrogen); V; Ti; Al; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 주사속도(mV/s); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF128" s="12" t="str">
+        <x:v>Table3 A/m2 conflicts current/derivedCR magnitudes; do not silently reinterpret as A/cm2. P/S/Ti combined column; B/N combined column: no individual values. Author draft has revision annotations; not final published table verification.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="40" customHeight="1">
+      <x:c r="A129" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B129" s="13" t="str">
+        <x:v>304형 스테인리스강(MnS vs CeS 개재물 비교)</x:v>
+      </x:c>
+      <x:c r="C129" s="13" t="str">
+        <x:v>MnS_A_NaCl</x:v>
+      </x:c>
+      <x:c r="D129" s="14" t="n">
+        <x:v>0.051</x:v>
+      </x:c>
+      <x:c r="E129" s="14" t="n">
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="F129" s="14" t="n">
+        <x:v>1.51</x:v>
+      </x:c>
+      <x:c r="G129" s="14" t="n">
+        <x:v>0.039</x:v>
+      </x:c>
+      <x:c r="H129" s="14" t="n">
+        <x:v>0.0215</x:v>
+      </x:c>
+      <x:c r="I129" s="14" t="n">
+        <x:v>18.3</x:v>
+      </x:c>
+      <x:c r="J129" s="14" t="n">
+        <x:v>8.27</x:v>
+      </x:c>
+      <x:c r="K129" s="14" t="n">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="L129" s="14" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="M129" s="14" t="n">
+        <x:v>0.0799</x:v>
+      </x:c>
+      <x:c r="N129" s="14"/>
+      <x:c r="O129" s="14"/>
+      <x:c r="P129" s="14"/>
+      <x:c r="Q129" s="14" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="R129" s="14"/>
+      <x:c r="S129" s="14"/>
+      <x:c r="T129" s="14"/>
+      <x:c r="U129" s="14"/>
+      <x:c r="V129" s="14"/>
+      <x:c r="W129" s="14"/>
+      <x:c r="X129" s="14"/>
+      <x:c r="Y129" s="12"/>
+      <x:c r="Z129" s="12" t="n">
+        <x:v>20.271400000000003</x:v>
+      </x:c>
+      <x:c r="AA129" s="15" t="n">
+        <x:v>1099.85</x:v>
+      </x:c>
+      <x:c r="AB129" s="15" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AC129" s="12" t="str">
+        <x:v>water</x:v>
+      </x:c>
+      <x:c r="AD129" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE129" s="12"/>
+      <x:c r="AF129" s="12"/>
+      <x:c r="AG129" s="12"/>
+      <x:c r="AH129" s="12"/>
+      <x:c r="AI129" s="12" t="str">
+        <x:v>AgAgCl_3.33M_KCl</x:v>
+      </x:c>
+      <x:c r="AJ129" s="12" t="n">
+        <x:v>0.383</x:v>
+      </x:c>
+      <x:c r="AK129" s="16"/>
+      <x:c r="AL129" s="16"/>
+      <x:c r="AM129" s="12" t="str">
+        <x:v>WM18_MnS_A_NaCl</x:v>
+      </x:c>
+      <x:c r="AN129" s="12" t="str">
+        <x:v>10.1149/2.0051714jes</x:v>
+      </x:c>
+      <x:c r="AO129" s="12" t="str">
+        <x:v>https://doi.org/10.1149/2.0051714jes</x:v>
+      </x:c>
+      <x:c r="AP129" s="12" t="str">
+        <x:v>Author CC-BY paper TableI pp1-2; micro-PDP methods p2</x:v>
+      </x:c>
+      <x:c r="AQ129" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR129" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS129" s="12"/>
+      <x:c r="AT129" s="12"/>
+      <x:c r="AU129" s="12" t="str">
+        <x:v>0.1 mol/L NaCl</x:v>
+      </x:c>
+      <x:c r="AV129" s="12"/>
+      <x:c r="AW129" s="12"/>
+      <x:c r="AX129" s="12"/>
+      <x:c r="AY129" s="12"/>
+      <x:c r="AZ129" s="12"/>
+      <x:c r="BA129" s="12"/>
+      <x:c r="BB129" s="12" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="BC129" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD129" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE129" s="12" t="str">
+        <x:v>Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF129" s="12" t="str">
+        <x:v>Microscopic anodic/pitting test, not reported Tafel icorr. B steel Mn&lt;.05/Mo&lt;.01/Cu&lt;.01/Al&lt;.005 remain unavailable numeric values. 1373K converted to1099.85C. A steel Ce dash means no addition, not measured zero. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="40" customHeight="1">
+      <x:c r="A130" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B130" s="13" t="str">
+        <x:v>304형 스테인리스강(MnS vs CeS 개재물 비교)</x:v>
+      </x:c>
+      <x:c r="C130" s="13" t="str">
+        <x:v>MnS_A_Na2SO4</x:v>
+      </x:c>
+      <x:c r="D130" s="14" t="n">
+        <x:v>0.051</x:v>
+      </x:c>
+      <x:c r="E130" s="14" t="n">
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="F130" s="14" t="n">
+        <x:v>1.51</x:v>
+      </x:c>
+      <x:c r="G130" s="14" t="n">
+        <x:v>0.039</x:v>
+      </x:c>
+      <x:c r="H130" s="14" t="n">
+        <x:v>0.0215</x:v>
+      </x:c>
+      <x:c r="I130" s="14" t="n">
+        <x:v>18.3</x:v>
+      </x:c>
+      <x:c r="J130" s="14" t="n">
+        <x:v>8.27</x:v>
+      </x:c>
+      <x:c r="K130" s="14" t="n">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="L130" s="14" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="M130" s="14" t="n">
+        <x:v>0.0799</x:v>
+      </x:c>
+      <x:c r="N130" s="14"/>
+      <x:c r="O130" s="14"/>
+      <x:c r="P130" s="14"/>
+      <x:c r="Q130" s="14" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="R130" s="14"/>
+      <x:c r="S130" s="14"/>
+      <x:c r="T130" s="14"/>
+      <x:c r="U130" s="14"/>
+      <x:c r="V130" s="14"/>
+      <x:c r="W130" s="14"/>
+      <x:c r="X130" s="14"/>
+      <x:c r="Y130" s="12"/>
+      <x:c r="Z130" s="12" t="n">
+        <x:v>20.271400000000003</x:v>
+      </x:c>
+      <x:c r="AA130" s="15" t="n">
+        <x:v>1099.85</x:v>
+      </x:c>
+      <x:c r="AB130" s="15" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AC130" s="12" t="str">
+        <x:v>water</x:v>
+      </x:c>
+      <x:c r="AD130" s="12" t="str">
+        <x:v>Na2SO4</x:v>
+      </x:c>
+      <x:c r="AE130" s="12"/>
+      <x:c r="AF130" s="12"/>
+      <x:c r="AG130" s="12"/>
+      <x:c r="AH130" s="12"/>
+      <x:c r="AI130" s="12" t="str">
+        <x:v>AgAgCl_3.33M_KCl</x:v>
+      </x:c>
+      <x:c r="AJ130" s="12" t="n">
+        <x:v>0.383</x:v>
+      </x:c>
+      <x:c r="AK130" s="16"/>
+      <x:c r="AL130" s="16"/>
+      <x:c r="AM130" s="12" t="str">
+        <x:v>WM18_MnS_A_Na2SO4</x:v>
+      </x:c>
+      <x:c r="AN130" s="12" t="str">
+        <x:v>10.1149/2.0051714jes</x:v>
+      </x:c>
+      <x:c r="AO130" s="12" t="str">
+        <x:v>https://doi.org/10.1149/2.0051714jes</x:v>
+      </x:c>
+      <x:c r="AP130" s="12" t="str">
+        <x:v>Author CC-BY paper TableI pp1-2; micro-PDP methods p2</x:v>
+      </x:c>
+      <x:c r="AQ130" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR130" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS130" s="12"/>
+      <x:c r="AT130" s="12"/>
+      <x:c r="AU130" s="12" t="str">
+        <x:v>0.1 mol/L Na2SO4</x:v>
+      </x:c>
+      <x:c r="AV130" s="12"/>
+      <x:c r="AW130" s="12"/>
+      <x:c r="AX130" s="12"/>
+      <x:c r="AY130" s="12"/>
+      <x:c r="AZ130" s="12"/>
+      <x:c r="BA130" s="12"/>
+      <x:c r="BB130" s="12" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="BC130" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD130" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE130" s="12" t="str">
+        <x:v>Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF130" s="12" t="str">
+        <x:v>Microscopic anodic/pitting test, not reported Tafel icorr. B steel Mn&lt;.05/Mo&lt;.01/Cu&lt;.01/Al&lt;.005 remain unavailable numeric values. 1373K converted to1099.85C. A steel Ce dash means no addition, not measured zero. PREN calculated as Cr+3.3Mo+16N; not a measurement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="40" customHeight="1">
+      <x:c r="A131" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B131" s="13" t="str">
+        <x:v>304형 스테인리스강(MnS vs CeS 개재물 비교)</x:v>
+      </x:c>
+      <x:c r="C131" s="13" t="str">
+        <x:v>CeS_B_NaCl</x:v>
+      </x:c>
+      <x:c r="D131" s="14" t="n">
+        <x:v>0.011</x:v>
+      </x:c>
+      <x:c r="E131" s="14" t="n">
+        <x:v>0.47</x:v>
+      </x:c>
+      <x:c r="F131" s="14"/>
+      <x:c r="G131" s="14" t="n">
+        <x:v>0.033</x:v>
+      </x:c>
+      <x:c r="H131" s="14" t="n">
+        <x:v>0.017</x:v>
+      </x:c>
+      <x:c r="I131" s="14" t="n">
+        <x:v>17.9</x:v>
+      </x:c>
+      <x:c r="J131" s="14" t="n">
+        <x:v>9.41</x:v>
+      </x:c>
+      <x:c r="K131" s="14"/>
+      <x:c r="L131" s="14"/>
+      <x:c r="M131" s="14" t="n">
+        <x:v>0.0039</x:v>
+      </x:c>
+      <x:c r="N131" s="14"/>
+      <x:c r="O131" s="14"/>
+      <x:c r="P131" s="14"/>
+      <x:c r="Q131" s="14"/>
+      <x:c r="R131" s="14"/>
+      <x:c r="S131" s="14" t="n">
+        <x:v>0.091</x:v>
+      </x:c>
+      <x:c r="T131" s="14"/>
+      <x:c r="U131" s="14"/>
+      <x:c r="V131" s="14"/>
+      <x:c r="W131" s="14"/>
+      <x:c r="X131" s="14"/>
+      <x:c r="Y131" s="12"/>
+      <x:c r="Z131" s="12"/>
+      <x:c r="AA131" s="15" t="n">
+        <x:v>1099.85</x:v>
+      </x:c>
+      <x:c r="AB131" s="15" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AC131" s="12" t="str">
+        <x:v>water</x:v>
+      </x:c>
+      <x:c r="AD131" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE131" s="12"/>
+      <x:c r="AF131" s="12"/>
+      <x:c r="AG131" s="12"/>
+      <x:c r="AH131" s="12"/>
+      <x:c r="AI131" s="12" t="str">
+        <x:v>AgAgCl_3.33M_KCl</x:v>
+      </x:c>
+      <x:c r="AJ131" s="12" t="n">
+        <x:v>0.383</x:v>
+      </x:c>
+      <x:c r="AK131" s="16"/>
+      <x:c r="AL131" s="16"/>
+      <x:c r="AM131" s="12" t="str">
+        <x:v>WM18_CeS_B_NaCl</x:v>
+      </x:c>
+      <x:c r="AN131" s="12" t="str">
+        <x:v>10.1149/2.0051714jes</x:v>
+      </x:c>
+      <x:c r="AO131" s="12" t="str">
+        <x:v>https://doi.org/10.1149/2.0051714jes</x:v>
+      </x:c>
+      <x:c r="AP131" s="12" t="str">
+        <x:v>Author CC-BY paper TableI pp1-2; micro-PDP methods p2</x:v>
+      </x:c>
+      <x:c r="AQ131" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR131" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS131" s="12"/>
+      <x:c r="AT131" s="12"/>
+      <x:c r="AU131" s="12" t="str">
+        <x:v>0.1 mol/L NaCl</x:v>
+      </x:c>
+      <x:c r="AV131" s="12"/>
+      <x:c r="AW131" s="12"/>
+      <x:c r="AX131" s="12"/>
+      <x:c r="AY131" s="12"/>
+      <x:c r="AZ131" s="12"/>
+      <x:c r="BA131" s="12"/>
+      <x:c r="BB131" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="BC131" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD131" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE131" s="12" t="str">
+        <x:v>Mn; Mo; Cu; Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF131" s="12" t="str">
+        <x:v>Microscopic anodic/pitting test, not reported Tafel icorr. B steel Mn&lt;.05/Mo&lt;.01/Cu&lt;.01/Al&lt;.005 remain unavailable numeric values. 1373K converted to1099.85C. A steel Ce dash means no addition, not measured zero.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="40" customHeight="1">
+      <x:c r="A132" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B132" s="13" t="str">
+        <x:v>304형 스테인리스강(MnS vs CeS 개재물 비교)</x:v>
+      </x:c>
+      <x:c r="C132" s="13" t="str">
+        <x:v>CeS_B_Na2SO4</x:v>
+      </x:c>
+      <x:c r="D132" s="14" t="n">
+        <x:v>0.011</x:v>
+      </x:c>
+      <x:c r="E132" s="14" t="n">
+        <x:v>0.47</x:v>
+      </x:c>
+      <x:c r="F132" s="14"/>
+      <x:c r="G132" s="14" t="n">
+        <x:v>0.033</x:v>
+      </x:c>
+      <x:c r="H132" s="14" t="n">
+        <x:v>0.017</x:v>
+      </x:c>
+      <x:c r="I132" s="14" t="n">
+        <x:v>17.9</x:v>
+      </x:c>
+      <x:c r="J132" s="14" t="n">
+        <x:v>9.41</x:v>
+      </x:c>
+      <x:c r="K132" s="14"/>
+      <x:c r="L132" s="14"/>
+      <x:c r="M132" s="14" t="n">
+        <x:v>0.0039</x:v>
+      </x:c>
+      <x:c r="N132" s="14"/>
+      <x:c r="O132" s="14"/>
+      <x:c r="P132" s="14"/>
+      <x:c r="Q132" s="14"/>
+      <x:c r="R132" s="14"/>
+      <x:c r="S132" s="14" t="n">
+        <x:v>0.091</x:v>
+      </x:c>
+      <x:c r="T132" s="14"/>
+      <x:c r="U132" s="14"/>
+      <x:c r="V132" s="14"/>
+      <x:c r="W132" s="14"/>
+      <x:c r="X132" s="14"/>
+      <x:c r="Y132" s="12"/>
+      <x:c r="Z132" s="12"/>
+      <x:c r="AA132" s="15" t="n">
+        <x:v>1099.85</x:v>
+      </x:c>
+      <x:c r="AB132" s="15" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AC132" s="12" t="str">
+        <x:v>water</x:v>
+      </x:c>
+      <x:c r="AD132" s="12" t="str">
+        <x:v>Na2SO4</x:v>
+      </x:c>
+      <x:c r="AE132" s="12"/>
+      <x:c r="AF132" s="12"/>
+      <x:c r="AG132" s="12"/>
+      <x:c r="AH132" s="12"/>
+      <x:c r="AI132" s="12" t="str">
+        <x:v>AgAgCl_3.33M_KCl</x:v>
+      </x:c>
+      <x:c r="AJ132" s="12" t="n">
+        <x:v>0.383</x:v>
+      </x:c>
+      <x:c r="AK132" s="16"/>
+      <x:c r="AL132" s="16"/>
+      <x:c r="AM132" s="12" t="str">
+        <x:v>WM18_CeS_B_Na2SO4</x:v>
+      </x:c>
+      <x:c r="AN132" s="12" t="str">
+        <x:v>10.1149/2.0051714jes</x:v>
+      </x:c>
+      <x:c r="AO132" s="12" t="str">
+        <x:v>https://doi.org/10.1149/2.0051714jes</x:v>
+      </x:c>
+      <x:c r="AP132" s="12" t="str">
+        <x:v>Author CC-BY paper TableI pp1-2; micro-PDP methods p2</x:v>
+      </x:c>
+      <x:c r="AQ132" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR132" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS132" s="12"/>
+      <x:c r="AT132" s="12"/>
+      <x:c r="AU132" s="12" t="str">
+        <x:v>0.1 mol/L Na2SO4</x:v>
+      </x:c>
+      <x:c r="AV132" s="12"/>
+      <x:c r="AW132" s="12"/>
+      <x:c r="AX132" s="12"/>
+      <x:c r="AY132" s="12"/>
+      <x:c r="AZ132" s="12"/>
+      <x:c r="BA132" s="12"/>
+      <x:c r="BB132" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="BC132" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD132" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE132" s="12" t="str">
+        <x:v>Mn; Mo; Cu; Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 전해질 농도(wt%); 침지시간(min); 온도(°C); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF132" s="12" t="str">
+        <x:v>Microscopic anodic/pitting test, not reported Tafel icorr. B steel Mn&lt;.05/Mo&lt;.01/Cu&lt;.01/Al&lt;.005 remain unavailable numeric values. 1373K converted to1099.85C. A steel Ce dash means no addition, not measured zero.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="40" customHeight="1">
+      <x:c r="A133" s="12" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B133" s="13" t="str">
+        <x:v>OC404 페라이트계 스테인리스강(20Cr-5Al-0.02C) + 전착 Ce2O3/CeO2 막</x:v>
+      </x:c>
+      <x:c r="C133" s="13" t="str">
+        <x:v>surfaceCe0_as_deposited</x:v>
+      </x:c>
+      <x:c r="D133" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="E133" s="14"/>
+      <x:c r="F133" s="14"/>
+      <x:c r="G133" s="14"/>
+      <x:c r="H133" s="14"/>
+      <x:c r="I133" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J133" s="14"/>
+      <x:c r="K133" s="14"/>
+      <x:c r="L133" s="14"/>
+      <x:c r="M133" s="14"/>
+      <x:c r="N133" s="14"/>
+      <x:c r="O133" s="14"/>
+      <x:c r="P133" s="14"/>
+      <x:c r="Q133" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R133" s="14"/>
+      <x:c r="S133" s="14"/>
+      <x:c r="T133" s="14"/>
+      <x:c r="U133" s="14"/>
+      <x:c r="V133" s="14"/>
+      <x:c r="W133" s="14"/>
+      <x:c r="X133" s="14"/>
+      <x:c r="Y133" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z133" s="12"/>
+      <x:c r="AA133" s="15"/>
+      <x:c r="AB133" s="15"/>
+      <x:c r="AC133" s="12"/>
+      <x:c r="AD133" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE133" s="12"/>
+      <x:c r="AF133" s="12"/>
+      <x:c r="AG133" s="12"/>
+      <x:c r="AH133" s="12"/>
+      <x:c r="AI133" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ133" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AK133" s="16" t="n">
+        <x:v>-0.172</x:v>
+      </x:c>
+      <x:c r="AL133" s="16" t="n">
+        <x:v>6e-7</x:v>
+      </x:c>
+      <x:c r="AM133" s="12" t="str">
+        <x:v>WM42_surfaceCe0_as_deposited</x:v>
+      </x:c>
+      <x:c r="AN133" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO133" s="12" t="str">
+        <x:v>https://bcc.bas.bg/BCC_Volumes/Volume_43_Number_1_2011/Volume_43_Number_1_2011_PDF/2011-43-1_24.pdf</x:v>
+      </x:c>
+      <x:c r="AP133" s="12" t="str">
+        <x:v>Publisher PDF methods pp1-2; Tables1/2 p2</x:v>
+      </x:c>
+      <x:c r="AQ133" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR133" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS133" s="12" t="n">
+        <x:v>6e-7</x:v>
+      </x:c>
+      <x:c r="AT133" s="12" t="str">
+        <x:v>A/cm2</x:v>
+      </x:c>
+      <x:c r="AU133" s="12" t="str">
+        <x:v>3.5% NaCl; percentage basis not reassigned</x:v>
+      </x:c>
+      <x:c r="AV133" s="12"/>
+      <x:c r="AW133" s="12"/>
+      <x:c r="AX133" s="12"/>
+      <x:c r="AY133" s="12"/>
+      <x:c r="AZ133" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA133" s="12"/>
+      <x:c r="BB133" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="BC133" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD133" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE133" s="12" t="str">
+        <x:v>Si; Mn; P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF133" s="12" t="str">
+        <x:v>OC404 substrate composition only. Surface oxide Ce atomic percent is not bulk Ce wt%. Room-temperature PDP not forced to25C. Thermal treatment performed in air; cooling route unreported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="40" customHeight="1">
+      <x:c r="A134" s="12" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B134" s="13" t="str">
+        <x:v>OC404 페라이트계 스테인리스강(20Cr-5Al-0.02C) + 전착 Ce2O3/CeO2 막</x:v>
+      </x:c>
+      <x:c r="C134" s="13" t="str">
+        <x:v>surfaceCe3.6_as_deposited</x:v>
+      </x:c>
+      <x:c r="D134" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="E134" s="14"/>
+      <x:c r="F134" s="14"/>
+      <x:c r="G134" s="14"/>
+      <x:c r="H134" s="14"/>
+      <x:c r="I134" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J134" s="14"/>
+      <x:c r="K134" s="14"/>
+      <x:c r="L134" s="14"/>
+      <x:c r="M134" s="14"/>
+      <x:c r="N134" s="14"/>
+      <x:c r="O134" s="14"/>
+      <x:c r="P134" s="14"/>
+      <x:c r="Q134" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R134" s="14"/>
+      <x:c r="S134" s="14"/>
+      <x:c r="T134" s="14"/>
+      <x:c r="U134" s="14"/>
+      <x:c r="V134" s="14"/>
+      <x:c r="W134" s="14"/>
+      <x:c r="X134" s="14"/>
+      <x:c r="Y134" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z134" s="12"/>
+      <x:c r="AA134" s="15"/>
+      <x:c r="AB134" s="15"/>
+      <x:c r="AC134" s="12"/>
+      <x:c r="AD134" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE134" s="12"/>
+      <x:c r="AF134" s="12"/>
+      <x:c r="AG134" s="12"/>
+      <x:c r="AH134" s="12"/>
+      <x:c r="AI134" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ134" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AK134" s="16" t="n">
+        <x:v>-0.168</x:v>
+      </x:c>
+      <x:c r="AL134" s="16" t="n">
+        <x:v>5.1e-7</x:v>
+      </x:c>
+      <x:c r="AM134" s="12" t="str">
+        <x:v>WM42_surfaceCe3.6_as_deposited</x:v>
+      </x:c>
+      <x:c r="AN134" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO134" s="12" t="str">
+        <x:v>https://bcc.bas.bg/BCC_Volumes/Volume_43_Number_1_2011/Volume_43_Number_1_2011_PDF/2011-43-1_24.pdf</x:v>
+      </x:c>
+      <x:c r="AP134" s="12" t="str">
+        <x:v>Publisher PDF methods pp1-2; Tables1/2 p2</x:v>
+      </x:c>
+      <x:c r="AQ134" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR134" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS134" s="12" t="n">
+        <x:v>5.1e-7</x:v>
+      </x:c>
+      <x:c r="AT134" s="12" t="str">
+        <x:v>A/cm2</x:v>
+      </x:c>
+      <x:c r="AU134" s="12" t="str">
+        <x:v>3.5% NaCl; percentage basis not reassigned</x:v>
+      </x:c>
+      <x:c r="AV134" s="12"/>
+      <x:c r="AW134" s="12"/>
+      <x:c r="AX134" s="12"/>
+      <x:c r="AY134" s="12"/>
+      <x:c r="AZ134" s="12" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="BA134" s="12"/>
+      <x:c r="BB134" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="BC134" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD134" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE134" s="12" t="str">
+        <x:v>Si; Mn; P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF134" s="12" t="str">
+        <x:v>OC404 substrate composition only. Surface oxide Ce atomic percent is not bulk Ce wt%. Room-temperature PDP not forced to25C. Thermal treatment performed in air; cooling route unreported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="40" customHeight="1">
+      <x:c r="A135" s="12" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B135" s="13" t="str">
+        <x:v>OC404 페라이트계 스테인리스강(20Cr-5Al-0.02C) + 전착 Ce2O3/CeO2 막</x:v>
+      </x:c>
+      <x:c r="C135" s="13" t="str">
+        <x:v>surfaceCe13.1_as_deposited</x:v>
+      </x:c>
+      <x:c r="D135" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="E135" s="14"/>
+      <x:c r="F135" s="14"/>
+      <x:c r="G135" s="14"/>
+      <x:c r="H135" s="14"/>
+      <x:c r="I135" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J135" s="14"/>
+      <x:c r="K135" s="14"/>
+      <x:c r="L135" s="14"/>
+      <x:c r="M135" s="14"/>
+      <x:c r="N135" s="14"/>
+      <x:c r="O135" s="14"/>
+      <x:c r="P135" s="14"/>
+      <x:c r="Q135" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R135" s="14"/>
+      <x:c r="S135" s="14"/>
+      <x:c r="T135" s="14"/>
+      <x:c r="U135" s="14"/>
+      <x:c r="V135" s="14"/>
+      <x:c r="W135" s="14"/>
+      <x:c r="X135" s="14"/>
+      <x:c r="Y135" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z135" s="12"/>
+      <x:c r="AA135" s="15"/>
+      <x:c r="AB135" s="15"/>
+      <x:c r="AC135" s="12"/>
+      <x:c r="AD135" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE135" s="12"/>
+      <x:c r="AF135" s="12"/>
+      <x:c r="AG135" s="12"/>
+      <x:c r="AH135" s="12"/>
+      <x:c r="AI135" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ135" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AK135" s="16" t="n">
+        <x:v>-0.163</x:v>
+      </x:c>
+      <x:c r="AL135" s="16" t="n">
+        <x:v>3e-7</x:v>
+      </x:c>
+      <x:c r="AM135" s="12" t="str">
+        <x:v>WM42_surfaceCe13.1_as_deposited</x:v>
+      </x:c>
+      <x:c r="AN135" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO135" s="12" t="str">
+        <x:v>https://bcc.bas.bg/BCC_Volumes/Volume_43_Number_1_2011/Volume_43_Number_1_2011_PDF/2011-43-1_24.pdf</x:v>
+      </x:c>
+      <x:c r="AP135" s="12" t="str">
+        <x:v>Publisher PDF methods pp1-2; Tables1/2 p2</x:v>
+      </x:c>
+      <x:c r="AQ135" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR135" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS135" s="12" t="n">
+        <x:v>3e-7</x:v>
+      </x:c>
+      <x:c r="AT135" s="12" t="str">
+        <x:v>A/cm2</x:v>
+      </x:c>
+      <x:c r="AU135" s="12" t="str">
+        <x:v>3.5% NaCl; percentage basis not reassigned</x:v>
+      </x:c>
+      <x:c r="AV135" s="12"/>
+      <x:c r="AW135" s="12"/>
+      <x:c r="AX135" s="12"/>
+      <x:c r="AY135" s="12"/>
+      <x:c r="AZ135" s="12" t="n">
+        <x:v>13.1</x:v>
+      </x:c>
+      <x:c r="BA135" s="12"/>
+      <x:c r="BB135" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="BC135" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD135" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE135" s="12" t="str">
+        <x:v>Si; Mn; P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF135" s="12" t="str">
+        <x:v>OC404 substrate composition only. Surface oxide Ce atomic percent is not bulk Ce wt%. Room-temperature PDP not forced to25C. Thermal treatment performed in air; cooling route unreported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="40" customHeight="1">
+      <x:c r="A136" s="12" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B136" s="13" t="str">
+        <x:v>OC404 페라이트계 스테인리스강(20Cr-5Al-0.02C) + 전착 Ce2O3/CeO2 막</x:v>
+      </x:c>
+      <x:c r="C136" s="13" t="str">
+        <x:v>surfaceCe25.7_as_deposited</x:v>
+      </x:c>
+      <x:c r="D136" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="E136" s="14"/>
+      <x:c r="F136" s="14"/>
+      <x:c r="G136" s="14"/>
+      <x:c r="H136" s="14"/>
+      <x:c r="I136" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J136" s="14"/>
+      <x:c r="K136" s="14"/>
+      <x:c r="L136" s="14"/>
+      <x:c r="M136" s="14"/>
+      <x:c r="N136" s="14"/>
+      <x:c r="O136" s="14"/>
+      <x:c r="P136" s="14"/>
+      <x:c r="Q136" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R136" s="14"/>
+      <x:c r="S136" s="14"/>
+      <x:c r="T136" s="14"/>
+      <x:c r="U136" s="14"/>
+      <x:c r="V136" s="14"/>
+      <x:c r="W136" s="14"/>
+      <x:c r="X136" s="14"/>
+      <x:c r="Y136" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z136" s="12"/>
+      <x:c r="AA136" s="15"/>
+      <x:c r="AB136" s="15"/>
+      <x:c r="AC136" s="12"/>
+      <x:c r="AD136" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE136" s="12"/>
+      <x:c r="AF136" s="12"/>
+      <x:c r="AG136" s="12"/>
+      <x:c r="AH136" s="12"/>
+      <x:c r="AI136" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ136" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AK136" s="16" t="n">
+        <x:v>-0.056</x:v>
+      </x:c>
+      <x:c r="AL136" s="16" t="n">
+        <x:v>6.9e-8</x:v>
+      </x:c>
+      <x:c r="AM136" s="12" t="str">
+        <x:v>WM42_surfaceCe25.7_as_deposited</x:v>
+      </x:c>
+      <x:c r="AN136" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO136" s="12" t="str">
+        <x:v>https://bcc.bas.bg/BCC_Volumes/Volume_43_Number_1_2011/Volume_43_Number_1_2011_PDF/2011-43-1_24.pdf</x:v>
+      </x:c>
+      <x:c r="AP136" s="12" t="str">
+        <x:v>Publisher PDF methods pp1-2; Tables1/2 p2</x:v>
+      </x:c>
+      <x:c r="AQ136" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR136" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS136" s="12" t="n">
+        <x:v>6.9e-8</x:v>
+      </x:c>
+      <x:c r="AT136" s="12" t="str">
+        <x:v>A/cm2</x:v>
+      </x:c>
+      <x:c r="AU136" s="12" t="str">
+        <x:v>3.5% NaCl; percentage basis not reassigned</x:v>
+      </x:c>
+      <x:c r="AV136" s="12"/>
+      <x:c r="AW136" s="12"/>
+      <x:c r="AX136" s="12"/>
+      <x:c r="AY136" s="12"/>
+      <x:c r="AZ136" s="12" t="n">
+        <x:v>25.7</x:v>
+      </x:c>
+      <x:c r="BA136" s="12"/>
+      <x:c r="BB136" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="BC136" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD136" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE136" s="12" t="str">
+        <x:v>Si; Mn; P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF136" s="12" t="str">
+        <x:v>OC404 substrate composition only. Surface oxide Ce atomic percent is not bulk Ce wt%. Room-temperature PDP not forced to25C. Thermal treatment performed in air; cooling route unreported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="40" customHeight="1">
+      <x:c r="A137" s="12" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B137" s="13" t="str">
+        <x:v>OC404 페라이트계 스테인리스강(20Cr-5Al-0.02C) + 전착 Ce2O3/CeO2 막</x:v>
+      </x:c>
+      <x:c r="C137" s="13" t="str">
+        <x:v>surfaceCe0_450C</x:v>
+      </x:c>
+      <x:c r="D137" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="E137" s="14"/>
+      <x:c r="F137" s="14"/>
+      <x:c r="G137" s="14"/>
+      <x:c r="H137" s="14"/>
+      <x:c r="I137" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J137" s="14"/>
+      <x:c r="K137" s="14"/>
+      <x:c r="L137" s="14"/>
+      <x:c r="M137" s="14"/>
+      <x:c r="N137" s="14"/>
+      <x:c r="O137" s="14"/>
+      <x:c r="P137" s="14"/>
+      <x:c r="Q137" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R137" s="14"/>
+      <x:c r="S137" s="14"/>
+      <x:c r="T137" s="14"/>
+      <x:c r="U137" s="14"/>
+      <x:c r="V137" s="14"/>
+      <x:c r="W137" s="14"/>
+      <x:c r="X137" s="14"/>
+      <x:c r="Y137" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z137" s="12"/>
+      <x:c r="AA137" s="15" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="AB137" s="15" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AC137" s="12"/>
+      <x:c r="AD137" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE137" s="12"/>
+      <x:c r="AF137" s="12"/>
+      <x:c r="AG137" s="12"/>
+      <x:c r="AH137" s="12"/>
+      <x:c r="AI137" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ137" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AK137" s="16" t="n">
+        <x:v>-1.083</x:v>
+      </x:c>
+      <x:c r="AL137" s="16" t="n">
+        <x:v>0.0000046</x:v>
+      </x:c>
+      <x:c r="AM137" s="12" t="str">
+        <x:v>WM42_surfaceCe0_450C</x:v>
+      </x:c>
+      <x:c r="AN137" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO137" s="12" t="str">
+        <x:v>https://bcc.bas.bg/BCC_Volumes/Volume_43_Number_1_2011/Volume_43_Number_1_2011_PDF/2011-43-1_24.pdf</x:v>
+      </x:c>
+      <x:c r="AP137" s="12" t="str">
+        <x:v>Publisher PDF methods pp1-2; Tables1/2 p2</x:v>
+      </x:c>
+      <x:c r="AQ137" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR137" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS137" s="12" t="n">
+        <x:v>0.0000046</x:v>
+      </x:c>
+      <x:c r="AT137" s="12" t="str">
+        <x:v>A/cm2</x:v>
+      </x:c>
+      <x:c r="AU137" s="12" t="str">
+        <x:v>3.5% NaCl; percentage basis not reassigned</x:v>
+      </x:c>
+      <x:c r="AV137" s="12"/>
+      <x:c r="AW137" s="12"/>
+      <x:c r="AX137" s="12"/>
+      <x:c r="AY137" s="12"/>
+      <x:c r="AZ137" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA137" s="12"/>
+      <x:c r="BB137" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="BC137" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD137" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE137" s="12" t="str">
+        <x:v>Si; Mn; P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF137" s="12" t="str">
+        <x:v>OC404 substrate composition only. Surface oxide Ce atomic percent is not bulk Ce wt%. Room-temperature PDP not forced to25C. Thermal treatment performed in air; cooling route unreported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="40" customHeight="1">
+      <x:c r="A138" s="12" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B138" s="13" t="str">
+        <x:v>OC404 페라이트계 스테인리스강(20Cr-5Al-0.02C) + 전착 Ce2O3/CeO2 막</x:v>
+      </x:c>
+      <x:c r="C138" s="13" t="str">
+        <x:v>surfaceCe4.2_450C</x:v>
+      </x:c>
+      <x:c r="D138" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="E138" s="14"/>
+      <x:c r="F138" s="14"/>
+      <x:c r="G138" s="14"/>
+      <x:c r="H138" s="14"/>
+      <x:c r="I138" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J138" s="14"/>
+      <x:c r="K138" s="14"/>
+      <x:c r="L138" s="14"/>
+      <x:c r="M138" s="14"/>
+      <x:c r="N138" s="14"/>
+      <x:c r="O138" s="14"/>
+      <x:c r="P138" s="14"/>
+      <x:c r="Q138" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R138" s="14"/>
+      <x:c r="S138" s="14"/>
+      <x:c r="T138" s="14"/>
+      <x:c r="U138" s="14"/>
+      <x:c r="V138" s="14"/>
+      <x:c r="W138" s="14"/>
+      <x:c r="X138" s="14"/>
+      <x:c r="Y138" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z138" s="12"/>
+      <x:c r="AA138" s="15" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="AB138" s="15" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AC138" s="12"/>
+      <x:c r="AD138" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE138" s="12"/>
+      <x:c r="AF138" s="12"/>
+      <x:c r="AG138" s="12"/>
+      <x:c r="AH138" s="12"/>
+      <x:c r="AI138" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ138" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AK138" s="16" t="n">
+        <x:v>-0.3</x:v>
+      </x:c>
+      <x:c r="AL138" s="16" t="n">
+        <x:v>5.1e-7</x:v>
+      </x:c>
+      <x:c r="AM138" s="12" t="str">
+        <x:v>WM42_surfaceCe4.2_450C</x:v>
+      </x:c>
+      <x:c r="AN138" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO138" s="12" t="str">
+        <x:v>https://bcc.bas.bg/BCC_Volumes/Volume_43_Number_1_2011/Volume_43_Number_1_2011_PDF/2011-43-1_24.pdf</x:v>
+      </x:c>
+      <x:c r="AP138" s="12" t="str">
+        <x:v>Publisher PDF methods pp1-2; Tables1/2 p2</x:v>
+      </x:c>
+      <x:c r="AQ138" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR138" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS138" s="12" t="n">
+        <x:v>5.1e-7</x:v>
+      </x:c>
+      <x:c r="AT138" s="12" t="str">
+        <x:v>A/cm2</x:v>
+      </x:c>
+      <x:c r="AU138" s="12" t="str">
+        <x:v>3.5% NaCl; percentage basis not reassigned</x:v>
+      </x:c>
+      <x:c r="AV138" s="12"/>
+      <x:c r="AW138" s="12"/>
+      <x:c r="AX138" s="12"/>
+      <x:c r="AY138" s="12"/>
+      <x:c r="AZ138" s="12" t="n">
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="BA138" s="12"/>
+      <x:c r="BB138" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="BC138" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD138" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE138" s="12" t="str">
+        <x:v>Si; Mn; P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF138" s="12" t="str">
+        <x:v>OC404 substrate composition only. Surface oxide Ce atomic percent is not bulk Ce wt%. Room-temperature PDP not forced to25C. Thermal treatment performed in air; cooling route unreported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="40" customHeight="1">
+      <x:c r="A139" s="12" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B139" s="13" t="str">
+        <x:v>OC404 페라이트계 스테인리스강(20Cr-5Al-0.02C) + 전착 Ce2O3/CeO2 막</x:v>
+      </x:c>
+      <x:c r="C139" s="13" t="str">
+        <x:v>surfaceCe11.2_450C</x:v>
+      </x:c>
+      <x:c r="D139" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="E139" s="14"/>
+      <x:c r="F139" s="14"/>
+      <x:c r="G139" s="14"/>
+      <x:c r="H139" s="14"/>
+      <x:c r="I139" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J139" s="14"/>
+      <x:c r="K139" s="14"/>
+      <x:c r="L139" s="14"/>
+      <x:c r="M139" s="14"/>
+      <x:c r="N139" s="14"/>
+      <x:c r="O139" s="14"/>
+      <x:c r="P139" s="14"/>
+      <x:c r="Q139" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R139" s="14"/>
+      <x:c r="S139" s="14"/>
+      <x:c r="T139" s="14"/>
+      <x:c r="U139" s="14"/>
+      <x:c r="V139" s="14"/>
+      <x:c r="W139" s="14"/>
+      <x:c r="X139" s="14"/>
+      <x:c r="Y139" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z139" s="12"/>
+      <x:c r="AA139" s="15" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="AB139" s="15" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AC139" s="12"/>
+      <x:c r="AD139" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE139" s="12"/>
+      <x:c r="AF139" s="12"/>
+      <x:c r="AG139" s="12"/>
+      <x:c r="AH139" s="12"/>
+      <x:c r="AI139" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ139" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AK139" s="16" t="n">
+        <x:v>-0.284</x:v>
+      </x:c>
+      <x:c r="AL139" s="16" t="n">
+        <x:v>1.2e-7</x:v>
+      </x:c>
+      <x:c r="AM139" s="12" t="str">
+        <x:v>WM42_surfaceCe11.2_450C</x:v>
+      </x:c>
+      <x:c r="AN139" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO139" s="12" t="str">
+        <x:v>https://bcc.bas.bg/BCC_Volumes/Volume_43_Number_1_2011/Volume_43_Number_1_2011_PDF/2011-43-1_24.pdf</x:v>
+      </x:c>
+      <x:c r="AP139" s="12" t="str">
+        <x:v>Publisher PDF methods pp1-2; Tables1/2 p2</x:v>
+      </x:c>
+      <x:c r="AQ139" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR139" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS139" s="12" t="n">
+        <x:v>1.2e-7</x:v>
+      </x:c>
+      <x:c r="AT139" s="12" t="str">
+        <x:v>A/cm2</x:v>
+      </x:c>
+      <x:c r="AU139" s="12" t="str">
+        <x:v>3.5% NaCl; percentage basis not reassigned</x:v>
+      </x:c>
+      <x:c r="AV139" s="12"/>
+      <x:c r="AW139" s="12"/>
+      <x:c r="AX139" s="12"/>
+      <x:c r="AY139" s="12"/>
+      <x:c r="AZ139" s="12" t="n">
+        <x:v>11.2</x:v>
+      </x:c>
+      <x:c r="BA139" s="12"/>
+      <x:c r="BB139" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="BC139" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD139" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE139" s="12" t="str">
+        <x:v>Si; Mn; P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF139" s="12" t="str">
+        <x:v>OC404 substrate composition only. Surface oxide Ce atomic percent is not bulk Ce wt%. Room-temperature PDP not forced to25C. Thermal treatment performed in air; cooling route unreported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="40" customHeight="1">
+      <x:c r="A140" s="12" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B140" s="13" t="str">
+        <x:v>OC404 페라이트계 스테인리스강(20Cr-5Al-0.02C) + 전착 Ce2O3/CeO2 막</x:v>
+      </x:c>
+      <x:c r="C140" s="13" t="str">
+        <x:v>surfaceCe29.6_450C</x:v>
+      </x:c>
+      <x:c r="D140" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="E140" s="14"/>
+      <x:c r="F140" s="14"/>
+      <x:c r="G140" s="14"/>
+      <x:c r="H140" s="14"/>
+      <x:c r="I140" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J140" s="14"/>
+      <x:c r="K140" s="14"/>
+      <x:c r="L140" s="14"/>
+      <x:c r="M140" s="14"/>
+      <x:c r="N140" s="14"/>
+      <x:c r="O140" s="14"/>
+      <x:c r="P140" s="14"/>
+      <x:c r="Q140" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R140" s="14"/>
+      <x:c r="S140" s="14"/>
+      <x:c r="T140" s="14"/>
+      <x:c r="U140" s="14"/>
+      <x:c r="V140" s="14"/>
+      <x:c r="W140" s="14"/>
+      <x:c r="X140" s="14"/>
+      <x:c r="Y140" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z140" s="12"/>
+      <x:c r="AA140" s="15" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="AB140" s="15" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AC140" s="12"/>
+      <x:c r="AD140" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE140" s="12"/>
+      <x:c r="AF140" s="12"/>
+      <x:c r="AG140" s="12"/>
+      <x:c r="AH140" s="12"/>
+      <x:c r="AI140" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ140" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AK140" s="16" t="n">
+        <x:v>-0.168</x:v>
+      </x:c>
+      <x:c r="AL140" s="16" t="n">
+        <x:v>1.3e-8</x:v>
+      </x:c>
+      <x:c r="AM140" s="12" t="str">
+        <x:v>WM42_surfaceCe29.6_450C</x:v>
+      </x:c>
+      <x:c r="AN140" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO140" s="12" t="str">
+        <x:v>https://bcc.bas.bg/BCC_Volumes/Volume_43_Number_1_2011/Volume_43_Number_1_2011_PDF/2011-43-1_24.pdf</x:v>
+      </x:c>
+      <x:c r="AP140" s="12" t="str">
+        <x:v>Publisher PDF methods pp1-2; Tables1/2 p2</x:v>
+      </x:c>
+      <x:c r="AQ140" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR140" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS140" s="12" t="n">
+        <x:v>1.3e-8</x:v>
+      </x:c>
+      <x:c r="AT140" s="12" t="str">
+        <x:v>A/cm2</x:v>
+      </x:c>
+      <x:c r="AU140" s="12" t="str">
+        <x:v>3.5% NaCl; percentage basis not reassigned</x:v>
+      </x:c>
+      <x:c r="AV140" s="12"/>
+      <x:c r="AW140" s="12"/>
+      <x:c r="AX140" s="12"/>
+      <x:c r="AY140" s="12"/>
+      <x:c r="AZ140" s="12" t="n">
+        <x:v>29.6</x:v>
+      </x:c>
+      <x:c r="BA140" s="12"/>
+      <x:c r="BB140" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="BC140" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD140" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE140" s="12" t="str">
+        <x:v>Si; Mn; P; S; Ni; Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; PREN; 냉각방식; 전해질 농도(wt%); 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF140" s="12" t="str">
+        <x:v>OC404 substrate composition only. Surface oxide Ce atomic percent is not bulk Ce wt%. Room-temperature PDP not forced to25C. Thermal treatment performed in air; cooling route unreported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="40" customHeight="1">
+      <x:c r="A141" s="12" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B141" s="13" t="str">
+        <x:v>Q355NHq 내후성 교량강 (La-Ce 희토류 4수준: 30/90/170/280 ppm)</x:v>
+      </x:c>
+      <x:c r="C141" s="13" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="D141" s="14" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="E141" s="14" t="n">
+        <x:v>0.23</x:v>
+      </x:c>
+      <x:c r="F141" s="14" t="n">
+        <x:v>1.19</x:v>
+      </x:c>
+      <x:c r="G141" s="14" t="n">
+        <x:v>0.015</x:v>
+      </x:c>
+      <x:c r="H141" s="14" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="I141" s="14" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="J141" s="14" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="K141" s="14"/>
+      <x:c r="L141" s="14" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="M141" s="14"/>
+      <x:c r="N141" s="14"/>
+      <x:c r="O141" s="14"/>
+      <x:c r="P141" s="14"/>
+      <x:c r="Q141" s="14" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="R141" s="14"/>
+      <x:c r="S141" s="14" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="T141" s="14" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="U141" s="14"/>
+      <x:c r="V141" s="14"/>
+      <x:c r="W141" s="14"/>
+      <x:c r="X141" s="14" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="Y141" s="12"/>
+      <x:c r="Z141" s="12"/>
+      <x:c r="AA141" s="15"/>
+      <x:c r="AB141" s="15"/>
+      <x:c r="AC141" s="12"/>
+      <x:c r="AD141" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE141" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF141" s="12"/>
+      <x:c r="AG141" s="12"/>
+      <x:c r="AH141" s="12"/>
+      <x:c r="AI141" s="12" t="str">
+        <x:v>AgAgCl</x:v>
+      </x:c>
+      <x:c r="AJ141" s="12" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="AK141" s="16" t="n">
+        <x:v>-0.56</x:v>
+      </x:c>
+      <x:c r="AL141" s="16" t="n">
+        <x:v>0.0000439</x:v>
+      </x:c>
+      <x:c r="AM141" s="12" t="str">
+        <x:v>WM35_Base</x:v>
+      </x:c>
+      <x:c r="AN141" s="12" t="str">
+        <x:v>10.11973/fsyfh-202403006</x:v>
+      </x:c>
+      <x:c r="AO141" s="12" t="str">
+        <x:v>https://fsyfh.mat-test.com/cn/article/doi/10.11973/fsyfh-202403006</x:v>
+      </x:c>
+      <x:c r="AP141" s="12" t="str">
+        <x:v>Publisher PDF Table1 p2; methods p3; Table3/Fig7 p5</x:v>
+      </x:c>
+      <x:c r="AQ141" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR141" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS141" s="12" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="AT141" s="12" t="str">
+        <x:v>x10^-5 A/cm2</x:v>
+      </x:c>
+      <x:c r="AU141" s="12"/>
+      <x:c r="AV141" s="12"/>
+      <x:c r="AW141" s="12" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="AX141" s="12"/>
+      <x:c r="AY141" s="12"/>
+      <x:c r="AZ141" s="12"/>
+      <x:c r="BA141" s="12"/>
+      <x:c r="BB141" s="12" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="BC141" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD141" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE141" s="12" t="str">
+        <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF141" s="12" t="str">
+        <x:v>Base is not RE-free: measuredCe.002+La.001. Reference is AgAgCl, not workbook bibliographySCE. 25C belongs to separate6%NaCl inclusion-immersion test; pre-EIS30min OCP not total PDP immersion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="40" customHeight="1">
+      <x:c r="A142" s="12" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B142" s="13" t="str">
+        <x:v>Q355NHq 내후성 교량강 (La-Ce 희토류 4수준: 30/90/170/280 ppm)</x:v>
+      </x:c>
+      <x:c r="C142" s="13" t="str">
+        <x:v>RE90</x:v>
+      </x:c>
+      <x:c r="D142" s="14" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="E142" s="14" t="n">
+        <x:v>0.23</x:v>
+      </x:c>
+      <x:c r="F142" s="14" t="n">
+        <x:v>1.19</x:v>
+      </x:c>
+      <x:c r="G142" s="14" t="n">
+        <x:v>0.016</x:v>
+      </x:c>
+      <x:c r="H142" s="14" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="I142" s="14" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="J142" s="14" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="K142" s="14"/>
+      <x:c r="L142" s="14" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="M142" s="14"/>
+      <x:c r="N142" s="14"/>
+      <x:c r="O142" s="14"/>
+      <x:c r="P142" s="14"/>
+      <x:c r="Q142" s="14" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="R142" s="14"/>
+      <x:c r="S142" s="14" t="n">
+        <x:v>0.006</x:v>
+      </x:c>
+      <x:c r="T142" s="14" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="U142" s="14"/>
+      <x:c r="V142" s="14"/>
+      <x:c r="W142" s="14"/>
+      <x:c r="X142" s="14" t="n">
+        <x:v>0.009000000000000001</x:v>
+      </x:c>
+      <x:c r="Y142" s="12"/>
+      <x:c r="Z142" s="12"/>
+      <x:c r="AA142" s="15"/>
+      <x:c r="AB142" s="15"/>
+      <x:c r="AC142" s="12"/>
+      <x:c r="AD142" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE142" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF142" s="12"/>
+      <x:c r="AG142" s="12"/>
+      <x:c r="AH142" s="12"/>
+      <x:c r="AI142" s="12" t="str">
+        <x:v>AgAgCl</x:v>
+      </x:c>
+      <x:c r="AJ142" s="12" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="AK142" s="16" t="n">
+        <x:v>-0.55</x:v>
+      </x:c>
+      <x:c r="AL142" s="16" t="n">
+        <x:v>0.0000394</x:v>
+      </x:c>
+      <x:c r="AM142" s="12" t="str">
+        <x:v>WM35_RE90</x:v>
+      </x:c>
+      <x:c r="AN142" s="12" t="str">
+        <x:v>10.11973/fsyfh-202403006</x:v>
+      </x:c>
+      <x:c r="AO142" s="12" t="str">
+        <x:v>https://fsyfh.mat-test.com/cn/article/doi/10.11973/fsyfh-202403006</x:v>
+      </x:c>
+      <x:c r="AP142" s="12" t="str">
+        <x:v>Publisher PDF Table1 p2; methods p3; Table3/Fig7 p5</x:v>
+      </x:c>
+      <x:c r="AQ142" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR142" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS142" s="12" t="n">
+        <x:v>3.94</x:v>
+      </x:c>
+      <x:c r="AT142" s="12" t="str">
+        <x:v>x10^-5 A/cm2</x:v>
+      </x:c>
+      <x:c r="AU142" s="12"/>
+      <x:c r="AV142" s="12"/>
+      <x:c r="AW142" s="12" t="n">
+        <x:v>0.009000000000000001</x:v>
+      </x:c>
+      <x:c r="AX142" s="12"/>
+      <x:c r="AY142" s="12"/>
+      <x:c r="AZ142" s="12"/>
+      <x:c r="BA142" s="12"/>
+      <x:c r="BB142" s="12" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="BC142" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD142" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE142" s="12" t="str">
+        <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF142" s="12" t="str">
+        <x:v>Base is not RE-free: measuredCe.002+La.001. Reference is AgAgCl, not workbook bibliographySCE. 25C belongs to separate6%NaCl inclusion-immersion test; pre-EIS30min OCP not total PDP immersion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="40" customHeight="1">
+      <x:c r="A143" s="12" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B143" s="13" t="str">
+        <x:v>Q355NHq 내후성 교량강 (La-Ce 희토류 4수준: 30/90/170/280 ppm)</x:v>
+      </x:c>
+      <x:c r="C143" s="13" t="str">
+        <x:v>RE170</x:v>
+      </x:c>
+      <x:c r="D143" s="14" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="E143" s="14" t="n">
+        <x:v>0.23</x:v>
+      </x:c>
+      <x:c r="F143" s="14" t="n">
+        <x:v>1.19</x:v>
+      </x:c>
+      <x:c r="G143" s="14" t="n">
+        <x:v>0.015</x:v>
+      </x:c>
+      <x:c r="H143" s="14" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="I143" s="14" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="J143" s="14" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="K143" s="14"/>
+      <x:c r="L143" s="14" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="M143" s="14"/>
+      <x:c r="N143" s="14"/>
+      <x:c r="O143" s="14"/>
+      <x:c r="P143" s="14"/>
+      <x:c r="Q143" s="14" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="R143" s="14"/>
+      <x:c r="S143" s="14" t="n">
+        <x:v>0.011</x:v>
+      </x:c>
+      <x:c r="T143" s="14" t="n">
+        <x:v>0.006</x:v>
+      </x:c>
+      <x:c r="U143" s="14"/>
+      <x:c r="V143" s="14"/>
+      <x:c r="W143" s="14"/>
+      <x:c r="X143" s="14" t="n">
+        <x:v>0.017</x:v>
+      </x:c>
+      <x:c r="Y143" s="12"/>
+      <x:c r="Z143" s="12"/>
+      <x:c r="AA143" s="15"/>
+      <x:c r="AB143" s="15"/>
+      <x:c r="AC143" s="12"/>
+      <x:c r="AD143" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE143" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF143" s="12"/>
+      <x:c r="AG143" s="12"/>
+      <x:c r="AH143" s="12"/>
+      <x:c r="AI143" s="12" t="str">
+        <x:v>AgAgCl</x:v>
+      </x:c>
+      <x:c r="AJ143" s="12" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="AK143" s="16" t="n">
+        <x:v>-0.5</x:v>
+      </x:c>
+      <x:c r="AL143" s="16" t="n">
+        <x:v>0.0000225</x:v>
+      </x:c>
+      <x:c r="AM143" s="12" t="str">
+        <x:v>WM35_RE170</x:v>
+      </x:c>
+      <x:c r="AN143" s="12" t="str">
+        <x:v>10.11973/fsyfh-202403006</x:v>
+      </x:c>
+      <x:c r="AO143" s="12" t="str">
+        <x:v>https://fsyfh.mat-test.com/cn/article/doi/10.11973/fsyfh-202403006</x:v>
+      </x:c>
+      <x:c r="AP143" s="12" t="str">
+        <x:v>Publisher PDF Table1 p2; methods p3; Table3/Fig7 p5</x:v>
+      </x:c>
+      <x:c r="AQ143" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR143" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS143" s="12" t="n">
+        <x:v>2.25</x:v>
+      </x:c>
+      <x:c r="AT143" s="12" t="str">
+        <x:v>x10^-5 A/cm2</x:v>
+      </x:c>
+      <x:c r="AU143" s="12"/>
+      <x:c r="AV143" s="12"/>
+      <x:c r="AW143" s="12" t="n">
+        <x:v>0.017</x:v>
+      </x:c>
+      <x:c r="AX143" s="12"/>
+      <x:c r="AY143" s="12"/>
+      <x:c r="AZ143" s="12"/>
+      <x:c r="BA143" s="12"/>
+      <x:c r="BB143" s="12" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="BC143" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD143" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE143" s="12" t="str">
+        <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF143" s="12" t="str">
+        <x:v>Base is not RE-free: measuredCe.002+La.001. Reference is AgAgCl, not workbook bibliographySCE. 25C belongs to separate6%NaCl inclusion-immersion test; pre-EIS30min OCP not total PDP immersion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="40" customHeight="1">
+      <x:c r="A144" s="12" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B144" s="13" t="str">
+        <x:v>Q355NHq 내후성 교량강 (La-Ce 희토류 4수준: 30/90/170/280 ppm)</x:v>
+      </x:c>
+      <x:c r="C144" s="13" t="str">
+        <x:v>RE280</x:v>
+      </x:c>
+      <x:c r="D144" s="14" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="E144" s="14" t="n">
+        <x:v>0.23</x:v>
+      </x:c>
+      <x:c r="F144" s="14" t="n">
+        <x:v>1.19</x:v>
+      </x:c>
+      <x:c r="G144" s="14" t="n">
+        <x:v>0.015</x:v>
+      </x:c>
+      <x:c r="H144" s="14" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="I144" s="14" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="J144" s="14" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="K144" s="14"/>
+      <x:c r="L144" s="14" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="M144" s="14"/>
+      <x:c r="N144" s="14"/>
+      <x:c r="O144" s="14"/>
+      <x:c r="P144" s="14"/>
+      <x:c r="Q144" s="14" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="R144" s="14"/>
+      <x:c r="S144" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="T144" s="14" t="n">
+        <x:v>0.008</x:v>
+      </x:c>
+      <x:c r="U144" s="14"/>
+      <x:c r="V144" s="14"/>
+      <x:c r="W144" s="14"/>
+      <x:c r="X144" s="14" t="n">
+        <x:v>0.028</x:v>
+      </x:c>
+      <x:c r="Y144" s="12"/>
+      <x:c r="Z144" s="12"/>
+      <x:c r="AA144" s="15"/>
+      <x:c r="AB144" s="15"/>
+      <x:c r="AC144" s="12"/>
+      <x:c r="AD144" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE144" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF144" s="12"/>
+      <x:c r="AG144" s="12"/>
+      <x:c r="AH144" s="12"/>
+      <x:c r="AI144" s="12" t="str">
+        <x:v>AgAgCl</x:v>
+      </x:c>
+      <x:c r="AJ144" s="12" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="AK144" s="16" t="n">
+        <x:v>-0.54</x:v>
+      </x:c>
+      <x:c r="AL144" s="16" t="n">
+        <x:v>0.0000363</x:v>
+      </x:c>
+      <x:c r="AM144" s="12" t="str">
+        <x:v>WM35_RE280</x:v>
+      </x:c>
+      <x:c r="AN144" s="12" t="str">
+        <x:v>10.11973/fsyfh-202403006</x:v>
+      </x:c>
+      <x:c r="AO144" s="12" t="str">
+        <x:v>https://fsyfh.mat-test.com/cn/article/doi/10.11973/fsyfh-202403006</x:v>
+      </x:c>
+      <x:c r="AP144" s="12" t="str">
+        <x:v>Publisher PDF Table1 p2; methods p3; Table3/Fig7 p5</x:v>
+      </x:c>
+      <x:c r="AQ144" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR144" s="12" t="str">
+        <x:v>reported_numeric</x:v>
+      </x:c>
+      <x:c r="AS144" s="12" t="n">
+        <x:v>3.63</x:v>
+      </x:c>
+      <x:c r="AT144" s="12" t="str">
+        <x:v>x10^-5 A/cm2</x:v>
+      </x:c>
+      <x:c r="AU144" s="12"/>
+      <x:c r="AV144" s="12"/>
+      <x:c r="AW144" s="12" t="n">
+        <x:v>0.028</x:v>
+      </x:c>
+      <x:c r="AX144" s="12"/>
+      <x:c r="AY144" s="12"/>
+      <x:c r="AZ144" s="12"/>
+      <x:c r="BA144" s="12"/>
+      <x:c r="BB144" s="12" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="BC144" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD144" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE144" s="12" t="str">
+        <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Pr; W; Y; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C)</x:v>
+      </x:c>
+      <x:c r="BF144" s="12" t="str">
+        <x:v>Base is not RE-free: measuredCe.002+La.001. Reference is AgAgCl, not workbook bibliographySCE. 25C belongs to separate6%NaCl inclusion-immersion test; pre-EIS30min OCP not total PDP immersion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="40" customHeight="1">
+      <x:c r="A145" s="12" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B145" s="13" t="str">
+        <x:v>304 스테인리스강(Ce)</x:v>
+      </x:c>
+      <x:c r="C145" s="13" t="str">
+        <x:v>Ce0</x:v>
+      </x:c>
+      <x:c r="D145" s="14" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="E145" s="14" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="F145" s="14" t="n">
+        <x:v>1.38</x:v>
+      </x:c>
+      <x:c r="G145" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="H145" s="14" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="I145" s="14" t="n">
+        <x:v>18.37</x:v>
+      </x:c>
+      <x:c r="J145" s="14" t="n">
+        <x:v>7.21</x:v>
+      </x:c>
+      <x:c r="K145" s="14"/>
+      <x:c r="L145" s="14"/>
+      <x:c r="M145" s="14"/>
+      <x:c r="N145" s="14"/>
+      <x:c r="O145" s="14"/>
+      <x:c r="P145" s="14"/>
+      <x:c r="Q145" s="14"/>
+      <x:c r="R145" s="14"/>
+      <x:c r="S145" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T145" s="14"/>
+      <x:c r="U145" s="14"/>
+      <x:c r="V145" s="14"/>
+      <x:c r="W145" s="14"/>
+      <x:c r="X145" s="14"/>
+      <x:c r="Y145" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z145" s="12"/>
+      <x:c r="AA145" s="15"/>
+      <x:c r="AB145" s="15"/>
+      <x:c r="AC145" s="12" t="str">
+        <x:v>water</x:v>
+      </x:c>
+      <x:c r="AD145" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE145" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF145" s="12"/>
+      <x:c r="AG145" s="12"/>
+      <x:c r="AH145" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="AI145" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ145" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="AK145" s="16"/>
+      <x:c r="AL145" s="16"/>
+      <x:c r="AM145" s="12" t="str">
+        <x:v>WM27_Ce0</x:v>
+      </x:c>
+      <x:c r="AN145" s="12" t="str">
+        <x:v>10.7449/2019/MST_2019_122_129</x:v>
+      </x:c>
+      <x:c r="AO145" s="12" t="str">
+        <x:v>https://www.tms.org/membercontent/pdf2/mst_2019_122_129.pdf</x:v>
+      </x:c>
+      <x:c r="AP145" s="12" t="str">
+        <x:v>TMS-hosted conference paper TableI p2; Sec2.2.2 p3; polarization discussion pp6-7</x:v>
+      </x:c>
+      <x:c r="AQ145" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR145" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS145" s="12"/>
+      <x:c r="AT145" s="12"/>
+      <x:c r="AU145" s="12"/>
+      <x:c r="AV145" s="12"/>
+      <x:c r="AW145" s="12"/>
+      <x:c r="AX145" s="12"/>
+      <x:c r="AY145" s="12"/>
+      <x:c r="AZ145" s="12"/>
+      <x:c r="BA145" s="12"/>
+      <x:c r="BB145" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="BC145" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD145" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE145" s="12" t="str">
+        <x:v>Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF145" s="12" t="str">
+        <x:v>Shared starting-steel composition; Ce is nominal laboratory level, not individually verified residual. 1600C is melting, not post-cast heat treatment. No numerical icorr in text/table; Ecorr -.31125 only explicit .012Ce sample.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="40" customHeight="1">
+      <x:c r="A146" s="12" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B146" s="13" t="str">
+        <x:v>304 스테인리스강(Ce)</x:v>
+      </x:c>
+      <x:c r="C146" s="13" t="str">
+        <x:v>Ce0.006</x:v>
+      </x:c>
+      <x:c r="D146" s="14" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="E146" s="14" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="F146" s="14" t="n">
+        <x:v>1.38</x:v>
+      </x:c>
+      <x:c r="G146" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="H146" s="14" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="I146" s="14" t="n">
+        <x:v>18.37</x:v>
+      </x:c>
+      <x:c r="J146" s="14" t="n">
+        <x:v>7.21</x:v>
+      </x:c>
+      <x:c r="K146" s="14"/>
+      <x:c r="L146" s="14"/>
+      <x:c r="M146" s="14"/>
+      <x:c r="N146" s="14"/>
+      <x:c r="O146" s="14"/>
+      <x:c r="P146" s="14"/>
+      <x:c r="Q146" s="14"/>
+      <x:c r="R146" s="14"/>
+      <x:c r="S146" s="14" t="n">
+        <x:v>0.006</x:v>
+      </x:c>
+      <x:c r="T146" s="14"/>
+      <x:c r="U146" s="14"/>
+      <x:c r="V146" s="14"/>
+      <x:c r="W146" s="14"/>
+      <x:c r="X146" s="14"/>
+      <x:c r="Y146" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z146" s="12"/>
+      <x:c r="AA146" s="15"/>
+      <x:c r="AB146" s="15"/>
+      <x:c r="AC146" s="12" t="str">
+        <x:v>water</x:v>
+      </x:c>
+      <x:c r="AD146" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE146" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF146" s="12"/>
+      <x:c r="AG146" s="12"/>
+      <x:c r="AH146" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="AI146" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ146" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="AK146" s="16"/>
+      <x:c r="AL146" s="16"/>
+      <x:c r="AM146" s="12" t="str">
+        <x:v>WM27_Ce0.006</x:v>
+      </x:c>
+      <x:c r="AN146" s="12" t="str">
+        <x:v>10.7449/2019/MST_2019_122_129</x:v>
+      </x:c>
+      <x:c r="AO146" s="12" t="str">
+        <x:v>https://www.tms.org/membercontent/pdf2/mst_2019_122_129.pdf</x:v>
+      </x:c>
+      <x:c r="AP146" s="12" t="str">
+        <x:v>TMS-hosted conference paper TableI p2; Sec2.2.2 p3; polarization discussion pp6-7</x:v>
+      </x:c>
+      <x:c r="AQ146" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR146" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS146" s="12"/>
+      <x:c r="AT146" s="12"/>
+      <x:c r="AU146" s="12"/>
+      <x:c r="AV146" s="12"/>
+      <x:c r="AW146" s="12"/>
+      <x:c r="AX146" s="12"/>
+      <x:c r="AY146" s="12"/>
+      <x:c r="AZ146" s="12"/>
+      <x:c r="BA146" s="12"/>
+      <x:c r="BB146" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="BC146" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD146" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE146" s="12" t="str">
+        <x:v>Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF146" s="12" t="str">
+        <x:v>Shared starting-steel composition; Ce is nominal laboratory level, not individually verified residual. 1600C is melting, not post-cast heat treatment. No numerical icorr in text/table; Ecorr -.31125 only explicit .012Ce sample.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="40" customHeight="1">
+      <x:c r="A147" s="12" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B147" s="13" t="str">
+        <x:v>304 스테인리스강(Ce)</x:v>
+      </x:c>
+      <x:c r="C147" s="13" t="str">
+        <x:v>Ce0.012</x:v>
+      </x:c>
+      <x:c r="D147" s="14" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="E147" s="14" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="F147" s="14" t="n">
+        <x:v>1.38</x:v>
+      </x:c>
+      <x:c r="G147" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="H147" s="14" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="I147" s="14" t="n">
+        <x:v>18.37</x:v>
+      </x:c>
+      <x:c r="J147" s="14" t="n">
+        <x:v>7.21</x:v>
+      </x:c>
+      <x:c r="K147" s="14"/>
+      <x:c r="L147" s="14"/>
+      <x:c r="M147" s="14"/>
+      <x:c r="N147" s="14"/>
+      <x:c r="O147" s="14"/>
+      <x:c r="P147" s="14"/>
+      <x:c r="Q147" s="14"/>
+      <x:c r="R147" s="14"/>
+      <x:c r="S147" s="14" t="n">
+        <x:v>0.012</x:v>
+      </x:c>
+      <x:c r="T147" s="14"/>
+      <x:c r="U147" s="14"/>
+      <x:c r="V147" s="14"/>
+      <x:c r="W147" s="14"/>
+      <x:c r="X147" s="14"/>
+      <x:c r="Y147" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z147" s="12"/>
+      <x:c r="AA147" s="15"/>
+      <x:c r="AB147" s="15"/>
+      <x:c r="AC147" s="12" t="str">
+        <x:v>water</x:v>
+      </x:c>
+      <x:c r="AD147" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE147" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF147" s="12"/>
+      <x:c r="AG147" s="12"/>
+      <x:c r="AH147" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="AI147" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ147" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="AK147" s="16" t="n">
+        <x:v>-0.31125</x:v>
+      </x:c>
+      <x:c r="AL147" s="16"/>
+      <x:c r="AM147" s="12" t="str">
+        <x:v>WM27_Ce0.012</x:v>
+      </x:c>
+      <x:c r="AN147" s="12" t="str">
+        <x:v>10.7449/2019/MST_2019_122_129</x:v>
+      </x:c>
+      <x:c r="AO147" s="12" t="str">
+        <x:v>https://www.tms.org/membercontent/pdf2/mst_2019_122_129.pdf</x:v>
+      </x:c>
+      <x:c r="AP147" s="12" t="str">
+        <x:v>TMS-hosted conference paper TableI p2; Sec2.2.2 p3; polarization discussion pp6-7</x:v>
+      </x:c>
+      <x:c r="AQ147" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR147" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS147" s="12"/>
+      <x:c r="AT147" s="12"/>
+      <x:c r="AU147" s="12"/>
+      <x:c r="AV147" s="12"/>
+      <x:c r="AW147" s="12"/>
+      <x:c r="AX147" s="12"/>
+      <x:c r="AY147" s="12"/>
+      <x:c r="AZ147" s="12"/>
+      <x:c r="BA147" s="12"/>
+      <x:c r="BB147" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="BC147" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD147" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE147" s="12" t="str">
+        <x:v>Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 침지시간(min); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF147" s="12" t="str">
+        <x:v>Shared starting-steel composition; Ce is nominal laboratory level, not individually verified residual. 1600C is melting, not post-cast heat treatment. No numerical icorr in text/table; Ecorr -.31125 only explicit .012Ce sample.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="40" customHeight="1">
+      <x:c r="A148" s="12" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B148" s="13" t="str">
+        <x:v>304 스테인리스강(Ce)</x:v>
+      </x:c>
+      <x:c r="C148" s="13" t="str">
+        <x:v>Ce0.018</x:v>
+      </x:c>
+      <x:c r="D148" s="14" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="E148" s="14" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="F148" s="14" t="n">
+        <x:v>1.38</x:v>
+      </x:c>
+      <x:c r="G148" s="14" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="H148" s="14" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="I148" s="14" t="n">
+        <x:v>18.37</x:v>
+      </x:c>
+      <x:c r="J148" s="14" t="n">
+        <x:v>7.21</x:v>
+      </x:c>
+      <x:c r="K148" s="14"/>
+      <x:c r="L148" s="14"/>
+      <x:c r="M148" s="14"/>
+      <x:c r="N148" s="14"/>
+      <x:c r="O148" s="14"/>
+      <x:c r="P148" s="14"/>
+      <x:c r="Q148" s="14"/>
+      <x:c r="R148" s="14"/>
+      <x:c r="S148" s="14" t="n">
+        <x:v>0.018</x:v>
+      </x:c>
+      <x:c r="T148" s="14"/>
+      <x:c r="U148" s="14"/>
+      <x:c r="V148" s="14"/>
+      <x:c r="W148" s="14"/>
+      <x:c r="X148" s="14"/>
+      <x:c r="Y148" s="12" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="Z148" s="12"/>
+      <x:c r="AA148" s="15"/>
+      <x:c r="AB148" s="15"/>
+      <x:c r="AC148" s="12" t="str">
+        <x:v>water</x:v>
+      </x:c>
+      <x:c r="AD148" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE148" s="12" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AF148" s="12"/>
+      <x:c r="AG148" s="12"/>
+      <x:c r="AH148" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="AI148" s="12" t="str">
+        <x:v>SCE</x:v>
+      </x:c>
+      <x:c r="AJ148" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="AK148" s="16"/>
+      <x:c r="AL148" s="16"/>
+      <x:c r="AM148" s="12" t="str">
+        <x:v>WM27_Ce0.018</x:v>
+      </x:c>
+      <x:c r="AN148" s="12" t="str">
+        <x:v>10.7449/2019/MST_2019_122_129</x:v>
+      </x:c>
+      <x:c r="AO148" s="12" t="str">
+        <x:v>https://www.tms.org/membercontent/pdf2/mst_2019_122_129.pdf</x:v>
+      </x:c>
+      <x:c r="AP148" s="12" t="str">
+        <x:v>TMS-hosted conference paper TableI p2; Sec2.2.2 p3; polarization discussion pp6-7</x:v>
+      </x:c>
+      <x:c r="AQ148" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR148" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS148" s="12"/>
+      <x:c r="AT148" s="12"/>
+      <x:c r="AU148" s="12"/>
+      <x:c r="AV148" s="12"/>
+      <x:c r="AW148" s="12"/>
+      <x:c r="AX148" s="12"/>
+      <x:c r="AY148" s="12"/>
+      <x:c r="AZ148" s="12"/>
+      <x:c r="BA148" s="12"/>
+      <x:c r="BB148" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="BC148" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD148" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE148" s="12" t="str">
+        <x:v>Mo; Cu; T.N.(Total Nitrogen); Nb; V; Ti; Al; Sb; La; Pr; W; Y; La+Ce_합산; PREN; 열처리 온도(°C); Time(min); 침지시간(min); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF148" s="12" t="str">
+        <x:v>Shared starting-steel composition; Ce is nominal laboratory level, not individually verified residual. 1600C is melting, not post-cast heat treatment. No numerical icorr in text/table; Ecorr -.31125 only explicit .012Ce sample.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="40" customHeight="1">
+      <x:c r="A149" s="12" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B149" s="13" t="str">
+        <x:v>Cu-P계 내후성강 (RE 0~0.064wt% 첨가)</x:v>
+      </x:c>
+      <x:c r="C149" s="13" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="D149" s="14" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+      <x:c r="E149" s="14" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="F149" s="14" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="G149" s="14" t="n">
+        <x:v>0.087</x:v>
+      </x:c>
+      <x:c r="H149" s="14" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="I149" s="14" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="J149" s="14" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K149" s="14"/>
+      <x:c r="L149" s="14" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="M149" s="14"/>
+      <x:c r="N149" s="14"/>
+      <x:c r="O149" s="14"/>
+      <x:c r="P149" s="14"/>
+      <x:c r="Q149" s="14" t="n">
+        <x:v>0.036</x:v>
+      </x:c>
+      <x:c r="R149" s="14"/>
+      <x:c r="S149" s="14"/>
+      <x:c r="T149" s="14"/>
+      <x:c r="U149" s="14"/>
+      <x:c r="V149" s="14"/>
+      <x:c r="W149" s="14"/>
+      <x:c r="X149" s="14"/>
+      <x:c r="Y149" s="12"/>
+      <x:c r="Z149" s="12"/>
+      <x:c r="AA149" s="15"/>
+      <x:c r="AB149" s="15"/>
+      <x:c r="AC149" s="12"/>
+      <x:c r="AD149" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE149" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="AF149" s="12"/>
+      <x:c r="AG149" s="12"/>
+      <x:c r="AH149" s="12"/>
+      <x:c r="AI149" s="12"/>
+      <x:c r="AJ149" s="12"/>
+      <x:c r="AK149" s="16"/>
+      <x:c r="AL149" s="16"/>
+      <x:c r="AM149" s="12" t="str">
+        <x:v>WM44_A</x:v>
+      </x:c>
+      <x:c r="AN149" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO149" s="12" t="str">
+        <x:v>https://www.anticorr.org.tw/JCCE/paper/V26/260207.pdf</x:v>
+      </x:c>
+      <x:c r="AP149" s="12" t="str">
+        <x:v>Publisher paper Table1 printed p108; experimental Sec2.4</x:v>
+      </x:c>
+      <x:c r="AQ149" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR149" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS149" s="12"/>
+      <x:c r="AT149" s="12"/>
+      <x:c r="AU149" s="12"/>
+      <x:c r="AV149" s="12"/>
+      <x:c r="AW149" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX149" s="12"/>
+      <x:c r="AY149" s="12"/>
+      <x:c r="AZ149" s="12"/>
+      <x:c r="BA149" s="12"/>
+      <x:c r="BB149" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="BC149" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD149" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE149" s="12" t="str">
+        <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF149" s="12" t="str">
+        <x:v>Primary publisher PDF indexed text Table1. Individual rare-earth species unreported; total RE not assigned to Ce/La. No sample-specific numerical icorr table; no estimated polarization-curve extraction. Direct download endpoint404; indexed primary text used.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="40" customHeight="1">
+      <x:c r="A150" s="12" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B150" s="13" t="str">
+        <x:v>Cu-P계 내후성강 (RE 0~0.064wt% 첨가)</x:v>
+      </x:c>
+      <x:c r="C150" s="13" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D150" s="14" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="E150" s="14" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="F150" s="14" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="G150" s="14" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="H150" s="14" t="n">
+        <x:v>0.008</x:v>
+      </x:c>
+      <x:c r="I150" s="14" t="n">
+        <x:v>0.47</x:v>
+      </x:c>
+      <x:c r="J150" s="14" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K150" s="14"/>
+      <x:c r="L150" s="14" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="M150" s="14"/>
+      <x:c r="N150" s="14"/>
+      <x:c r="O150" s="14"/>
+      <x:c r="P150" s="14"/>
+      <x:c r="Q150" s="14" t="n">
+        <x:v>0.022</x:v>
+      </x:c>
+      <x:c r="R150" s="14"/>
+      <x:c r="S150" s="14"/>
+      <x:c r="T150" s="14"/>
+      <x:c r="U150" s="14"/>
+      <x:c r="V150" s="14"/>
+      <x:c r="W150" s="14"/>
+      <x:c r="X150" s="14"/>
+      <x:c r="Y150" s="12"/>
+      <x:c r="Z150" s="12"/>
+      <x:c r="AA150" s="15"/>
+      <x:c r="AB150" s="15"/>
+      <x:c r="AC150" s="12"/>
+      <x:c r="AD150" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE150" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="AF150" s="12"/>
+      <x:c r="AG150" s="12"/>
+      <x:c r="AH150" s="12"/>
+      <x:c r="AI150" s="12"/>
+      <x:c r="AJ150" s="12"/>
+      <x:c r="AK150" s="16"/>
+      <x:c r="AL150" s="16"/>
+      <x:c r="AM150" s="12" t="str">
+        <x:v>WM44_B</x:v>
+      </x:c>
+      <x:c r="AN150" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO150" s="12" t="str">
+        <x:v>https://www.anticorr.org.tw/JCCE/paper/V26/260207.pdf</x:v>
+      </x:c>
+      <x:c r="AP150" s="12" t="str">
+        <x:v>Publisher paper Table1 printed p108; experimental Sec2.4</x:v>
+      </x:c>
+      <x:c r="AQ150" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR150" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS150" s="12"/>
+      <x:c r="AT150" s="12"/>
+      <x:c r="AU150" s="12"/>
+      <x:c r="AV150" s="12"/>
+      <x:c r="AW150" s="12" t="n">
+        <x:v>0.0016</x:v>
+      </x:c>
+      <x:c r="AX150" s="12"/>
+      <x:c r="AY150" s="12"/>
+      <x:c r="AZ150" s="12"/>
+      <x:c r="BA150" s="12"/>
+      <x:c r="BB150" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="BC150" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD150" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE150" s="12" t="str">
+        <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF150" s="12" t="str">
+        <x:v>Primary publisher PDF indexed text Table1. Individual rare-earth species unreported; total RE not assigned to Ce/La. No sample-specific numerical icorr table; no estimated polarization-curve extraction. Direct download endpoint404; indexed primary text used.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="40" customHeight="1">
+      <x:c r="A151" s="12" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B151" s="13" t="str">
+        <x:v>Cu-P계 내후성강 (RE 0~0.064wt% 첨가)</x:v>
+      </x:c>
+      <x:c r="C151" s="13" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="D151" s="14" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+      <x:c r="E151" s="14" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="F151" s="14" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="G151" s="14" t="n">
+        <x:v>0.086</x:v>
+      </x:c>
+      <x:c r="H151" s="14" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="I151" s="14" t="n">
+        <x:v>0.47</x:v>
+      </x:c>
+      <x:c r="J151" s="14" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K151" s="14"/>
+      <x:c r="L151" s="14" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="M151" s="14"/>
+      <x:c r="N151" s="14"/>
+      <x:c r="O151" s="14"/>
+      <x:c r="P151" s="14"/>
+      <x:c r="Q151" s="14" t="n">
+        <x:v>0.038</x:v>
+      </x:c>
+      <x:c r="R151" s="14"/>
+      <x:c r="S151" s="14"/>
+      <x:c r="T151" s="14"/>
+      <x:c r="U151" s="14"/>
+      <x:c r="V151" s="14"/>
+      <x:c r="W151" s="14"/>
+      <x:c r="X151" s="14"/>
+      <x:c r="Y151" s="12"/>
+      <x:c r="Z151" s="12"/>
+      <x:c r="AA151" s="15"/>
+      <x:c r="AB151" s="15"/>
+      <x:c r="AC151" s="12"/>
+      <x:c r="AD151" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE151" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="AF151" s="12"/>
+      <x:c r="AG151" s="12"/>
+      <x:c r="AH151" s="12"/>
+      <x:c r="AI151" s="12"/>
+      <x:c r="AJ151" s="12"/>
+      <x:c r="AK151" s="16"/>
+      <x:c r="AL151" s="16"/>
+      <x:c r="AM151" s="12" t="str">
+        <x:v>WM44_C</x:v>
+      </x:c>
+      <x:c r="AN151" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO151" s="12" t="str">
+        <x:v>https://www.anticorr.org.tw/JCCE/paper/V26/260207.pdf</x:v>
+      </x:c>
+      <x:c r="AP151" s="12" t="str">
+        <x:v>Publisher paper Table1 printed p108; experimental Sec2.4</x:v>
+      </x:c>
+      <x:c r="AQ151" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR151" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS151" s="12"/>
+      <x:c r="AT151" s="12"/>
+      <x:c r="AU151" s="12"/>
+      <x:c r="AV151" s="12"/>
+      <x:c r="AW151" s="12" t="n">
+        <x:v>0.036</x:v>
+      </x:c>
+      <x:c r="AX151" s="12"/>
+      <x:c r="AY151" s="12"/>
+      <x:c r="AZ151" s="12"/>
+      <x:c r="BA151" s="12"/>
+      <x:c r="BB151" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="BC151" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD151" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE151" s="12" t="str">
+        <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF151" s="12" t="str">
+        <x:v>Primary publisher PDF indexed text Table1. Individual rare-earth species unreported; total RE not assigned to Ce/La. No sample-specific numerical icorr table; no estimated polarization-curve extraction. Direct download endpoint404; indexed primary text used.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="40" customHeight="1">
+      <x:c r="A152" s="12" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B152" s="13" t="str">
+        <x:v>Cu-P계 내후성강 (RE 0~0.064wt% 첨가)</x:v>
+      </x:c>
+      <x:c r="C152" s="13" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="D152" s="14" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="E152" s="14" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="F152" s="14" t="n">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="G152" s="14" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="H152" s="14" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="I152" s="14" t="n">
+        <x:v>0.49</x:v>
+      </x:c>
+      <x:c r="J152" s="14" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="K152" s="14"/>
+      <x:c r="L152" s="14" t="n">
+        <x:v>0.27</x:v>
+      </x:c>
+      <x:c r="M152" s="14"/>
+      <x:c r="N152" s="14"/>
+      <x:c r="O152" s="14"/>
+      <x:c r="P152" s="14"/>
+      <x:c r="Q152" s="14" t="n">
+        <x:v>0.038</x:v>
+      </x:c>
+      <x:c r="R152" s="14"/>
+      <x:c r="S152" s="14"/>
+      <x:c r="T152" s="14"/>
+      <x:c r="U152" s="14"/>
+      <x:c r="V152" s="14"/>
+      <x:c r="W152" s="14"/>
+      <x:c r="X152" s="14"/>
+      <x:c r="Y152" s="12"/>
+      <x:c r="Z152" s="12"/>
+      <x:c r="AA152" s="15"/>
+      <x:c r="AB152" s="15"/>
+      <x:c r="AC152" s="12"/>
+      <x:c r="AD152" s="12" t="str">
+        <x:v>NaCl</x:v>
+      </x:c>
+      <x:c r="AE152" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="AF152" s="12"/>
+      <x:c r="AG152" s="12"/>
+      <x:c r="AH152" s="12"/>
+      <x:c r="AI152" s="12"/>
+      <x:c r="AJ152" s="12"/>
+      <x:c r="AK152" s="16"/>
+      <x:c r="AL152" s="16"/>
+      <x:c r="AM152" s="12" t="str">
+        <x:v>WM44_D</x:v>
+      </x:c>
+      <x:c r="AN152" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AO152" s="12" t="str">
+        <x:v>https://www.anticorr.org.tw/JCCE/paper/V26/260207.pdf</x:v>
+      </x:c>
+      <x:c r="AP152" s="12" t="str">
+        <x:v>Publisher paper Table1 printed p108; experimental Sec2.4</x:v>
+      </x:c>
+      <x:c r="AQ152" s="12" t="str">
+        <x:v>primary_source_transcription</x:v>
+      </x:c>
+      <x:c r="AR152" s="12" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="AS152" s="12"/>
+      <x:c r="AT152" s="12"/>
+      <x:c r="AU152" s="12"/>
+      <x:c r="AV152" s="12"/>
+      <x:c r="AW152" s="12" t="n">
+        <x:v>0.064</x:v>
+      </x:c>
+      <x:c r="AX152" s="12"/>
+      <x:c r="AY152" s="12"/>
+      <x:c r="AZ152" s="12"/>
+      <x:c r="BA152" s="12"/>
+      <x:c r="BB152" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="BC152" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD152" s="17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE152" s="12" t="str">
+        <x:v>Mo; T.N.(Total Nitrogen); Nb; V; Ti; Sb; Ce; La; Pr; W; Y; La+Ce_합산; Fe; PREN; 열처리 온도(°C); Time(min); 냉각방식; 침지시간(min); 온도(°C); 기준전극; 주사속도(mV/s); Ecorr(V); icorr(A/cm2)</x:v>
+      </x:c>
+      <x:c r="BF152" s="12" t="str">
+        <x:v>Primary publisher PDF indexed text Table1. Individual rare-earth species unreported; total RE not assigned to Ce/La. No sample-specific numerical icorr table; no estimated polarization-curve extraction. Direct download endpoint404; indexed primary text used.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbec15820f3d491c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R464066b9093248d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14189,13 +18665,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="18" t="n">
-        <x:v>114</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B4" s="18" t="n">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C4" s="18" t="n">
-        <x:v>57</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D4" s="18" t="n">
         <x:v>0</x:v>
@@ -14231,14 +18707,14 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="B7" s="18" t="n">
-        <x:v>109</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C7" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D7" s="23" t="n">
         <x:f>B7/(B7+C7)</x:f>
-        <x:v>0.956140350877193</x:v>
+        <x:v>0.9668874172185431</x:v>
       </x:c>
       <x:c r="E7" s="18" t="str">
         <x:v>미보고 값을 0·평균·강종 대표값으로 채우지 않음</x:v>
@@ -14249,14 +18725,14 @@
         <x:v>Si</x:v>
       </x:c>
       <x:c r="B8" s="18" t="n">
-        <x:v>103</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C8" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D8" s="23" t="n">
         <x:f>B8/(B8+C8)</x:f>
-        <x:v>0.9035087719298246</x:v>
+        <x:v>0.8741721854304636</x:v>
       </x:c>
       <x:c r="E8" s="18" t="str">
         <x:v>표면 산화물·침투제 첨가량을 벌크 RE 함량으로 바꾸지 않음</x:v>
@@ -14267,14 +18743,14 @@
         <x:v>Mn</x:v>
       </x:c>
       <x:c r="B9" s="18" t="n">
-        <x:v>109</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C9" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="23" t="n">
         <x:f>B9/(B9+C9)</x:f>
-        <x:v>0.956140350877193</x:v>
+        <x:v>0.9006622516556292</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
         <x:v>Ipass·공식전위·질량감소를 icorr로 바꾸지 않음</x:v>
@@ -14285,14 +18761,14 @@
         <x:v>P</x:v>
       </x:c>
       <x:c r="B10" s="18" t="n">
-        <x:v>81</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C10" s="18" t="n">
-        <x:v>33</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="23" t="n">
         <x:f>B10/(B10+C10)</x:f>
-        <x:v>0.7105263157894737</x:v>
+        <x:v>0.6821192052980133</x:v>
       </x:c>
       <x:c r="E10" s="18" t="str">
         <x:v>전체 컬럼 기준으로 학습에 투입 가능한 행: 0</x:v>
@@ -14303,17 +18779,17 @@
         <x:v>S</x:v>
       </x:c>
       <x:c r="B11" s="18" t="n">
-        <x:v>76</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C11" s="18" t="n">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D11" s="23" t="n">
         <x:f>B11/(B11+C11)</x:f>
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.6490066225165563</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
-        <x:v>신규 수집 82행. 기존 자료 32행은 이번에 전체 원문 재검증하지 않음</x:v>
+        <x:v>신규 수집 119행. 기존 자료 32행은 이번에 전체 원문 재검증하지 않음</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
@@ -14321,17 +18797,17 @@
         <x:v>Cr</x:v>
       </x:c>
       <x:c r="B12" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C12" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D12" s="23" t="n">
         <x:f>B12/(B12+C12)</x:f>
-        <x:v>0.6929824561403509</x:v>
+        <x:v>0.7549668874172185</x:v>
       </x:c>
       <x:c r="E12" s="18" t="str">
-        <x:v>49편 중 23편은 원문 재확보·추출이 남아 있음</x:v>
+        <x:v>49편 중 14편은 원문 재확보·추출이 남아 있음</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
@@ -14339,14 +18815,14 @@
         <x:v>Ni</x:v>
       </x:c>
       <x:c r="B13" s="18" t="n">
-        <x:v>59</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C13" s="18" t="n">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D13" s="23" t="n">
         <x:f>B13/(B13+C13)</x:f>
-        <x:v>0.5175438596491229</x:v>
+        <x:v>0.5695364238410596</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
         <x:v>원본 데이터마이닝 시트의 행 연결 오류를 그대로 학습하지 않음</x:v>
@@ -14357,14 +18833,14 @@
         <x:v>Mo</x:v>
       </x:c>
       <x:c r="B14" s="18" t="n">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C14" s="18" t="n">
-        <x:v>73</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D14" s="23" t="n">
         <x:f>B14/(B14+C14)</x:f>
-        <x:v>0.35964912280701755</x:v>
+        <x:v>0.31788079470198677</x:v>
       </x:c>
       <x:c r="E14" s="18" t="str">
         <x:v>공란은 미확보 값. 표의 Balance는 원문 표기이며 수치가 아님</x:v>
@@ -14375,14 +18851,14 @@
         <x:v>Cu</x:v>
       </x:c>
       <x:c r="B15" s="18" t="n">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C15" s="18" t="n">
-        <x:v>68</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D15" s="23" t="n">
         <x:f>B15/(B15+C15)</x:f>
-        <x:v>0.40350877192982454</x:v>
+        <x:v>0.41721854304635764</x:v>
       </x:c>
       <x:c r="E15" s="18"/>
     </x:row>
@@ -14391,14 +18867,14 @@
         <x:v>T.N.(Total Nitrogen)</x:v>
       </x:c>
       <x:c r="B16" s="18" t="n">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="18" t="n">
-        <x:v>88</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D16" s="23" t="n">
         <x:f>B16/(B16+C16)</x:f>
-        <x:v>0.22807017543859648</x:v>
+        <x:v>0.2251655629139073</x:v>
       </x:c>
       <x:c r="E16" s="18"/>
     </x:row>
@@ -14407,14 +18883,14 @@
         <x:v>Nb</x:v>
       </x:c>
       <x:c r="B17" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C17" s="18" t="n">
-        <x:v>111</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D17" s="23" t="n">
         <x:f>B17/(B17+C17)</x:f>
-        <x:v>0.02631578947368421</x:v>
+        <x:v>0.06622516556291391</x:v>
       </x:c>
       <x:c r="E17" s="18"/>
     </x:row>
@@ -14423,14 +18899,14 @@
         <x:v>V</x:v>
       </x:c>
       <x:c r="B18" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="18" t="n">
-        <x:v>110</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D18" s="23" t="n">
         <x:f>B18/(B18+C18)</x:f>
-        <x:v>0.03508771929824561</x:v>
+        <x:v>0.052980132450331126</x:v>
       </x:c>
       <x:c r="E18" s="18"/>
     </x:row>
@@ -14442,11 +18918,11 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C19" s="18" t="n">
-        <x:v>99</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D19" s="23" t="n">
         <x:f>B19/(B19+C19)</x:f>
-        <x:v>0.13157894736842105</x:v>
+        <x:v>0.09933774834437085</x:v>
       </x:c>
       <x:c r="E19" s="18"/>
     </x:row>
@@ -14455,14 +18931,14 @@
         <x:v>Al</x:v>
       </x:c>
       <x:c r="B20" s="18" t="n">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C20" s="18" t="n">
-        <x:v>83</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D20" s="23" t="n">
         <x:f>B20/(B20+C20)</x:f>
-        <x:v>0.2719298245614035</x:v>
+        <x:v>0.36423841059602646</x:v>
       </x:c>
       <x:c r="E20" s="18"/>
     </x:row>
@@ -14474,7 +18950,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C21" s="18" t="n">
-        <x:v>114</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D21" s="23" t="n">
         <x:f>B21/(B21+C21)</x:f>
@@ -14487,14 +18963,14 @@
         <x:v>Ce</x:v>
       </x:c>
       <x:c r="B22" s="18" t="n">
-        <x:v>39</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C22" s="18" t="n">
-        <x:v>75</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D22" s="23" t="n">
         <x:f>B22/(B22+C22)</x:f>
-        <x:v>0.34210526315789475</x:v>
+        <x:v>0.3841059602649007</x:v>
       </x:c>
       <x:c r="E22" s="18"/>
     </x:row>
@@ -14503,14 +18979,14 @@
         <x:v>La</x:v>
       </x:c>
       <x:c r="B23" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="18" t="n">
-        <x:v>103</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D23" s="23" t="n">
         <x:f>B23/(B23+C23)</x:f>
-        <x:v>0.09649122807017543</x:v>
+        <x:v>0.10596026490066225</x:v>
       </x:c>
       <x:c r="E23" s="18"/>
     </x:row>
@@ -14522,11 +18998,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C24" s="18" t="n">
-        <x:v>113</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D24" s="23" t="n">
         <x:f>B24/(B24+C24)</x:f>
-        <x:v>0.008771929824561403</x:v>
+        <x:v>0.006622516556291391</x:v>
       </x:c>
       <x:c r="E24" s="18"/>
     </x:row>
@@ -14538,11 +19014,11 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C25" s="18" t="n">
-        <x:v>107</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D25" s="23" t="n">
         <x:f>B25/(B25+C25)</x:f>
-        <x:v>0.06140350877192982</x:v>
+        <x:v>0.046357615894039736</x:v>
       </x:c>
       <x:c r="E25" s="18"/>
     </x:row>
@@ -14554,11 +19030,11 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="18" t="n">
-        <x:v>103</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D26" s="23" t="n">
         <x:f>B26/(B26+C26)</x:f>
-        <x:v>0.09649122807017543</x:v>
+        <x:v>0.0728476821192053</x:v>
       </x:c>
       <x:c r="E26" s="18"/>
     </x:row>
@@ -14567,14 +19043,14 @@
         <x:v>La+Ce_합산</x:v>
       </x:c>
       <x:c r="B27" s="18" t="n">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="18" t="n">
-        <x:v>96</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D27" s="23" t="n">
         <x:f>B27/(B27+C27)</x:f>
-        <x:v>0.15789473684210525</x:v>
+        <x:v>0.152317880794702</x:v>
       </x:c>
       <x:c r="E27" s="18"/>
     </x:row>
@@ -14583,14 +19059,14 @@
         <x:v>Fe</x:v>
       </x:c>
       <x:c r="B28" s="18" t="n">
-        <x:v>43</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="18" t="n">
-        <x:v>71</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D28" s="23" t="n">
         <x:f>B28/(B28+C28)</x:f>
-        <x:v>0.37719298245614036</x:v>
+        <x:v>0.37748344370860926</x:v>
       </x:c>
       <x:c r="E28" s="18"/>
     </x:row>
@@ -14599,14 +19075,14 @@
         <x:v>PREN</x:v>
       </x:c>
       <x:c r="B29" s="18" t="n">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C29" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D29" s="23" t="n">
         <x:f>B29/(B29+C29)</x:f>
-        <x:v>0.19298245614035087</x:v>
+        <x:v>0.15894039735099338</x:v>
       </x:c>
       <x:c r="E29" s="18"/>
     </x:row>
@@ -14615,14 +19091,14 @@
         <x:v>열처리 온도(°C)</x:v>
       </x:c>
       <x:c r="B30" s="18" t="n">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C30" s="18" t="n">
-        <x:v>86</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D30" s="23" t="n">
         <x:f>B30/(B30+C30)</x:f>
-        <x:v>0.24561403508771928</x:v>
+        <x:v>0.23841059602649006</x:v>
       </x:c>
       <x:c r="E30" s="18"/>
     </x:row>
@@ -14631,14 +19107,14 @@
         <x:v>Time(min)</x:v>
       </x:c>
       <x:c r="B31" s="18" t="n">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C31" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D31" s="23" t="n">
         <x:f>B31/(B31+C31)</x:f>
-        <x:v>0.21929824561403508</x:v>
+        <x:v>0.2185430463576159</x:v>
       </x:c>
       <x:c r="E31" s="18"/>
     </x:row>
@@ -14647,14 +19123,14 @@
         <x:v>냉각방식</x:v>
       </x:c>
       <x:c r="B32" s="18" t="n">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C32" s="18" t="n">
-        <x:v>78</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D32" s="23" t="n">
         <x:f>B32/(B32+C32)</x:f>
-        <x:v>0.3157894736842105</x:v>
+        <x:v>0.2913907284768212</x:v>
       </x:c>
       <x:c r="E32" s="18"/>
     </x:row>
@@ -14663,14 +19139,14 @@
         <x:v>전해질</x:v>
       </x:c>
       <x:c r="B33" s="18" t="n">
-        <x:v>103</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C33" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D33" s="23" t="n">
         <x:f>B33/(B33+C33)</x:f>
-        <x:v>0.9035087719298246</x:v>
+        <x:v>0.9139072847682119</x:v>
       </x:c>
       <x:c r="E33" s="18"/>
     </x:row>
@@ -14679,14 +19155,14 @@
         <x:v>전해질 농도(wt%)</x:v>
       </x:c>
       <x:c r="B34" s="18" t="n">
-        <x:v>60</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C34" s="18" t="n">
-        <x:v>54</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D34" s="23" t="n">
         <x:f>B34/(B34+C34)</x:f>
-        <x:v>0.5263157894736842</x:v>
+        <x:v>0.5496688741721855</x:v>
       </x:c>
       <x:c r="E34" s="18"/>
     </x:row>
@@ -14695,14 +19171,14 @@
         <x:v>침지시간(min)</x:v>
       </x:c>
       <x:c r="B35" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C35" s="18" t="n">
-        <x:v>99</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D35" s="23" t="n">
         <x:f>B35/(B35+C35)</x:f>
-        <x:v>0.13157894736842105</x:v>
+        <x:v>0.13245033112582782</x:v>
       </x:c>
       <x:c r="E35" s="18"/>
     </x:row>
@@ -14711,14 +19187,14 @@
         <x:v>온도(°C)</x:v>
       </x:c>
       <x:c r="B36" s="18" t="n">
-        <x:v>61</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C36" s="18" t="n">
-        <x:v>53</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D36" s="23" t="n">
         <x:f>B36/(B36+C36)</x:f>
-        <x:v>0.5350877192982456</x:v>
+        <x:v>0.46357615894039733</x:v>
       </x:c>
       <x:c r="E36" s="18"/>
     </x:row>
@@ -14727,14 +19203,14 @@
         <x:v>기준전극</x:v>
       </x:c>
       <x:c r="B37" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C37" s="18" t="n">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D37" s="23" t="n">
         <x:f>B37/(B37+C37)</x:f>
-        <x:v>0.8070175438596491</x:v>
+        <x:v>0.7880794701986755</x:v>
       </x:c>
       <x:c r="E37" s="18"/>
     </x:row>
@@ -14743,14 +19219,14 @@
         <x:v>주사속도(mV/s)</x:v>
       </x:c>
       <x:c r="B38" s="18" t="n">
-        <x:v>67</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C38" s="18" t="n">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D38" s="23" t="n">
         <x:f>B38/(B38+C38)</x:f>
-        <x:v>0.5877192982456141</x:v>
+        <x:v>0.5761589403973509</x:v>
       </x:c>
       <x:c r="E38" s="18"/>
     </x:row>
@@ -14759,14 +19235,14 @@
         <x:v>Ecorr(V)</x:v>
       </x:c>
       <x:c r="B39" s="18" t="n">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C39" s="18" t="n">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D39" s="23" t="n">
         <x:f>B39/(B39+C39)</x:f>
-        <x:v>0.4649122807017544</x:v>
+        <x:v>0.47019867549668876</x:v>
       </x:c>
       <x:c r="E39" s="18"/>
     </x:row>
@@ -14775,14 +19251,14 @@
         <x:v>icorr(A/cm2)</x:v>
       </x:c>
       <x:c r="B40" s="18" t="n">
-        <x:v>57</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C40" s="18" t="n">
-        <x:v>57</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D40" s="23" t="n">
         <x:f>B40/(B40+C40)</x:f>
-        <x:v>0.5</x:v>
+        <x:v>0.45695364238410596</x:v>
       </x:c>
       <x:c r="E40" s="18"/>
     </x:row>
@@ -14818,7 +19294,8 @@
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="46" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="90" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="46" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="90" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
@@ -14850,6 +19327,9 @@
         <x:v>this_batch_status</x:v>
       </x:c>
       <x:c r="J1" s="7" t="str">
+        <x:v>source_access_result</x:v>
+      </x:c>
+      <x:c r="K1" s="7" t="str">
         <x:v>workbook_note</x:v>
       </x:c>
     </x:row>
@@ -14882,6 +19362,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J2" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K2" s="2" t="str">
         <x:v>3.5wt% NaCl(탈기), REM(65Ce-35La 미쉬메탈) 0~0.057wt%, icorr 최대 83.3% 감소(가장 큰 개선폭)</x:v>
       </x:c>
     </x:row>
@@ -14914,6 +19397,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J3" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K3" s="2" t="str">
         <x:v>1M H2SO4 60°C, 용접금속 Y 0.0018~0.0023wt%, 부식속도(중량감소) 74.5% 감소</x:v>
       </x:c>
     </x:row>
@@ -14946,6 +19432,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J4" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K4" s="2" t="str">
         <x:v>3.5wt% NaCl, Tafel+EIS 수치 확보 완료 (icorr 최대 66.4% 감소)</x:v>
       </x:c>
     </x:row>
@@ -14978,6 +19467,9 @@
         <x:v>prior_dataset_retained</x:v>
       </x:c>
       <x:c r="J5" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K5" s="2" t="str">
         <x:v>3.5wt% NaCl, La/Ce/Pr 각각 첨가, icorr 최대 63.8% 감소(La 최적)</x:v>
       </x:c>
     </x:row>
@@ -15010,6 +19502,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J6" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K6" s="2" t="str">
         <x:v>해수침지 384h, Ce 0~1.97wt%(항균 겸용강 특성상 고농도), 1.02wt%에서 부식속도 56.9% 감소(과첨가 시 악화)</x:v>
       </x:c>
     </x:row>
@@ -15042,6 +19537,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J7" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K7" s="2" t="str">
         <x:v>공식성장지수(KI) 최대 69.9% 감소, 공식전위(Ep) 개선. icorr 수치는 원문 미제시</x:v>
       </x:c>
     </x:row>
@@ -15074,6 +19572,9 @@
         <x:v>prior_dataset_retained</x:v>
       </x:c>
       <x:c r="J8" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K8" s="2" t="str">
         <x:v>1M H2SO4+0.5M NaCl, Ce 0~0.056wt%(W 병용), icorr 최대 45.7% 감소</x:v>
       </x:c>
     </x:row>
@@ -15106,6 +19607,9 @@
         <x:v>prior_dataset_retained</x:v>
       </x:c>
       <x:c r="J9" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K9" s="2" t="str">
         <x:v>3.5wt% NaCl, Ce/La 각 0.002~0.003wt%, Ti/Zr탈산 시 icorr 44.8% 감소(Al탈산 대비 우수)</x:v>
       </x:c>
     </x:row>
@@ -15138,6 +19642,9 @@
         <x:v>prior_dataset_retained</x:v>
       </x:c>
       <x:c r="J10" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K10" s="2" t="str">
         <x:v>3.5wt% NaCl + 6wt% FeCl3(ASTM G48), Ce 0.0082% 첨가 시 icorr 44.3% 감소</x:v>
       </x:c>
     </x:row>
@@ -15170,6 +19677,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J11" s="2" t="str">
+        <x:v>no_public_source_identifier</x:v>
+      </x:c>
+      <x:c r="K11" s="2" t="str">
         <x:v>HNO3 전처리 후 0.6wt% NaCl, Ce 0.0143% 첨가 시 icorr 34.4% 감소(과첨가 시 저감률 오히려 축소)</x:v>
       </x:c>
     </x:row>
@@ -15202,6 +19712,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J12" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K12" s="2" t="str">
         <x:v>중성 염수분무(5일), Ce 0.0025% 첨가 시 부식속도 33.6% 감소</x:v>
       </x:c>
     </x:row>
@@ -15234,6 +19747,9 @@
         <x:v>prior_dataset_retained</x:v>
       </x:c>
       <x:c r="J13" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K13" s="2" t="str">
         <x:v>3.5wt% NaCl, Ce 0.0025%+La 0.0015% 첨가 시 icorr 33.2% 감소</x:v>
       </x:c>
     </x:row>
@@ -15266,6 +19782,9 @@
         <x:v>prior_dataset_retained</x:v>
       </x:c>
       <x:c r="J14" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K14" s="2" t="str">
         <x:v>모의 열대해양 습건반복, La+Ce 0.33% 합산 첨가 시 icorr 31.9% 감소</x:v>
       </x:c>
     </x:row>
@@ -15298,6 +19817,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J15" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K15" s="2" t="str">
         <x:v>3.5wt% NaCl, Ce 0.0019% 첨가 시 icorr 24.8% 감소</x:v>
       </x:c>
     </x:row>
@@ -15330,6 +19852,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J16" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K16" s="2" t="str">
         <x:v>10% NaCl, Ce 0.048% 첨가 시 공식전위 +232mV, 막저항 +53.3% 개선</x:v>
       </x:c>
     </x:row>
@@ -15362,6 +19887,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J17" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K17" s="2" t="str">
         <x:v>0.1mol/L NaCl, Y 0.014%(140ppm) 첨가 시 템퍼링에 의한 Ecorr저하 58.3% 완화, 20h침지 부식체적손실 46.6% 감소</x:v>
       </x:c>
     </x:row>
@@ -15394,6 +19922,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J18" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K18" s="2" t="str">
         <x:v>3.5% NaCl, Y 0.019% 첨가 시 공식전위 최고(-0.11V). 과첨가(0.049%)·과소첨가(0.007%)는 오히려 악화(비단조적)</x:v>
       </x:c>
     </x:row>
@@ -15411,10 +19942,10 @@
         <x:v>Verified</x:v>
       </x:c>
       <x:c r="E19" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F19" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G19" s="2" t="n">
         <x:v>0</x:v>
@@ -15423,9 +19954,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I19" s="2" t="str">
-        <x:v>not_transcribed_requires_source_review</x:v>
+        <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J19" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K19" s="2" t="str">
         <x:v>미소전기화학셀(0.1M NaCl), CeS 개재물강(Ce 0.091%)이 MnS강 대비 공식개시전위 약 2배(0.41→0.8V)</x:v>
       </x:c>
     </x:row>
@@ -15443,10 +19977,10 @@
         <x:v>Verified</x:v>
       </x:c>
       <x:c r="E20" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F20" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G20" s="2" t="n">
         <x:v>0</x:v>
@@ -15455,9 +19989,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I20" s="2" t="str">
-        <x:v>not_transcribed_requires_source_review</x:v>
+        <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J20" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K20" s="2" t="str">
         <x:v>CO2포화 3.5wt% NaCl. 단기시험에서 미량 Ce첨가(0.0057~0.0263%)가 오히려 부식속도를 증가시킴(부정적 결과) - 다만 4종 실험강 모두 상용 X100보다는 우수</x:v>
       </x:c>
     </x:row>
@@ -15490,6 +20027,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J21" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K21" s="2" t="str">
         <x:v>모의콘크리트공극액(Cl- 0~3.5%), RE(Ce+La) 0.012% 첨가가 Cr전용 시료보다 Rct를 오히려 낮춤(부정적 결과)</x:v>
       </x:c>
     </x:row>
@@ -15522,6 +20062,9 @@
         <x:v>prior_dataset_retained</x:v>
       </x:c>
       <x:c r="J22" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K22" s="2" t="str">
         <x:v>0.01mol/L NaHSO3(공업대기 모사), La 함량 증가에 따라 icorr 지속 감소(310ppm 최저). 정확한 단일 저감률은 baseline 수치 부재로 산출 불가</x:v>
       </x:c>
     </x:row>
@@ -15554,6 +20097,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J23" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K23" s="2" t="str">
         <x:v>조성만 확보, Tafel 수치는 그래프로만 제시되어 미확보</x:v>
       </x:c>
     </x:row>
@@ -15586,6 +20132,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J24" s="2" t="str">
+        <x:v>retrieval_failed</x:v>
+      </x:c>
+      <x:c r="K24" s="2" t="str">
         <x:v>Ce 0/0.015/0.045wt% 조성만 확보, 전기화학 수치는 원문 미공개</x:v>
       </x:c>
     </x:row>
@@ -15618,6 +20167,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J25" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K25" s="2" t="str">
         <x:v>조성 및 정성적 결과(PAI, 공식깊이) 확보, Ecorr/icorr는 그림으로만 제시되어 미확보</x:v>
       </x:c>
     </x:row>
@@ -15650,6 +20202,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J26" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K26" s="2" t="str">
         <x:v>Ce 0~0.034wt% 조성 확보, 공식전위는 그래프로만 제시(수치 없음)</x:v>
       </x:c>
     </x:row>
@@ -15667,10 +20222,10 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="E27" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F27" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G27" s="2" t="n">
         <x:v>0</x:v>
@@ -15679,9 +20234,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I27" s="2" t="str">
-        <x:v>not_transcribed_requires_source_review</x:v>
+        <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J27" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K27" s="2" t="str">
         <x:v>5wt% H2SO4 침지 부식속도(중량감소법) 확보 - Ce첨가가 오히려 부식속도 증가(26.7→39.6 g/mm²/day)</x:v>
       </x:c>
     </x:row>
@@ -15699,10 +20257,10 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="E28" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F28" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G28" s="2" t="n">
         <x:v>0</x:v>
@@ -15711,9 +20269,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="2" t="str">
-        <x:v>not_transcribed_requires_source_review</x:v>
+        <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J28" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K28" s="2" t="str">
         <x:v>베이스 조성표 확보, Ce 0.012% 시료의 Ecorr(-311.25mV)만 원문에 수치로 확인(최적)</x:v>
       </x:c>
     </x:row>
@@ -15746,6 +20307,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J29" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K29" s="2" t="str">
         <x:v>La 9~10.2ppm 조성 확보, 녹층 α/γ*비 개선 확인. Ecorr/icorr는 그래프로만 제시</x:v>
       </x:c>
     </x:row>
@@ -15778,6 +20342,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J30" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K30" s="2" t="str">
         <x:v>misch metal(REM) 합계 0.067wt% 첨가 - 원소별 분리 불가(2차 인용문헌 기반), 전기화학 수치 미확보</x:v>
       </x:c>
     </x:row>
@@ -15810,6 +20377,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J31" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K31" s="2" t="str">
         <x:v>모의 배연탈황 응축액(11.5%H2SO4+1.2%HCl+1.0%FeCl3+1.0%CuCl2, 30℃, SCE)에서 950℃/30min 시효재 비교. B+Ce 복합 미량첨가로 icorr이 7.41×10^-7 → 1.07×10^-7 A/cm²로 감소하고 Epit이 0.979 → 1.032 V로 상승.</x:v>
       </x:c>
     </x:row>
@@ -15842,6 +20412,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J32" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K32" s="2" t="str">
         <x:v>1M/4M HNO3 및 0.61M NaCl에서 SCE 기준 3 mV/s 동전위분극. Y2O3 분산강화 12Cr ODS가 1M HNO3와 NaCl에서 RE 무첨가 X46Cr13보다 icorr이 크게 낮고 Rp가 높음(1M HNO3에서 icorr 1.7 vs 429.8 µA/cm²).</x:v>
       </x:c>
     </x:row>
@@ -15874,6 +20447,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J33" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K33" s="2" t="str">
         <x:v>포화 Ca(OH)2 모의 콘크리트 공극액(pH 약 12.5), 25±1 C, SCE 기준, Pt 대극, 노출면적 1 cm2, 주사속도 0.33 mV/s, EIS 100 kHz~10 mHz(10 mV). Cl- 농도 0.5/1/2/3.5 wt% NaCl 조건별 Epass/Ipass 및 Rct 확보. RE는 La 60 wt%의 La-Ce 합금.</x:v>
       </x:c>
     </x:row>
@@ -15906,6 +20482,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J34" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K34" s="2" t="str">
         <x:v>희토류(Y2O3)는 강 중 고용이 아니라 침투제(49%Cr+Al2O3+2%NH4I) 첨가제 형태. 3.5wt% NaCl, SCE, 1 mV/s 분극 결과 REO 첨가 시 icorr이 오히려 증가(6.09×10⁻⁹→최대 5.30×10⁻⁸ A/cm²)하여 내식성은 저하, 층 두께는 4% REO에서 최대. / 주의: 원문 조성표 Cr·Ni 값이 316H 규격과 불일치(원문값 그대로 기재)</x:v>
       </x:c>
     </x:row>
@@ -15938,6 +20517,9 @@
         <x:v>prior_dataset_retained</x:v>
       </x:c>
       <x:c r="J35" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K35" s="2" t="str">
         <x:v>Ce 첨가로 Al2O3·MnS 계 개재물이 Ce2O2S, Ce2O2S-CeAlO3 로 개질됨. 3.5wt% NaCl, SCE 에서 동전위분극 결과 Ce 0.0195wt% 에서 icorr 최소, 공식전위 최고.</x:v>
       </x:c>
     </x:row>
@@ -15955,21 +20537,24 @@
         <x:v>Verified</x:v>
       </x:c>
       <x:c r="E36" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F36" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G36" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H36" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="2" t="str">
-        <x:v>not_transcribed_requires_source_review</x:v>
+        <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J36" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K36" s="2" t="str">
         <x:v>腐蚀与防护 2024, 45(3): 37-46. 염수분무(GB/T 10125-2005 준용 표기, 5 wt% NaCl 중성, 35 C 연속분무) 및 3.5% NaCl 용액 중 분극곡선/EIS 측정. 조성은 표1, 분극 결과는 표3, EIS 결과는 표4에서 확인.</x:v>
       </x:c>
     </x:row>
@@ -16002,6 +20587,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J37" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K37" s="2" t="str">
         <x:v>REE-Si-Fe(Ce 12.56/La 4.43/Nd 1.41/Pr 0.55/Sm 4.53 wt% 함유) 를 플럭스에 0~1.0wt% 첨가한 용착금속. 3.5wt% NaCl, SCE, 1 mV/s 동전위분극과 EIS 수행. 희토류 첨가로 icorr 이 24.9 → 13.4 µA/cm2 까지 감소.</x:v>
       </x:c>
     </x:row>
@@ -16034,6 +20622,9 @@
         <x:v>prior_dataset_retained</x:v>
       </x:c>
       <x:c r="J38" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K38" s="2" t="str">
         <x:v>Ce 0/6/10 ppm 3종을 9일 염수분무(salt spray) 후 3.5wt% NaCl에서 동전위분극·EIS 평가. 미량 Ce 첨가로 icorr 약 30~33% 감소, Rct 149→283.5 Ω·cm2 증가, 청도 3개월 옥외폭로 부식속도도 0.0752→0.0665 mm/a로 감소.</x:v>
       </x:c>
     </x:row>
@@ -16066,6 +20657,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J39" s="2" t="str">
+        <x:v>retrieval_failed</x:v>
+      </x:c>
+      <x:c r="K39" s="2" t="str">
         <x:v>La 20 ppm 첨가로 MnS 가 La 산황화물 복합 개재물로 개질됨. NaHSO3 (1.0±0.05)×10-2 mol/L, 35 ℃ 주기부식 환경에서 0분·180분 시점 분극 측정, La 첨가재의 Icorr 이 더 낮음. DOI 는 원문에서 확인하지 못해 N/A.</x:v>
       </x:c>
     </x:row>
@@ -16083,10 +20677,10 @@
         <x:v>Verified</x:v>
       </x:c>
       <x:c r="E40" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F40" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G40" s="2" t="n">
         <x:v>0</x:v>
@@ -16095,9 +20689,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="2" t="str">
-        <x:v>not_transcribed_requires_source_review</x:v>
+        <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J40" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K40" s="2" t="str">
         <x:v>3.5wt% NaCl(상온, SCE, 0.333 mV/s)에서 모재와 조립열영향부(CGHAZ) 비교. CGHAZ의 icorr가 모재보다 크고 Rct는 낮아 국부부식 저항이 열위. RE 함량은 Al+Ca+Zr+Ti+RE 합산 0.04wt%로만 표기되어 개별 RE 값 확인 불가.</x:v>
       </x:c>
     </x:row>
@@ -16130,6 +20727,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J41" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K41" s="2" t="str">
         <x:v>3.5% NaCl(30±1℃, SCE)에서 RE 0~0.198 wt% 4종 비교. EIS 전하이동저항 Rt가 RE 0.198%에서 3.68×10^4 → 8.79×10^4 Ω·cm²로 약 2.4배 증가했고, Ecorr/icorr/Epit은 Fig.15~16 그래프로만 제시됨.</x:v>
       </x:c>
     </x:row>
@@ -16162,6 +20762,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J42" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K42" s="2" t="str">
         <x:v>Ce 0.004% 함유 S31254를 고용처리 및 800~900℃ 시효 후 10% NaCl(25℃, SCE)에서 평가. 고용재의 Epit 1.137 V, icorr 2.11×10^-7 A/cm², Rct 2138.8 Ω·cm²이며 시효온도 상승에 따라 σ상 석출로 열화됨.</x:v>
       </x:c>
     </x:row>
@@ -16179,21 +20782,24 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="E43" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F43" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G43" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H43" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I43" s="2" t="str">
-        <x:v>not_transcribed_requires_source_review</x:v>
+        <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J43" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K43" s="2" t="str">
         <x:v>3.5% NaCl(pH 6.5, ~25℃, SCE, 10 mV/s)에서 Ce 산화막 표면농도(at%) 증가에 따라 icorr이 6.0×10^-7 → 6.9×10^-8 A/cm²로 감소하고 Epit이 -0.065 → +0.091 V로 상승. 희토류가 벌크 합금원소가 아니라 전착 산화막 형태이며 조성은 강종 공칭치와 표면 Ce at%만 확인됨.</x:v>
       </x:c>
     </x:row>
@@ -16226,6 +20832,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J44" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K44" s="2" t="str">
         <x:v>건습교대 침지(wet-dry cycle immersion) 시험. RE(Ce+La) 첨가재가 부식속도 저하 및 녹층 α-FeOOH 분율 증가(Q235B 28%→35%)를 보였으나, 부식속도는 그래프(Figure 2)로만 제시되고 Ecorr/icorr/Rct 수치는 원문 표에 없음.</x:v>
       </x:c>
     </x:row>
@@ -16243,10 +20852,10 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="E45" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F45" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G45" s="2" t="n">
         <x:v>0</x:v>
@@ -16255,9 +20864,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="2" t="str">
-        <x:v>not_transcribed_requires_source_review</x:v>
+        <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J45" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K45" s="2" t="str">
         <x:v>0.05wt% NaCl 분무(35℃ 4h)/건조(60℃ 20h) 건습 반복 10·20·30 사이클 가속 대기부식 후 녹층 분석. 탈기 0.05wt% NaCl에서 Tafel 외삽을 수행했으나 시료별 Ecorr/icorr 수치는 제시되지 않고 전체 icorr 범위(약 1e-5~1e-4 A/cm2)만 기술됨.</x:v>
       </x:c>
     </x:row>
@@ -16290,6 +20902,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J46" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K46" s="2" t="str">
         <x:v>La 0/0.0075/0.0184/0.0425wt% 4종의 조성표는 원문에서 확인되나, 이 세션에서 확인한 페이지 내용에는 시료별 Ecorr/icorr/Rct/부식속도 수치가 제시되지 않음(전해질·기준전극 정보도 미확인).</x:v>
       </x:c>
     </x:row>
@@ -16322,6 +20937,9 @@
         <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J47" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K47" s="2" t="str">
         <x:v>인공해수(25 °C, ACLE, 1667 mV/s) 분극에서 Ecorr·항복전위(Eb)·ΔE만 제시되고 icorr·Rct 수치는 없음. Y2O3 증가에 따라 Eb·ΔE가 감소해 내공식성이 저하되며 SL-EPR QPa도 감소. 원소 조성표는 원문에 없어 조성행은 Y2O3 첨가량 기준으로만 기재(Partial).</x:v>
       </x:c>
     </x:row>
@@ -16339,10 +20957,10 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="E48" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F48" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G48" s="2" t="n">
         <x:v>0</x:v>
@@ -16351,9 +20969,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="2" t="str">
-        <x:v>not_transcribed_requires_source_review</x:v>
+        <x:v>primary_source_transcribed</x:v>
       </x:c>
       <x:c r="J48" s="2" t="str">
+        <x:v>record_sources_linked</x:v>
+      </x:c>
+      <x:c r="K48" s="2" t="str">
         <x:v>Ce 0.0144 + La 0.0064 wt% 첨가강과 무첨가 Q355 비교. 부식생성물 XRD 정량(α-FeOOH 40.8→46.2%, α/γ 19.4→35.5)은 확보했으나 Ecorr/icorr/Rct 등 전기화학 수치는 접근한 페이지에서 확인되지 않아 null 처리.</x:v>
       </x:c>
     </x:row>
@@ -16386,6 +21007,9 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J49" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K49" s="2" t="str">
         <x:v>침투제(49%Al2O3+45%Nb-Fe+5%NH4Cl)에 La2O3/CeO2/Y2O3/Nd2O3를 첨가해 950 °C/6 h 니오븀화. 3.5wt% NaCl 분극에서 2% La2O3가 icorr 최소(5.24×10⁻⁷ A/cm²), Y2O3·Nd2O3는 8×10⁻⁶ 수준으로 열세. GCr15 자체 조성표는 원문에 없어 Partial.</x:v>
       </x:c>
     </x:row>
@@ -16418,13 +21042,16 @@
         <x:v>not_transcribed_requires_source_review</x:v>
       </x:c>
       <x:c r="J50" s="2" t="str">
+        <x:v>landing_page_or_document_retrieved_not_table_verified</x:v>
+      </x:c>
+      <x:c r="K50" s="2" t="str">
         <x:v>Y(NO3)3 에탄올 용액에서 전착으로 2×10⁻⁶ kg/m² Y을 표면에 침적한 뒤 1173 K 공기 중 등온·열싸이클 산화시험(수용액 전기화학 데이터 없음). Y 침적재가 미침적재보다 산화속도가 낮고 스케일 박리 저항이 향상.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Read2d5c9cbed4358"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a89f132f43740a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>